--- a/cut_plan.xlsx
+++ b/cut_plan.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G241"/>
+  <dimension ref="A1:G249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -543,7 +543,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 94% | 1 חתיכות</t>
+          <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
         </is>
       </c>
     </row>
@@ -558,11 +558,11 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>9060×940 #1 ח1/5</t>
+          <t>5330×780 #1 ח1/3</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>940</v>
+        <v>780</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>2000</v>
@@ -582,7 +582,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 94% | 1 חתיכות</t>
+          <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
         </is>
       </c>
     </row>
@@ -597,11 +597,11 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>9060×940 #1 ח2/5</t>
+          <t>5330×780 #1 ח2/3</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>940</v>
+        <v>780</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>2000</v>
@@ -621,7 +621,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 94% | 1 חתיכות</t>
+          <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
         </is>
       </c>
     </row>
@@ -636,11 +636,11 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>9060×940 #1 ח3/5</t>
+          <t>5330×780 #2 ח1/3</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>940</v>
+        <v>780</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2000</v>
@@ -660,7 +660,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 94% | 1 חתיכות</t>
+          <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
         </is>
       </c>
     </row>
@@ -675,11 +675,11 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>9060×940 #1 ח4/5</t>
+          <t>5330×780 #2 ח2/3</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>940</v>
+        <v>780</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>2000</v>
@@ -699,7 +699,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 94% | 1 חתיכות</t>
+          <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
         </is>
       </c>
     </row>
@@ -714,11 +714,11 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>9060×940 #2 ח1/5</t>
+          <t>5330×780 #3 ח1/3</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>940</v>
+        <v>780</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>2000</v>
@@ -738,7 +738,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 94% | 1 חתיכות</t>
+          <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
         </is>
       </c>
     </row>
@@ -753,11 +753,11 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>9060×940 #2 ח2/5</t>
+          <t>5330×780 #3 ח2/3</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>940</v>
+        <v>780</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>2000</v>
@@ -777,7 +777,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 94% | 1 חתיכות</t>
+          <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
         </is>
       </c>
     </row>
@@ -792,11 +792,11 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>9060×940 #2 ח3/5</t>
+          <t>5330×780 #4 ח1/3</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>940</v>
+        <v>780</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>2000</v>
@@ -816,7 +816,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 94% | 1 חתיכות</t>
+          <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
         </is>
       </c>
     </row>
@@ -831,11 +831,11 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>9060×940 #2 ח4/5</t>
+          <t>5330×780 #4 ח2/3</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>940</v>
+        <v>780</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>2000</v>
@@ -855,7 +855,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 94% | 1 חתיכות</t>
+          <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
         </is>
       </c>
     </row>
@@ -870,11 +870,11 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>9060×940 #3 ח1/5</t>
+          <t>5330×780 #5 ח1/3</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>940</v>
+        <v>780</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>2000</v>
@@ -894,7 +894,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 94% | 1 חתיכות</t>
+          <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
         </is>
       </c>
     </row>
@@ -909,11 +909,11 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>9060×940 #3 ח2/5</t>
+          <t>5330×780 #5 ח2/3</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>940</v>
+        <v>780</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>2000</v>
@@ -933,7 +933,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 94% | 1 חתיכות</t>
+          <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
         </is>
       </c>
     </row>
@@ -948,11 +948,11 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>9060×940 #3 ח3/5</t>
+          <t>5330×780 #6 ח1/3</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>940</v>
+        <v>780</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>2000</v>
@@ -972,7 +972,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 94% | 1 חתיכות</t>
+          <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
         </is>
       </c>
     </row>
@@ -987,11 +987,11 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>9060×940 #3 ח4/5</t>
+          <t>5330×780 #6 ח2/3</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>940</v>
+        <v>780</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>2000</v>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 94% | 1 חתיכות</t>
+          <t>1000x2000 | ניצול 77% | 2 חתיכות</t>
         </is>
       </c>
     </row>
@@ -1026,14 +1026,14 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>9060×940 #4 ח1/5</t>
+          <t>5330×780 #1 ח3/3</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>940</v>
+        <v>780</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>2000</v>
+        <v>1330</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>0</v>
@@ -1043,59 +1043,74 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>1000x2000</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>780×640 #1</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>780</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>לוח 14</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>1000x2000 | ניצול 94% | 1 חתיכות</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>1000x2000 | ניצול 77% | 2 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>1000x2000</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>9060×940 #4 ח2/5</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>940</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>לוח 15</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>1000x2000 | ניצול 94% | 1 חתיכות</t>
-        </is>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>5330×780 #2 ח3/3</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>780</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>1330</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
@@ -1104,115 +1119,130 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>9060×940 #4 ח3/5</t>
+          <t>780×640 #2</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>940</v>
+        <v>780</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>2000</v>
+        <v>640</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>לוח 16</t>
+          <t>לוח 15</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 94% | 1 חתיכות</t>
+          <t>1000x2000 | ניצול 77% | 2 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>1000x2000</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>5330×780 #3 ח3/3</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>780</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>1330</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>1000x2000</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>780×640 #3</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>780</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>לוח 16</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>1000x2000 | ניצול 77% | 2 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>1000x2000</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>9060×940 #4 ח4/5</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>940</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>לוח 17</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>1000x2000 | ניצול 94% | 1 חתיכות</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>1000x2000</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>9060×940 #5 ח1/5</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>940</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>לוח 18</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>1000x2000 | ניצול 94% | 1 חתיכות</t>
-        </is>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>5330×780 #4 ח3/3</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>780</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>1330</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
@@ -1221,37 +1251,37 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>9060×940 #5 ח2/5</t>
+          <t>780×640 #4</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>940</v>
+        <v>780</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>2000</v>
+        <v>640</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>לוח 19</t>
+          <t>לוח 17</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 94% | 1 חתיכות</t>
+          <t>1000x2000 | ניצול 77% | 2 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
@@ -1260,14 +1290,14 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>9060×940 #5 ח3/5</t>
+          <t>5330×780 #5 ח3/3</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>940</v>
+        <v>780</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>2000</v>
+        <v>1330</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>0</v>
@@ -1277,59 +1307,74 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>לוח 20</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>1000x2000 | ניצול 94% | 1 חתיכות</t>
-        </is>
+      <c r="A40" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>1000x2000</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>780×640 #5</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>780</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>1330</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>לוח 18</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>1000x2000 | ניצול 77% | 2 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>1000x2000</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>9060×940 #5 ח4/5</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>940</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>לוח 21</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>1000x2000 | ניצול 94% | 1 חתיכות</t>
-        </is>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>5330×780 #6 ח3/3</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>780</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>1330</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
@@ -1338,37 +1383,37 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>9060×940 #6 ח1/5</t>
+          <t>780×640 #6</t>
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>940</v>
+        <v>780</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>2000</v>
+        <v>640</v>
       </c>
       <c r="F43" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>לוח 22</t>
+          <t>לוח 19</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 94% | 1 חתיכות</t>
+          <t>1000x2000 | ניצול 75% | 3 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
@@ -1377,14 +1422,14 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>9060×940 #6 ח2/5</t>
+          <t>780×640 #7</t>
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>940</v>
+        <v>780</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>2000</v>
+        <v>640</v>
       </c>
       <c r="F45" s="3" t="n">
         <v>0</v>
@@ -1394,20 +1439,35 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>לוח 23</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>1000x2000 | ניצול 94% | 1 חתיכות</t>
-        </is>
+      <c r="A46" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>1000x2000</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>780×640 #8</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>780</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>640</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
@@ -1416,37 +1476,37 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>9060×940 #6 ח3/5</t>
+          <t>780×640 #9</t>
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>940</v>
+        <v>780</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>2000</v>
+        <v>640</v>
       </c>
       <c r="F47" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>לוח 24</t>
+          <t>לוח 20</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 94% | 1 חתיכות</t>
+          <t>1000x2000 | ניצול 75% | 3 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
@@ -1455,14 +1515,14 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>9060×940 #6 ח4/5</t>
+          <t>780×640 #10</t>
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>940</v>
+        <v>780</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>2000</v>
+        <v>640</v>
       </c>
       <c r="F49" s="3" t="n">
         <v>0</v>
@@ -1472,20 +1532,35 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>לוח 25</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>1000x2000 | ניצול 80% | 1 חתיכות</t>
-        </is>
+      <c r="A50" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>1000x2000</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>780×640 #11</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>780</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>640</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
@@ -1494,53 +1569,53 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>9060×800 #1 ח1/5</t>
+          <t>780×640 #12</t>
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>800</v>
+        <v>780</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>2000</v>
+        <v>640</v>
       </c>
       <c r="F51" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>לוח 26</t>
+          <t>לוח 21</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 80% | 1 חתיכות</t>
+          <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>9060×800 #1 ח2/5</t>
+          <t>6160×1240 #1 ח1/6</t>
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F53" s="3" t="n">
         <v>0</v>
@@ -1552,34 +1627,34 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>לוח 27</t>
+          <t>לוח 22</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 80% | 1 חתיכות</t>
+          <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>9060×800 #1 ח3/5</t>
+          <t>6160×1240 #1 ח3/6</t>
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F55" s="3" t="n">
         <v>0</v>
@@ -1591,34 +1666,34 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>לוח 28</t>
+          <t>לוח 23</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 80% | 1 חתיכות</t>
+          <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>9060×800 #1 ח4/5</t>
+          <t>6160×1240 #2 ח1/6</t>
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F57" s="3" t="n">
         <v>0</v>
@@ -1630,34 +1705,34 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>לוח 29</t>
+          <t>לוח 24</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 80% | 1 חתיכות</t>
+          <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>9060×800 #2 ח1/5</t>
+          <t>6160×1240 #2 ח3/6</t>
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F59" s="3" t="n">
         <v>0</v>
@@ -1669,34 +1744,34 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>לוח 30</t>
+          <t>לוח 25</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 80% | 1 חתיכות</t>
+          <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>9060×800 #2 ח2/5</t>
+          <t>6160×1240 #3 ח1/6</t>
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F61" s="3" t="n">
         <v>0</v>
@@ -1708,34 +1783,34 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>לוח 31</t>
+          <t>לוח 26</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 80% | 1 חתיכות</t>
+          <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>9060×800 #2 ח3/5</t>
+          <t>6160×1240 #3 ח3/6</t>
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F63" s="3" t="n">
         <v>0</v>
@@ -1747,34 +1822,34 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>לוח 32</t>
+          <t>לוח 27</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 80% | 1 חתיכות</t>
+          <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>9060×800 #2 ח4/5</t>
+          <t>6160×1240 #4 ח1/6</t>
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F65" s="3" t="n">
         <v>0</v>
@@ -1786,34 +1861,34 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>לוח 33</t>
+          <t>לוח 28</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 80% | 1 חתיכות</t>
+          <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>9060×800 #3 ח1/5</t>
+          <t>6160×1240 #4 ח3/6</t>
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F67" s="3" t="n">
         <v>0</v>
@@ -1825,34 +1900,34 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>לוח 34</t>
+          <t>לוח 29</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 80% | 1 חתיכות</t>
+          <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>9060×800 #3 ח2/5</t>
+          <t>6160×1240 #5 ח1/6</t>
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F69" s="3" t="n">
         <v>0</v>
@@ -1864,34 +1939,34 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>לוח 35</t>
+          <t>לוח 30</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 80% | 1 חתיכות</t>
+          <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>9060×800 #3 ח3/5</t>
+          <t>6160×1240 #5 ח3/6</t>
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F71" s="3" t="n">
         <v>0</v>
@@ -1903,34 +1978,34 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>לוח 36</t>
+          <t>לוח 31</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 80% | 1 חתיכות</t>
+          <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>9060×800 #3 ח4/5</t>
+          <t>6160×1240 #6 ח1/6</t>
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F73" s="3" t="n">
         <v>0</v>
@@ -1942,34 +2017,34 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>לוח 37</t>
+          <t>לוח 32</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
+          <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>5330×780 #1 ח1/3</t>
+          <t>6160×1240 #6 ח3/6</t>
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>780</v>
+        <v>1000</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F75" s="3" t="n">
         <v>0</v>
@@ -1981,34 +2056,34 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>לוח 38</t>
+          <t>לוח 33</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
+          <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>5330×780 #1 ח2/3</t>
+          <t>6160×1200 #1 ח1/6</t>
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>780</v>
+        <v>1000</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F77" s="3" t="n">
         <v>0</v>
@@ -2020,34 +2095,34 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>לוח 39</t>
+          <t>לוח 34</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
+          <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>5330×780 #2 ח1/3</t>
+          <t>6160×1200 #1 ח3/6</t>
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>780</v>
+        <v>1000</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F79" s="3" t="n">
         <v>0</v>
@@ -2059,34 +2134,34 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>לוח 40</t>
+          <t>לוח 35</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
+          <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>5330×780 #2 ח2/3</t>
+          <t>6160×1200 #2 ח1/6</t>
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>780</v>
+        <v>1000</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F81" s="3" t="n">
         <v>0</v>
@@ -2098,34 +2173,34 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>לוח 41</t>
+          <t>לוח 36</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
+          <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>5330×780 #3 ח1/3</t>
+          <t>6160×1200 #2 ח3/6</t>
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>780</v>
+        <v>1000</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F83" s="3" t="n">
         <v>0</v>
@@ -2137,34 +2212,34 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>לוח 42</t>
+          <t>לוח 37</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
+          <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>5330×780 #3 ח2/3</t>
+          <t>6160×1200 #3 ח1/6</t>
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>780</v>
+        <v>1000</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F85" s="3" t="n">
         <v>0</v>
@@ -2176,34 +2251,34 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>לוח 43</t>
+          <t>לוח 38</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
+          <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>5330×780 #4 ח1/3</t>
+          <t>6160×1200 #3 ח3/6</t>
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>780</v>
+        <v>1000</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F87" s="3" t="n">
         <v>0</v>
@@ -2215,34 +2290,34 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>לוח 44</t>
+          <t>לוח 39</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
+          <t>1000x3000 | ניצול 100% | 4 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>5330×780 #4 ח2/3</t>
+          <t>9060×940 #1 ח1/4</t>
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>780</v>
+        <v>940</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F89" s="3" t="n">
         <v>0</v>
@@ -2252,192 +2327,237 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>לוח 45</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
-        </is>
+      <c r="A90" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>9060×940 #1 ח4/4</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>5330×780 #5 ח1/3</t>
+          <t>9060×940 #2 ח4/4</t>
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>780</v>
+        <v>60</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>2000</v>
+        <v>940</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>940</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>940</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>לוח 46</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
-        </is>
+      <c r="A92" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>9060×940 #3 ח4/4</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>1880</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t>1000x2000</t>
-        </is>
-      </c>
-      <c r="C93" s="3" t="inlineStr">
-        <is>
-          <t>5330×780 #5 ח2/3</t>
-        </is>
-      </c>
-      <c r="D93" s="3" t="n">
-        <v>780</v>
-      </c>
-      <c r="E93" s="3" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F93" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" s="3" t="n">
-        <v>0</v>
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>לוח 40</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 100% | 4 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>לוח 47</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
-        </is>
+      <c r="A94" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>9060×940 #1 ח2/4</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>5330×780 #6 ח1/3</t>
+          <t>9060×940 #4 ח4/4</t>
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>780</v>
+        <v>60</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>2000</v>
+        <v>940</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0</v>
+        <v>940</v>
       </c>
       <c r="G95" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>לוח 48</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
-        </is>
+      <c r="A96" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>9060×940 #5 ח4/4</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>940</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>5330×780 #6 ח2/3</t>
+          <t>9060×940 #6 ח4/4</t>
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>780</v>
+        <v>60</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>2000</v>
+        <v>940</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>0</v>
+        <v>940</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>0</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>לוח 49</t>
+          <t>לוח 41</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 77% | 2 חתיכות</t>
+          <t>1000x3000 | ניצול 99% | 4 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>5330×780 #1 ח3/3</t>
+          <t>9060×940 #1 ח3/4</t>
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>780</v>
+        <v>940</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>1330</v>
+        <v>3000</v>
       </c>
       <c r="F99" s="3" t="n">
         <v>0</v>
@@ -2448,194 +2568,194 @@
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>780×640 #1</t>
+          <t>9060×800 #1 ח4/4</t>
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>780</v>
+        <v>60</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>640</v>
+        <v>800</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>940</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>1330</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>לוח 50</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>1000x2000 | ניצול 77% | 2 חתיכות</t>
-        </is>
+      <c r="A101" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>9060×800 #2 ח4/4</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="G101" s="3" t="n">
+        <v>800</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>5330×780 #2 ח3/3</t>
+          <t>9060×800 #3 ח4/4</t>
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>780</v>
+        <v>60</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>1330</v>
+        <v>800</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>0</v>
+        <v>940</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>0</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="B103" s="3" t="inlineStr">
-        <is>
-          <t>1000x2000</t>
-        </is>
-      </c>
-      <c r="C103" s="3" t="inlineStr">
-        <is>
-          <t>780×640 #2</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="n">
-        <v>780</v>
-      </c>
-      <c r="E103" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="F103" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G103" s="3" t="n">
-        <v>1330</v>
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>לוח 42</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>לוח 51</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>1000x2000 | ניצול 77% | 2 חתיכות</t>
-        </is>
+      <c r="A104" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>9060×940 #2 ח1/4</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="B105" s="3" t="inlineStr">
-        <is>
-          <t>1000x2000</t>
-        </is>
-      </c>
-      <c r="C105" s="3" t="inlineStr">
-        <is>
-          <t>5330×780 #3 ח3/3</t>
-        </is>
-      </c>
-      <c r="D105" s="3" t="n">
-        <v>780</v>
-      </c>
-      <c r="E105" s="3" t="n">
-        <v>1330</v>
-      </c>
-      <c r="F105" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" s="3" t="n">
-        <v>0</v>
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>לוח 43</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>780×640 #3</t>
+          <t>9060×940 #2 ח2/4</t>
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>780</v>
+        <v>940</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>640</v>
+        <v>3000</v>
       </c>
       <c r="F106" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>1330</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>לוח 52</t>
+          <t>לוח 44</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 77% | 2 חתיכות</t>
+          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>5330×780 #4 ח3/3</t>
+          <t>9060×940 #2 ח3/4</t>
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>780</v>
+        <v>940</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>1330</v>
+        <v>3000</v>
       </c>
       <c r="F108" s="3" t="n">
         <v>0</v>
@@ -2645,129 +2765,114 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t>1000x2000</t>
-        </is>
-      </c>
-      <c r="C109" s="3" t="inlineStr">
-        <is>
-          <t>780×640 #4</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="n">
-        <v>780</v>
-      </c>
-      <c r="E109" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="F109" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G109" s="3" t="n">
-        <v>1330</v>
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>לוח 45</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>לוח 53</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>1000x2000 | ניצול 77% | 2 חתיכות</t>
-        </is>
+      <c r="A110" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>9060×940 #3 ח1/4</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="B111" s="3" t="inlineStr">
-        <is>
-          <t>1000x2000</t>
-        </is>
-      </c>
-      <c r="C111" s="3" t="inlineStr">
-        <is>
-          <t>5330×780 #5 ח3/3</t>
-        </is>
-      </c>
-      <c r="D111" s="3" t="n">
-        <v>780</v>
-      </c>
-      <c r="E111" s="3" t="n">
-        <v>1330</v>
-      </c>
-      <c r="F111" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G111" s="3" t="n">
-        <v>0</v>
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>לוח 46</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>780×640 #5</t>
+          <t>9060×940 #3 ח2/4</t>
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>780</v>
+        <v>940</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>640</v>
+        <v>3000</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>1330</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>לוח 54</t>
+          <t>לוח 47</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 77% | 2 חתיכות</t>
+          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>5330×780 #6 ח3/3</t>
+          <t>9060×940 #3 ח3/4</t>
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>780</v>
+        <v>940</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>1330</v>
+        <v>3000</v>
       </c>
       <c r="F114" s="3" t="n">
         <v>0</v>
@@ -2777,129 +2882,114 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="B115" s="3" t="inlineStr">
-        <is>
-          <t>1000x2000</t>
-        </is>
-      </c>
-      <c r="C115" s="3" t="inlineStr">
-        <is>
-          <t>780×640 #6</t>
-        </is>
-      </c>
-      <c r="D115" s="3" t="n">
-        <v>780</v>
-      </c>
-      <c r="E115" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="F115" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G115" s="3" t="n">
-        <v>1330</v>
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>לוח 48</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>לוח 55</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>1000x2000 | ניצול 87% | 2 חתיכות</t>
-        </is>
+      <c r="A116" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>9060×940 #4 ח1/4</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="B117" s="3" t="inlineStr">
-        <is>
-          <t>1000x2000</t>
-        </is>
-      </c>
-      <c r="C117" s="3" t="inlineStr">
-        <is>
-          <t>9060×940 #1 ח5/5</t>
-        </is>
-      </c>
-      <c r="D117" s="3" t="n">
-        <v>940</v>
-      </c>
-      <c r="E117" s="3" t="n">
-        <v>1060</v>
-      </c>
-      <c r="F117" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G117" s="3" t="n">
-        <v>0</v>
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>לוח 49</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>940×800 #1</t>
+          <t>9060×940 #4 ח2/4</t>
         </is>
       </c>
       <c r="D118" s="3" t="n">
-        <v>800</v>
+        <v>940</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>940</v>
+        <v>3000</v>
       </c>
       <c r="F118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>1060</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>לוח 56</t>
+          <t>לוח 50</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 87% | 2 חתיכות</t>
+          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>9060×940 #2 ח5/5</t>
+          <t>9060×940 #4 ח3/4</t>
         </is>
       </c>
       <c r="D120" s="3" t="n">
         <v>940</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>1060</v>
+        <v>3000</v>
       </c>
       <c r="F120" s="3" t="n">
         <v>0</v>
@@ -2909,129 +2999,114 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="B121" s="3" t="inlineStr">
-        <is>
-          <t>1000x2000</t>
-        </is>
-      </c>
-      <c r="C121" s="3" t="inlineStr">
-        <is>
-          <t>940×800 #2</t>
-        </is>
-      </c>
-      <c r="D121" s="3" t="n">
-        <v>800</v>
-      </c>
-      <c r="E121" s="3" t="n">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>לוח 51</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>9060×940 #5 ח1/4</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="F121" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G121" s="3" t="n">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>לוח 57</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>1000x2000 | ניצול 87% | 2 חתיכות</t>
-        </is>
+      <c r="E122" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="3" t="n">
-        <v>57</v>
-      </c>
-      <c r="B123" s="3" t="inlineStr">
-        <is>
-          <t>1000x2000</t>
-        </is>
-      </c>
-      <c r="C123" s="3" t="inlineStr">
-        <is>
-          <t>9060×940 #3 ח5/5</t>
-        </is>
-      </c>
-      <c r="D123" s="3" t="n">
-        <v>940</v>
-      </c>
-      <c r="E123" s="3" t="n">
-        <v>1060</v>
-      </c>
-      <c r="F123" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G123" s="3" t="n">
-        <v>0</v>
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>לוח 52</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>940×800 #3</t>
+          <t>9060×940 #5 ח2/4</t>
         </is>
       </c>
       <c r="D124" s="3" t="n">
-        <v>800</v>
+        <v>940</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>940</v>
+        <v>3000</v>
       </c>
       <c r="F124" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>1060</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>לוח 58</t>
+          <t>לוח 53</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 87% | 2 חתיכות</t>
+          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>9060×940 #4 ח5/5</t>
+          <t>9060×940 #5 ח3/4</t>
         </is>
       </c>
       <c r="D126" s="3" t="n">
         <v>940</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>1060</v>
+        <v>3000</v>
       </c>
       <c r="F126" s="3" t="n">
         <v>0</v>
@@ -3041,129 +3116,114 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="B127" s="3" t="inlineStr">
-        <is>
-          <t>1000x2000</t>
-        </is>
-      </c>
-      <c r="C127" s="3" t="inlineStr">
-        <is>
-          <t>940×800 #4</t>
-        </is>
-      </c>
-      <c r="D127" s="3" t="n">
-        <v>800</v>
-      </c>
-      <c r="E127" s="3" t="n">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>לוח 54</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>9060×940 #6 ח1/4</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="F127" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G127" s="3" t="n">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>לוח 59</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>1000x2000 | ניצול 87% | 2 חתיכות</t>
-        </is>
+      <c r="E128" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="B129" s="3" t="inlineStr">
-        <is>
-          <t>1000x2000</t>
-        </is>
-      </c>
-      <c r="C129" s="3" t="inlineStr">
-        <is>
-          <t>9060×940 #5 ח5/5</t>
-        </is>
-      </c>
-      <c r="D129" s="3" t="n">
-        <v>940</v>
-      </c>
-      <c r="E129" s="3" t="n">
-        <v>1060</v>
-      </c>
-      <c r="F129" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G129" s="3" t="n">
-        <v>0</v>
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>לוח 55</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>940×800 #5</t>
+          <t>9060×940 #6 ח2/4</t>
         </is>
       </c>
       <c r="D130" s="3" t="n">
-        <v>800</v>
+        <v>940</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>940</v>
+        <v>3000</v>
       </c>
       <c r="F130" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>1060</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>לוח 60</t>
+          <t>לוח 56</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 87% | 2 חתיכות</t>
+          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>9060×940 #6 ח5/5</t>
+          <t>9060×940 #6 ח3/4</t>
         </is>
       </c>
       <c r="D132" s="3" t="n">
         <v>940</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>1060</v>
+        <v>3000</v>
       </c>
       <c r="F132" s="3" t="n">
         <v>0</v>
@@ -3173,396 +3233,396 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="B133" s="3" t="inlineStr">
-        <is>
-          <t>1000x2000</t>
-        </is>
-      </c>
-      <c r="C133" s="3" t="inlineStr">
-        <is>
-          <t>940×800 #6</t>
-        </is>
-      </c>
-      <c r="D133" s="3" t="n">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>לוח 57</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 100% | 2 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>9060×800 #1 ח1/4</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="E133" s="3" t="n">
-        <v>940</v>
-      </c>
-      <c r="F133" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G133" s="3" t="n">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>לוח 61</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>1000x2000 | ניצול 67% | 2 חתיכות</t>
-        </is>
+      <c r="E134" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>9060×800 #1 ח5/5</t>
+          <t>6160×1200 #1 ח2/6</t>
         </is>
       </c>
       <c r="D135" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F135" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="E135" s="3" t="n">
-        <v>1060</v>
-      </c>
-      <c r="F135" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G135" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="B136" s="3" t="inlineStr">
-        <is>
-          <t>1000x2000</t>
-        </is>
-      </c>
-      <c r="C136" s="3" t="inlineStr">
-        <is>
-          <t>780×640 #7</t>
-        </is>
-      </c>
-      <c r="D136" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="E136" s="3" t="n">
-        <v>780</v>
-      </c>
-      <c r="F136" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G136" s="3" t="n">
-        <v>1060</v>
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>לוח 58</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 100% | 2 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>לוח 62</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>1000x2000 | ניצול 67% | 2 חתיכות</t>
-        </is>
+      <c r="A137" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>9060×800 #1 ח2/4</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F137" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>9060×800 #2 ח5/5</t>
+          <t>6160×1200 #1 ח4/6</t>
         </is>
       </c>
       <c r="D138" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F138" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="E138" s="3" t="n">
-        <v>1060</v>
-      </c>
-      <c r="F138" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G138" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="B139" s="3" t="inlineStr">
-        <is>
-          <t>1000x2000</t>
-        </is>
-      </c>
-      <c r="C139" s="3" t="inlineStr">
-        <is>
-          <t>780×640 #8</t>
-        </is>
-      </c>
-      <c r="D139" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="E139" s="3" t="n">
-        <v>780</v>
-      </c>
-      <c r="F139" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G139" s="3" t="n">
-        <v>1060</v>
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>לוח 59</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 100% | 2 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>לוח 63</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>1000x2000 | ניצול 67% | 2 חתיכות</t>
-        </is>
+      <c r="A140" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>9060×800 #1 ח3/4</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F140" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>9060×800 #3 ח5/5</t>
+          <t>6160×1200 #2 ח2/6</t>
         </is>
       </c>
       <c r="D141" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F141" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="E141" s="3" t="n">
-        <v>1060</v>
-      </c>
-      <c r="F141" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G141" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="B142" s="3" t="inlineStr">
-        <is>
-          <t>1000x2000</t>
-        </is>
-      </c>
-      <c r="C142" s="3" t="inlineStr">
-        <is>
-          <t>780×640 #9</t>
-        </is>
-      </c>
-      <c r="D142" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="E142" s="3" t="n">
-        <v>780</v>
-      </c>
-      <c r="F142" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G142" s="3" t="n">
-        <v>1060</v>
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>לוח 60</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 100% | 2 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>לוח 64</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>1000x2000 | ניצול 75% | 3 חתיכות</t>
-        </is>
+      <c r="A143" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>9060×800 #2 ח1/4</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F143" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>780×640 #10</t>
+          <t>6160×1200 #2 ח4/6</t>
         </is>
       </c>
       <c r="D144" s="3" t="n">
-        <v>780</v>
+        <v>200</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>640</v>
+        <v>3000</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="G144" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="B145" s="3" t="inlineStr">
-        <is>
-          <t>1000x2000</t>
-        </is>
-      </c>
-      <c r="C145" s="3" t="inlineStr">
-        <is>
-          <t>780×640 #11</t>
-        </is>
-      </c>
-      <c r="D145" s="3" t="n">
-        <v>780</v>
-      </c>
-      <c r="E145" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="F145" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G145" s="3" t="n">
-        <v>640</v>
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>לוח 61</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 100% | 2 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>780×640 #12</t>
+          <t>9060×800 #2 ח2/4</t>
         </is>
       </c>
       <c r="D146" s="3" t="n">
-        <v>780</v>
+        <v>800</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>640</v>
+        <v>3000</v>
       </c>
       <c r="F146" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>1280</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>לוח 65</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>1250x2500 | ניצול 99% | 1 חתיכות</t>
-        </is>
+      <c r="A147" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>6160×1200 #3 ח2/6</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F147" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="G147" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="3" t="n">
-        <v>65</v>
-      </c>
-      <c r="B148" s="3" t="inlineStr">
-        <is>
-          <t>1250x2500</t>
-        </is>
-      </c>
-      <c r="C148" s="3" t="inlineStr">
-        <is>
-          <t>6160×1240 #1 ח1/3</t>
-        </is>
-      </c>
-      <c r="D148" s="3" t="n">
-        <v>1240</v>
-      </c>
-      <c r="E148" s="3" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F148" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G148" s="3" t="n">
-        <v>0</v>
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>לוח 62</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 100% | 2 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>לוח 66</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>1250x2500 | ניצול 99% | 1 חתיכות</t>
-        </is>
+      <c r="A149" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>9060×800 #2 ח3/4</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F149" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G149" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>1250x2500</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>6160×1240 #1 ח2/3</t>
+          <t>6160×1200 #3 ח4/6</t>
         </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>1240</v>
+        <v>200</v>
       </c>
       <c r="E150" s="3" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="G150" s="3" t="n">
         <v>0</v>
@@ -3571,34 +3631,34 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>לוח 67</t>
+          <t>לוח 63</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>1250x2500 | ניצול 99% | 1 חתיכות</t>
+          <t>1000x3000 | ניצול 96% | 4 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>1250x2500</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>6160×1240 #2 ח1/3</t>
+          <t>9060×800 #3 ח1/4</t>
         </is>
       </c>
       <c r="D152" s="3" t="n">
-        <v>1240</v>
+        <v>800</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="F152" s="3" t="n">
         <v>0</v>
@@ -3608,192 +3668,237 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>לוח 68</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>1250x2500 | ניצול 99% | 1 חתיכות</t>
-        </is>
+      <c r="A153" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>6160×1240 #1 ח5/6</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="E153" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F153" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="G153" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>1250x2500</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>6160×1240 #2 ח2/3</t>
+          <t>6160×1240 #2 ח5/6</t>
         </is>
       </c>
       <c r="D154" s="3" t="n">
-        <v>1240</v>
+        <v>160</v>
       </c>
       <c r="E154" s="3" t="n">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>לוח 69</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>1250x2500 | ניצול 99% | 1 חתיכות</t>
-        </is>
+      <c r="A155" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>6160×1240 #3 ח5/6</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="E155" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F155" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="G155" s="3" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="3" t="n">
-        <v>69</v>
-      </c>
-      <c r="B156" s="3" t="inlineStr">
-        <is>
-          <t>1250x2500</t>
-        </is>
-      </c>
-      <c r="C156" s="3" t="inlineStr">
-        <is>
-          <t>6160×1240 #3 ח1/3</t>
-        </is>
-      </c>
-      <c r="D156" s="3" t="n">
-        <v>1240</v>
-      </c>
-      <c r="E156" s="3" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F156" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G156" s="3" t="n">
-        <v>0</v>
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>לוח 64</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 96% | 4 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="inlineStr">
-        <is>
-          <t>לוח 70</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>1250x2500 | ניצול 99% | 1 חתיכות</t>
-        </is>
+      <c r="A157" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>9060×800 #3 ח2/4</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="E157" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F157" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>1250x2500</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>6160×1240 #3 ח2/3</t>
+          <t>6160×1240 #4 ח5/6</t>
         </is>
       </c>
       <c r="D158" s="3" t="n">
-        <v>1240</v>
+        <v>160</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="G158" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>לוח 71</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>1250x2500 | ניצול 99% | 1 חתיכות</t>
-        </is>
+      <c r="A159" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>6160×1240 #5 ח5/6</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="E159" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F159" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="G159" s="3" t="n">
+        <v>1000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>1250x2500</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>6160×1240 #4 ח1/3</t>
+          <t>6160×1240 #6 ח5/6</t>
         </is>
       </c>
       <c r="D160" s="3" t="n">
-        <v>1240</v>
+        <v>160</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>לוח 72</t>
+          <t>לוח 65</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>1250x2500 | ניצול 99% | 1 חתיכות</t>
+          <t>1000x3000 | ניצול 96% | 4 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="3" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>1250x2500</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>6160×1240 #4 ח2/3</t>
+          <t>9060×800 #3 ח3/4</t>
         </is>
       </c>
       <c r="D162" s="3" t="n">
-        <v>1240</v>
+        <v>800</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="F162" s="3" t="n">
         <v>0</v>
@@ -3803,388 +3908,493 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>לוח 73</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>1250x2500 | ניצול 99% | 1 חתיכות</t>
-        </is>
+      <c r="A163" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>6160×1200 #1 ח5/6</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="E163" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F163" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="G163" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="3" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>1250x2500</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>6160×1240 #5 ח1/3</t>
+          <t>6160×1200 #2 ח5/6</t>
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>1240</v>
+        <v>160</v>
       </c>
       <c r="E164" s="3" t="n">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>לוח 74</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>1250x2500 | ניצול 99% | 1 חתיכות</t>
-        </is>
+      <c r="A165" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>6160×1200 #3 ח5/6</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="E165" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F165" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="G165" s="3" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="3" t="n">
-        <v>74</v>
-      </c>
-      <c r="B166" s="3" t="inlineStr">
-        <is>
-          <t>1250x2500</t>
-        </is>
-      </c>
-      <c r="C166" s="3" t="inlineStr">
-        <is>
-          <t>6160×1240 #5 ח2/3</t>
-        </is>
-      </c>
-      <c r="D166" s="3" t="n">
-        <v>1240</v>
-      </c>
-      <c r="E166" s="3" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F166" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G166" s="3" t="n">
-        <v>0</v>
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>לוח 66</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 91% | 11 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>לוח 75</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>1250x2500 | ניצול 99% | 1 חתיכות</t>
-        </is>
+      <c r="A167" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>1240×1200 #1 ח1/2</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E167" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F167" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G167" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="3" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>1250x2500</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>6160×1240 #6 ח1/3</t>
+          <t>1240×1200 #2 ח1/2</t>
         </is>
       </c>
       <c r="D168" s="3" t="n">
-        <v>1240</v>
+        <v>1000</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="F168" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="inlineStr">
-        <is>
-          <t>לוח 76</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>1250x2500 | ניצול 99% | 1 חתיכות</t>
-        </is>
+      <c r="A169" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>6160×1240 #1 ח6/6</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="E169" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="F169" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G169" s="3" t="n">
+        <v>2400</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="3" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>1250x2500</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>6160×1240 #6 ח2/3</t>
+          <t>6160×1240 #3 ח6/6</t>
         </is>
       </c>
       <c r="D170" s="3" t="n">
-        <v>1240</v>
+        <v>160</v>
       </c>
       <c r="E170" s="3" t="n">
-        <v>2500</v>
+        <v>240</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>0</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="inlineStr">
-        <is>
-          <t>לוח 77</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>1250x2500 | ניצול 96% | 1 חתיכות</t>
-        </is>
+      <c r="A171" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>6160×1240 #5 ח6/6</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="E171" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="F171" s="3" t="n">
+        <v>320</v>
+      </c>
+      <c r="G171" s="3" t="n">
+        <v>2400</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="3" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>1250x2500</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>6160×1200 #1 ח1/3</t>
+          <t>6160×1200 #1 ח6/6</t>
         </is>
       </c>
       <c r="D172" s="3" t="n">
-        <v>1200</v>
+        <v>200</v>
       </c>
       <c r="E172" s="3" t="n">
-        <v>2500</v>
+        <v>160</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="G172" s="3" t="n">
-        <v>0</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="inlineStr">
-        <is>
-          <t>לוח 78</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>1250x2500 | ניצול 96% | 1 חתיכות</t>
-        </is>
+      <c r="A173" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>6160×1200 #2 ח6/6</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E173" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="F173" s="3" t="n">
+        <v>680</v>
+      </c>
+      <c r="G173" s="3" t="n">
+        <v>2400</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="3" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>1250x2500</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>6160×1200 #1 ח2/3</t>
+          <t>6160×1200 #3 ח6/6</t>
         </is>
       </c>
       <c r="D174" s="3" t="n">
-        <v>1200</v>
+        <v>160</v>
       </c>
       <c r="E174" s="3" t="n">
-        <v>2500</v>
+        <v>200</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>0</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="inlineStr">
-        <is>
-          <t>לוח 79</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>1250x2500 | ניצול 96% | 1 חתיכות</t>
-        </is>
+      <c r="A175" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>6160×1240 #2 ח6/6</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="E175" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="F175" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" s="3" t="n">
+        <v>2640</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="3" t="n">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>1250x2500</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>6160×1200 #2 ח1/3</t>
+          <t>6160×1240 #4 ח6/6</t>
         </is>
       </c>
       <c r="D176" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="E176" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="F176" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="G176" s="3" t="n">
+        <v>2640</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>6160×1240 #6 ח6/6</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="E177" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="F177" s="3" t="n">
+        <v>320</v>
+      </c>
+      <c r="G177" s="3" t="n">
+        <v>2640</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>לוח 67</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 80% | 2 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>1240×1200 #3 ח1/2</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E179" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="E176" s="3" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F176" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G176" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
-        <is>
-          <t>לוח 80</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>1250x2500 | ניצול 96% | 1 חתיכות</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="B178" s="3" t="inlineStr">
-        <is>
-          <t>1250x2500</t>
-        </is>
-      </c>
-      <c r="C178" s="3" t="inlineStr">
-        <is>
-          <t>6160×1200 #2 ח2/3</t>
-        </is>
-      </c>
-      <c r="D178" s="3" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E178" s="3" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F178" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G178" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
-        <is>
-          <t>לוח 81</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>1250x2500 | ניצול 96% | 1 חתיכות</t>
-        </is>
+      <c r="F179" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G179" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="3" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>1250x2500</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>6160×1200 #3 ח1/3</t>
+          <t>1240×1200 #4 ח1/2</t>
         </is>
       </c>
       <c r="D180" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E180" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="E180" s="3" t="n">
-        <v>2500</v>
-      </c>
       <c r="F180" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G180" s="3" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>לוח 82</t>
+          <t>לוח 68</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>1250x2500 | ניצול 96% | 1 חתיכות</t>
+          <t>1000x3000 | ניצול 80% | 2 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="3" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>1250x2500</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>6160×1200 #3 ח2/3</t>
+          <t>1240×1200 #5 ח1/2</t>
         </is>
       </c>
       <c r="D182" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E182" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="E182" s="3" t="n">
-        <v>2500</v>
-      </c>
       <c r="F182" s="3" t="n">
         <v>0</v>
       </c>
@@ -4193,105 +4403,120 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="inlineStr">
-        <is>
-          <t>לוח 83</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>1250x2500 | ניצול 95% | 2 חתיכות</t>
-        </is>
+      <c r="A183" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>1240×1200 #6 ח1/2</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E183" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F183" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G183" s="3" t="n">
+        <v>1200</v>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="B184" s="3" t="inlineStr">
-        <is>
-          <t>1250x2500</t>
-        </is>
-      </c>
-      <c r="C184" s="3" t="inlineStr">
-        <is>
-          <t>1240×1200 #1</t>
-        </is>
-      </c>
-      <c r="D184" s="3" t="n">
-        <v>1240</v>
-      </c>
-      <c r="E184" s="3" t="n">
-        <v>1200</v>
-      </c>
-      <c r="F184" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G184" s="3" t="n">
-        <v>0</v>
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>לוח 69</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 96% | 4 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="3" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>1250x2500</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>1240×1200 #2</t>
+          <t>6160×1240 #1 ח2/6</t>
         </is>
       </c>
       <c r="D185" s="3" t="n">
-        <v>1240</v>
+        <v>240</v>
       </c>
       <c r="E185" s="3" t="n">
-        <v>1200</v>
+        <v>3000</v>
       </c>
       <c r="F185" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G185" s="3" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="inlineStr">
-        <is>
-          <t>לוח 84</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>1250x2500 | ניצול 95% | 2 חתיכות</t>
-        </is>
+      <c r="A186" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t>6160×1240 #1 ח4/6</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="E186" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F186" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="G186" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="3" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>1250x2500</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>1240×1200 #3</t>
+          <t>6160×1240 #2 ח2/6</t>
         </is>
       </c>
       <c r="D187" s="3" t="n">
-        <v>1240</v>
+        <v>240</v>
       </c>
       <c r="E187" s="3" t="n">
-        <v>1200</v>
+        <v>3000</v>
       </c>
       <c r="F187" s="3" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="G187" s="3" t="n">
         <v>0</v>
@@ -4299,62 +4524,62 @@
     </row>
     <row r="188">
       <c r="A188" s="3" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>1250x2500</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>1240×1200 #4</t>
+          <t>6160×1240 #2 ח4/6</t>
         </is>
       </c>
       <c r="D188" s="3" t="n">
-        <v>1240</v>
+        <v>240</v>
       </c>
       <c r="E188" s="3" t="n">
-        <v>1200</v>
+        <v>3000</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="G188" s="3" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>לוח 85</t>
+          <t>לוח 70</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>1250x2500 | ניצול 95% | 2 חתיכות</t>
+          <t>1000x3000 | ניצול 96% | 4 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="3" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>1250x2500</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>1240×1200 #5</t>
+          <t>6160×1240 #3 ח2/6</t>
         </is>
       </c>
       <c r="D190" s="3" t="n">
-        <v>1240</v>
+        <v>240</v>
       </c>
       <c r="E190" s="3" t="n">
-        <v>1200</v>
+        <v>3000</v>
       </c>
       <c r="F190" s="3" t="n">
         <v>0</v>
@@ -4365,131 +4590,146 @@
     </row>
     <row r="191">
       <c r="A191" s="3" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>1250x2500</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>1240×1200 #6</t>
+          <t>6160×1240 #3 ח4/6</t>
         </is>
       </c>
       <c r="D191" s="3" t="n">
-        <v>1240</v>
+        <v>240</v>
       </c>
       <c r="E191" s="3" t="n">
-        <v>1200</v>
+        <v>3000</v>
       </c>
       <c r="F191" s="3" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="G191" s="3" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="inlineStr">
-        <is>
-          <t>לוח 86</t>
-        </is>
-      </c>
-      <c r="C192" s="2" t="inlineStr">
-        <is>
-          <t>1250x2500 | ניצול 92% | 2 חתיכות</t>
-        </is>
+      <c r="A192" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>6160×1240 #4 ח2/6</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="E192" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F192" s="3" t="n">
+        <v>480</v>
+      </c>
+      <c r="G192" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="3" t="n">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>1250x2500</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>6160×1240 #1 ח3/3</t>
+          <t>6160×1240 #4 ח4/6</t>
         </is>
       </c>
       <c r="D193" s="3" t="n">
-        <v>1240</v>
+        <v>240</v>
       </c>
       <c r="E193" s="3" t="n">
-        <v>1160</v>
+        <v>3000</v>
       </c>
       <c r="F193" s="3" t="n">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="G193" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="3" t="n">
-        <v>86</v>
-      </c>
-      <c r="B194" s="3" t="inlineStr">
-        <is>
-          <t>1250x2500</t>
-        </is>
-      </c>
-      <c r="C194" s="3" t="inlineStr">
-        <is>
-          <t>6160×1240 #2 ח3/3</t>
-        </is>
-      </c>
-      <c r="D194" s="3" t="n">
-        <v>1240</v>
-      </c>
-      <c r="E194" s="3" t="n">
-        <v>1160</v>
-      </c>
-      <c r="F194" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G194" s="3" t="n">
-        <v>1160</v>
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>לוח 71</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 96% | 4 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="inlineStr">
-        <is>
-          <t>לוח 87</t>
-        </is>
-      </c>
-      <c r="C195" s="2" t="inlineStr">
-        <is>
-          <t>1250x2500 | ניצול 92% | 2 חתיכות</t>
-        </is>
+      <c r="A195" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>6160×1240 #5 ח2/6</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="E195" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F195" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G195" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="3" t="n">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>1250x2500</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>6160×1240 #3 ח3/3</t>
+          <t>6160×1240 #5 ח4/6</t>
         </is>
       </c>
       <c r="D196" s="3" t="n">
-        <v>1240</v>
+        <v>240</v>
       </c>
       <c r="E196" s="3" t="n">
-        <v>1160</v>
+        <v>3000</v>
       </c>
       <c r="F196" s="3" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="G196" s="3" t="n">
         <v>0</v>
@@ -4497,131 +4737,146 @@
     </row>
     <row r="197">
       <c r="A197" s="3" t="n">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>1250x2500</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>6160×1240 #4 ח3/3</t>
+          <t>6160×1240 #6 ח2/6</t>
         </is>
       </c>
       <c r="D197" s="3" t="n">
-        <v>1240</v>
+        <v>240</v>
       </c>
       <c r="E197" s="3" t="n">
-        <v>1160</v>
+        <v>3000</v>
       </c>
       <c r="F197" s="3" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="G197" s="3" t="n">
-        <v>1160</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="inlineStr">
-        <is>
-          <t>לוח 88</t>
-        </is>
-      </c>
-      <c r="C198" s="2" t="inlineStr">
-        <is>
-          <t>1250x2500 | ניצול 92% | 2 חתיכות</t>
-        </is>
+      <c r="A198" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C198" s="3" t="inlineStr">
+        <is>
+          <t>6160×1240 #6 ח4/6</t>
+        </is>
+      </c>
+      <c r="D198" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="E198" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F198" s="3" t="n">
+        <v>720</v>
+      </c>
+      <c r="G198" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="B199" s="3" t="inlineStr">
-        <is>
-          <t>1250x2500</t>
-        </is>
-      </c>
-      <c r="C199" s="3" t="inlineStr">
-        <is>
-          <t>6160×1240 #5 ח3/3</t>
-        </is>
-      </c>
-      <c r="D199" s="3" t="n">
-        <v>1240</v>
-      </c>
-      <c r="E199" s="3" t="n">
-        <v>1160</v>
-      </c>
-      <c r="F199" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G199" s="3" t="n">
-        <v>0</v>
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>לוח 72</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 58% | 6 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="3" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>1250x2500</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>6160×1240 #6 ח3/3</t>
+          <t>1240×1200 #1 ח2/2</t>
         </is>
       </c>
       <c r="D200" s="3" t="n">
-        <v>1240</v>
+        <v>240</v>
       </c>
       <c r="E200" s="3" t="n">
-        <v>1160</v>
+        <v>1200</v>
       </c>
       <c r="F200" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G200" s="3" t="n">
-        <v>1160</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="inlineStr">
-        <is>
-          <t>לוח 89</t>
-        </is>
-      </c>
-      <c r="C201" s="2" t="inlineStr">
-        <is>
-          <t>1250x2500 | ניצול 89% | 2 חתיכות</t>
-        </is>
+      <c r="A201" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>1240×1200 #2 ח2/2</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="E201" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F201" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="G201" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="3" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>1250x2500</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>6160×1200 #1 ח3/3</t>
+          <t>1240×1200 #3 ח2/2</t>
         </is>
       </c>
       <c r="D202" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="E202" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="E202" s="3" t="n">
-        <v>1160</v>
-      </c>
       <c r="F202" s="3" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="G202" s="3" t="n">
         <v>0</v>
@@ -4629,101 +4884,116 @@
     </row>
     <row r="203">
       <c r="A203" s="3" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>1250x2500</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>6160×1200 #2 ח3/3</t>
+          <t>1240×1200 #4 ח2/2</t>
         </is>
       </c>
       <c r="D203" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="E203" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="E203" s="3" t="n">
-        <v>1160</v>
-      </c>
       <c r="F203" s="3" t="n">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="G203" s="3" t="n">
-        <v>1160</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="inlineStr">
-        <is>
-          <t>לוח 90</t>
-        </is>
-      </c>
-      <c r="C204" s="2" t="inlineStr">
-        <is>
-          <t>1250x2500 | ניצול 45% | 1 חתיכות</t>
-        </is>
+      <c r="A204" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t>1240×1200 #5 ח2/2</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="E204" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F204" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G204" s="3" t="n">
+        <v>1200</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="3" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>1250x2500</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>6160×1200 #3 ח3/3</t>
+          <t>1240×1200 #6 ח2/2</t>
         </is>
       </c>
       <c r="D205" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="E205" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="E205" s="3" t="n">
-        <v>1160</v>
-      </c>
       <c r="F205" s="3" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="G205" s="3" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>לוח 91</t>
+          <t>לוח 73</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>1500x3000 | ניצול 85% | 2 חתיכות</t>
+          <t>1220x2440 | ניצול 76% | 3 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="3" t="n">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>1500x3000</t>
+          <t>1220x2440</t>
         </is>
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>5330×640 #1 ח1/2</t>
+          <t>940×800 #1</t>
         </is>
       </c>
       <c r="D207" s="3" t="n">
-        <v>640</v>
+        <v>940</v>
       </c>
       <c r="E207" s="3" t="n">
-        <v>3000</v>
+        <v>800</v>
       </c>
       <c r="F207" s="3" t="n">
         <v>0</v>
@@ -4734,178 +5004,193 @@
     </row>
     <row r="208">
       <c r="A208" s="3" t="n">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>1500x3000</t>
+          <t>1220x2440</t>
         </is>
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>5330×640 #2 ח1/2</t>
+          <t>940×800 #2</t>
         </is>
       </c>
       <c r="D208" s="3" t="n">
-        <v>640</v>
+        <v>940</v>
       </c>
       <c r="E208" s="3" t="n">
-        <v>3000</v>
+        <v>800</v>
       </c>
       <c r="F208" s="3" t="n">
-        <v>640</v>
+        <v>0</v>
       </c>
       <c r="G208" s="3" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="inlineStr">
-        <is>
-          <t>לוח 92</t>
-        </is>
-      </c>
-      <c r="C209" s="2" t="inlineStr">
-        <is>
-          <t>1500x3000 | ניצול 85% | 2 חתיכות</t>
-        </is>
+      <c r="A209" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>1220x2440</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>940×800 #3</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="E209" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="F209" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G209" s="3" t="n">
+        <v>1600</v>
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="B210" s="3" t="inlineStr">
-        <is>
-          <t>1500x3000</t>
-        </is>
-      </c>
-      <c r="C210" s="3" t="inlineStr">
-        <is>
-          <t>5330×640 #3 ח1/2</t>
-        </is>
-      </c>
-      <c r="D210" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="E210" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F210" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G210" s="3" t="n">
-        <v>0</v>
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>לוח 74</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>1220x2440 | ניצול 76% | 3 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="3" t="n">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>1500x3000</t>
+          <t>1220x2440</t>
         </is>
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>5330×640 #4 ח1/2</t>
+          <t>940×800 #4</t>
         </is>
       </c>
       <c r="D211" s="3" t="n">
-        <v>640</v>
+        <v>940</v>
       </c>
       <c r="E211" s="3" t="n">
-        <v>3000</v>
+        <v>800</v>
       </c>
       <c r="F211" s="3" t="n">
-        <v>640</v>
+        <v>0</v>
       </c>
       <c r="G211" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="inlineStr">
-        <is>
-          <t>לוח 93</t>
-        </is>
-      </c>
-      <c r="C212" s="2" t="inlineStr">
-        <is>
-          <t>1500x3000 | ניצול 85% | 2 חתיכות</t>
-        </is>
+      <c r="A212" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="B212" s="3" t="inlineStr">
+        <is>
+          <t>1220x2440</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="inlineStr">
+        <is>
+          <t>940×800 #5</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="E212" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="F212" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G212" s="3" t="n">
+        <v>800</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="3" t="n">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
+          <t>1220x2440</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="inlineStr">
+        <is>
+          <t>940×800 #6</t>
+        </is>
+      </c>
+      <c r="D213" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="E213" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="F213" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G213" s="3" t="n">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>לוח 75</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>1500x3000 | ניצול 85% | 2 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="B215" s="3" t="inlineStr">
+        <is>
           <t>1500x3000</t>
         </is>
       </c>
-      <c r="C213" s="3" t="inlineStr">
-        <is>
-          <t>5330×640 #5 ח1/2</t>
-        </is>
-      </c>
-      <c r="D213" s="3" t="n">
+      <c r="C215" s="3" t="inlineStr">
+        <is>
+          <t>5330×640 #1 ח1/2</t>
+        </is>
+      </c>
+      <c r="D215" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="E213" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F213" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G213" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="B214" s="3" t="inlineStr">
-        <is>
-          <t>1500x3000</t>
-        </is>
-      </c>
-      <c r="C214" s="3" t="inlineStr">
-        <is>
-          <t>5330×640 #6 ח1/2</t>
-        </is>
-      </c>
-      <c r="D214" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="E214" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F214" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="G214" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="2" t="inlineStr">
-        <is>
-          <t>לוח 94</t>
-        </is>
-      </c>
-      <c r="C215" s="2" t="inlineStr">
-        <is>
-          <t>1500x3000 | ניצול 85% | 2 חתיכות</t>
-        </is>
+      <c r="E215" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F215" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G215" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="3" t="n">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
@@ -4914,7 +5199,7 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>5330×640 #7 ח1/2</t>
+          <t>5330×640 #2 ח1/2</t>
         </is>
       </c>
       <c r="D216" s="3" t="n">
@@ -4924,54 +5209,54 @@
         <v>3000</v>
       </c>
       <c r="F216" s="3" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="G216" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="B217" s="3" t="inlineStr">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>לוח 76</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>1500x3000 | ניצול 85% | 2 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
         <is>
           <t>1500x3000</t>
         </is>
       </c>
-      <c r="C217" s="3" t="inlineStr">
-        <is>
-          <t>5330×640 #8 ח1/2</t>
-        </is>
-      </c>
-      <c r="D217" s="3" t="n">
+      <c r="C218" s="3" t="inlineStr">
+        <is>
+          <t>5330×640 #3 ח1/2</t>
+        </is>
+      </c>
+      <c r="D218" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="E217" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F217" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="G217" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="2" t="inlineStr">
-        <is>
-          <t>לוח 95</t>
-        </is>
-      </c>
-      <c r="C218" s="2" t="inlineStr">
-        <is>
-          <t>1500x3000 | ניצול 85% | 2 חתיכות</t>
-        </is>
+      <c r="E218" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F218" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G218" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="3" t="n">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
@@ -4980,7 +5265,7 @@
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>5330×640 #9 ח1/2</t>
+          <t>5330×640 #4 ח1/2</t>
         </is>
       </c>
       <c r="D219" s="3" t="n">
@@ -4990,54 +5275,54 @@
         <v>3000</v>
       </c>
       <c r="F219" s="3" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="G219" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="B220" s="3" t="inlineStr">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>לוח 77</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>1500x3000 | ניצול 85% | 2 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="B221" s="3" t="inlineStr">
         <is>
           <t>1500x3000</t>
         </is>
       </c>
-      <c r="C220" s="3" t="inlineStr">
-        <is>
-          <t>5330×640 #10 ח1/2</t>
-        </is>
-      </c>
-      <c r="D220" s="3" t="n">
+      <c r="C221" s="3" t="inlineStr">
+        <is>
+          <t>5330×640 #5 ח1/2</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="E220" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F220" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="G220" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="2" t="inlineStr">
-        <is>
-          <t>לוח 96</t>
-        </is>
-      </c>
-      <c r="C221" s="2" t="inlineStr">
-        <is>
-          <t>1500x3000 | ניצול 85% | 2 חתיכות</t>
-        </is>
+      <c r="E221" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F221" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G221" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="3" t="n">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
@@ -5046,7 +5331,7 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>5330×640 #11 ח1/2</t>
+          <t>5330×640 #6 ח1/2</t>
         </is>
       </c>
       <c r="D222" s="3" t="n">
@@ -5056,54 +5341,54 @@
         <v>3000</v>
       </c>
       <c r="F222" s="3" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="G222" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="B223" s="3" t="inlineStr">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>לוח 78</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>1500x3000 | ניצול 85% | 2 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="B224" s="3" t="inlineStr">
         <is>
           <t>1500x3000</t>
         </is>
       </c>
-      <c r="C223" s="3" t="inlineStr">
-        <is>
-          <t>5330×640 #12 ח1/2</t>
-        </is>
-      </c>
-      <c r="D223" s="3" t="n">
+      <c r="C224" s="3" t="inlineStr">
+        <is>
+          <t>5330×640 #7 ח1/2</t>
+        </is>
+      </c>
+      <c r="D224" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="E223" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F223" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="G223" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="2" t="inlineStr">
-        <is>
-          <t>לוח 97</t>
-        </is>
-      </c>
-      <c r="C224" s="2" t="inlineStr">
-        <is>
-          <t>1500x3000 | ניצול 66% | 2 חתיכות</t>
-        </is>
+      <c r="E224" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F224" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G224" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="3" t="n">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
@@ -5112,64 +5397,64 @@
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>5330×640 #1 ח2/2</t>
+          <t>5330×640 #8 ח1/2</t>
         </is>
       </c>
       <c r="D225" s="3" t="n">
         <v>640</v>
       </c>
       <c r="E225" s="3" t="n">
-        <v>2330</v>
+        <v>3000</v>
       </c>
       <c r="F225" s="3" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="G225" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="B226" s="3" t="inlineStr">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>לוח 79</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>1500x3000 | ניצול 85% | 2 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="B227" s="3" t="inlineStr">
         <is>
           <t>1500x3000</t>
         </is>
       </c>
-      <c r="C226" s="3" t="inlineStr">
-        <is>
-          <t>5330×640 #2 ח2/2</t>
-        </is>
-      </c>
-      <c r="D226" s="3" t="n">
+      <c r="C227" s="3" t="inlineStr">
+        <is>
+          <t>5330×640 #9 ח1/2</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="E226" s="3" t="n">
-        <v>2330</v>
-      </c>
-      <c r="F226" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="G226" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="2" t="inlineStr">
-        <is>
-          <t>לוח 98</t>
-        </is>
-      </c>
-      <c r="C227" s="2" t="inlineStr">
-        <is>
-          <t>1500x3000 | ניצול 66% | 2 חתיכות</t>
-        </is>
+      <c r="E227" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F227" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G227" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="3" t="n">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
@@ -5178,64 +5463,64 @@
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>5330×640 #3 ח2/2</t>
+          <t>5330×640 #10 ח1/2</t>
         </is>
       </c>
       <c r="D228" s="3" t="n">
         <v>640</v>
       </c>
       <c r="E228" s="3" t="n">
-        <v>2330</v>
+        <v>3000</v>
       </c>
       <c r="F228" s="3" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="G228" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="B229" s="3" t="inlineStr">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>לוח 80</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>1500x3000 | ניצול 85% | 2 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="B230" s="3" t="inlineStr">
         <is>
           <t>1500x3000</t>
         </is>
       </c>
-      <c r="C229" s="3" t="inlineStr">
-        <is>
-          <t>5330×640 #4 ח2/2</t>
-        </is>
-      </c>
-      <c r="D229" s="3" t="n">
+      <c r="C230" s="3" t="inlineStr">
+        <is>
+          <t>5330×640 #11 ח1/2</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="E229" s="3" t="n">
-        <v>2330</v>
-      </c>
-      <c r="F229" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="G229" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="2" t="inlineStr">
-        <is>
-          <t>לוח 99</t>
-        </is>
-      </c>
-      <c r="C230" s="2" t="inlineStr">
-        <is>
-          <t>1500x3000 | ניצול 66% | 2 חתיכות</t>
-        </is>
+      <c r="E230" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F230" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G230" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="3" t="n">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
@@ -5244,64 +5529,64 @@
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>5330×640 #5 ח2/2</t>
+          <t>5330×640 #12 ח1/2</t>
         </is>
       </c>
       <c r="D231" s="3" t="n">
         <v>640</v>
       </c>
       <c r="E231" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F231" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="G231" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>לוח 81</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>1500x3000 | ניצול 66% | 2 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="B233" s="3" t="inlineStr">
+        <is>
+          <t>1500x3000</t>
+        </is>
+      </c>
+      <c r="C233" s="3" t="inlineStr">
+        <is>
+          <t>5330×640 #1 ח2/2</t>
+        </is>
+      </c>
+      <c r="D233" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="E233" s="3" t="n">
         <v>2330</v>
       </c>
-      <c r="F231" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G231" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="B232" s="3" t="inlineStr">
-        <is>
-          <t>1500x3000</t>
-        </is>
-      </c>
-      <c r="C232" s="3" t="inlineStr">
-        <is>
-          <t>5330×640 #6 ח2/2</t>
-        </is>
-      </c>
-      <c r="D232" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="E232" s="3" t="n">
-        <v>2330</v>
-      </c>
-      <c r="F232" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="G232" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="2" t="inlineStr">
-        <is>
-          <t>לוח 100</t>
-        </is>
-      </c>
-      <c r="C233" s="2" t="inlineStr">
-        <is>
-          <t>1500x3000 | ניצול 66% | 2 חתיכות</t>
-        </is>
+      <c r="F233" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G233" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="3" t="n">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
@@ -5310,7 +5595,7 @@
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>5330×640 #7 ח2/2</t>
+          <t>5330×640 #2 ח2/2</t>
         </is>
       </c>
       <c r="D234" s="3" t="n">
@@ -5320,54 +5605,54 @@
         <v>2330</v>
       </c>
       <c r="F234" s="3" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="G234" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="B235" s="3" t="inlineStr">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>לוח 82</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>1500x3000 | ניצול 66% | 2 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="B236" s="3" t="inlineStr">
         <is>
           <t>1500x3000</t>
         </is>
       </c>
-      <c r="C235" s="3" t="inlineStr">
-        <is>
-          <t>5330×640 #8 ח2/2</t>
-        </is>
-      </c>
-      <c r="D235" s="3" t="n">
+      <c r="C236" s="3" t="inlineStr">
+        <is>
+          <t>5330×640 #3 ח2/2</t>
+        </is>
+      </c>
+      <c r="D236" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="E235" s="3" t="n">
+      <c r="E236" s="3" t="n">
         <v>2330</v>
       </c>
-      <c r="F235" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="G235" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="2" t="inlineStr">
-        <is>
-          <t>לוח 101</t>
-        </is>
-      </c>
-      <c r="C236" s="2" t="inlineStr">
-        <is>
-          <t>1500x3000 | ניצול 66% | 2 חתיכות</t>
-        </is>
+      <c r="F236" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G236" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="3" t="n">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
@@ -5376,7 +5661,7 @@
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>5330×640 #9 ח2/2</t>
+          <t>5330×640 #4 ח2/2</t>
         </is>
       </c>
       <c r="D237" s="3" t="n">
@@ -5386,54 +5671,54 @@
         <v>2330</v>
       </c>
       <c r="F237" s="3" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="G237" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="3" t="n">
-        <v>101</v>
-      </c>
-      <c r="B238" s="3" t="inlineStr">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>לוח 83</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>1500x3000 | ניצול 66% | 2 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="B239" s="3" t="inlineStr">
         <is>
           <t>1500x3000</t>
         </is>
       </c>
-      <c r="C238" s="3" t="inlineStr">
-        <is>
-          <t>5330×640 #10 ח2/2</t>
-        </is>
-      </c>
-      <c r="D238" s="3" t="n">
+      <c r="C239" s="3" t="inlineStr">
+        <is>
+          <t>5330×640 #5 ח2/2</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="E238" s="3" t="n">
+      <c r="E239" s="3" t="n">
         <v>2330</v>
       </c>
-      <c r="F238" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="G238" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="2" t="inlineStr">
-        <is>
-          <t>לוח 102</t>
-        </is>
-      </c>
-      <c r="C239" s="2" t="inlineStr">
-        <is>
-          <t>1500x3000 | ניצול 66% | 2 חתיכות</t>
-        </is>
+      <c r="F239" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G239" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="3" t="n">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
@@ -5442,7 +5727,7 @@
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>5330×640 #11 ח2/2</t>
+          <t>5330×640 #6 ח2/2</t>
         </is>
       </c>
       <c r="D240" s="3" t="n">
@@ -5452,244 +5737,383 @@
         <v>2330</v>
       </c>
       <c r="F240" s="3" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="G240" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="3" t="n">
-        <v>102</v>
-      </c>
-      <c r="B241" s="3" t="inlineStr">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>לוח 84</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>1500x3000 | ניצול 66% | 2 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="B242" s="3" t="inlineStr">
         <is>
           <t>1500x3000</t>
         </is>
       </c>
-      <c r="C241" s="3" t="inlineStr">
+      <c r="C242" s="3" t="inlineStr">
+        <is>
+          <t>5330×640 #7 ח2/2</t>
+        </is>
+      </c>
+      <c r="D242" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="E242" s="3" t="n">
+        <v>2330</v>
+      </c>
+      <c r="F242" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G242" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="B243" s="3" t="inlineStr">
+        <is>
+          <t>1500x3000</t>
+        </is>
+      </c>
+      <c r="C243" s="3" t="inlineStr">
+        <is>
+          <t>5330×640 #8 ח2/2</t>
+        </is>
+      </c>
+      <c r="D243" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="E243" s="3" t="n">
+        <v>2330</v>
+      </c>
+      <c r="F243" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="G243" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>לוח 85</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>1500x3000 | ניצול 66% | 2 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="B245" s="3" t="inlineStr">
+        <is>
+          <t>1500x3000</t>
+        </is>
+      </c>
+      <c r="C245" s="3" t="inlineStr">
+        <is>
+          <t>5330×640 #9 ח2/2</t>
+        </is>
+      </c>
+      <c r="D245" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="E245" s="3" t="n">
+        <v>2330</v>
+      </c>
+      <c r="F245" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G245" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="B246" s="3" t="inlineStr">
+        <is>
+          <t>1500x3000</t>
+        </is>
+      </c>
+      <c r="C246" s="3" t="inlineStr">
+        <is>
+          <t>5330×640 #10 ח2/2</t>
+        </is>
+      </c>
+      <c r="D246" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="E246" s="3" t="n">
+        <v>2330</v>
+      </c>
+      <c r="F246" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="G246" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>לוח 86</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>1500x3000 | ניצול 66% | 2 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="B248" s="3" t="inlineStr">
+        <is>
+          <t>1500x3000</t>
+        </is>
+      </c>
+      <c r="C248" s="3" t="inlineStr">
+        <is>
+          <t>5330×640 #11 ח2/2</t>
+        </is>
+      </c>
+      <c r="D248" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="E248" s="3" t="n">
+        <v>2330</v>
+      </c>
+      <c r="F248" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G248" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>1500x3000</t>
+        </is>
+      </c>
+      <c r="C249" s="3" t="inlineStr">
         <is>
           <t>5330×640 #12 ח2/2</t>
         </is>
       </c>
-      <c r="D241" s="3" t="n">
+      <c r="D249" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="E241" s="3" t="n">
+      <c r="E249" s="3" t="n">
         <v>2330</v>
       </c>
-      <c r="F241" s="3" t="n">
+      <c r="F249" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="G241" s="3" t="n">
+      <c r="G249" s="3" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="204">
+  <mergeCells count="172">
     <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C239:G239"/>
     <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A186:B186"/>
+    <mergeCell ref="C166:G166"/>
     <mergeCell ref="A98:B98"/>
-    <mergeCell ref="C175:G175"/>
+    <mergeCell ref="A226:B226"/>
     <mergeCell ref="C58:G58"/>
     <mergeCell ref="A107:B107"/>
+    <mergeCell ref="A178:B178"/>
     <mergeCell ref="C14:G14"/>
     <mergeCell ref="A88:B88"/>
     <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A241:B241"/>
+    <mergeCell ref="C29:G29"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="A54:B54"/>
-    <mergeCell ref="C147:G147"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="A212:B212"/>
-    <mergeCell ref="C218:G218"/>
+    <mergeCell ref="C109:G109"/>
+    <mergeCell ref="A41:B41"/>
     <mergeCell ref="C44:G44"/>
-    <mergeCell ref="C137:G137"/>
     <mergeCell ref="A74:B74"/>
     <mergeCell ref="A56:B56"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="A236:B236"/>
-    <mergeCell ref="A163:B163"/>
-    <mergeCell ref="A101:B101"/>
-    <mergeCell ref="C192:G192"/>
-    <mergeCell ref="A195:B195"/>
-    <mergeCell ref="C201:G201"/>
+    <mergeCell ref="C129:G129"/>
+    <mergeCell ref="A214:B214"/>
+    <mergeCell ref="C139:G139"/>
     <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A204:B204"/>
     <mergeCell ref="C60:G60"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="C110:G110"/>
-    <mergeCell ref="A140:B140"/>
+    <mergeCell ref="C244:G244"/>
+    <mergeCell ref="C241:G241"/>
+    <mergeCell ref="C123:G123"/>
+    <mergeCell ref="C194:G194"/>
     <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="A35:B35"/>
     <mergeCell ref="C181:G181"/>
+    <mergeCell ref="A62:B62"/>
     <mergeCell ref="A206:B206"/>
-    <mergeCell ref="A62:B62"/>
     <mergeCell ref="A68:B68"/>
-    <mergeCell ref="C165:G165"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A230:B230"/>
-    <mergeCell ref="C140:G140"/>
-    <mergeCell ref="C155:G155"/>
+    <mergeCell ref="A117:B117"/>
+    <mergeCell ref="A111:B111"/>
     <mergeCell ref="C18:G18"/>
     <mergeCell ref="C189:G189"/>
-    <mergeCell ref="C101:G101"/>
-    <mergeCell ref="A167:B167"/>
+    <mergeCell ref="C220:G220"/>
+    <mergeCell ref="C229:G229"/>
     <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C204:G204"/>
+    <mergeCell ref="A232:B232"/>
     <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C179:G179"/>
-    <mergeCell ref="C157:G157"/>
-    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="A142:B142"/>
     <mergeCell ref="C151:G151"/>
-    <mergeCell ref="A169:B169"/>
+    <mergeCell ref="A103:B103"/>
     <mergeCell ref="C206:G206"/>
-    <mergeCell ref="C215:G215"/>
-    <mergeCell ref="C128:G128"/>
-    <mergeCell ref="A153:B153"/>
-    <mergeCell ref="A218:B218"/>
     <mergeCell ref="C20:G20"/>
     <mergeCell ref="C113:G113"/>
-    <mergeCell ref="A227:B227"/>
-    <mergeCell ref="A128:B128"/>
-    <mergeCell ref="C143:G143"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="A137:B137"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A177:B177"/>
-    <mergeCell ref="C183:G183"/>
+    <mergeCell ref="C103:G103"/>
+    <mergeCell ref="A217:B217"/>
     <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C133:G133"/>
     <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C167:G167"/>
-    <mergeCell ref="A192:B192"/>
+    <mergeCell ref="C127:G127"/>
+    <mergeCell ref="A136:B136"/>
+    <mergeCell ref="C142:G142"/>
     <mergeCell ref="C80:G80"/>
-    <mergeCell ref="C198:G198"/>
+    <mergeCell ref="A105:B105"/>
+    <mergeCell ref="A145:B145"/>
+    <mergeCell ref="C247:G247"/>
     <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A139:B139"/>
+    <mergeCell ref="A210:B210"/>
     <mergeCell ref="C12:G12"/>
-    <mergeCell ref="A179:B179"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C169:G169"/>
-    <mergeCell ref="A116:B116"/>
+    <mergeCell ref="A129:B129"/>
+    <mergeCell ref="A194:B194"/>
+    <mergeCell ref="C178:G178"/>
     <mergeCell ref="A181:B181"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C159:G159"/>
     <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C153:G153"/>
+    <mergeCell ref="A184:B184"/>
     <mergeCell ref="A131:B131"/>
-    <mergeCell ref="C233:G233"/>
-    <mergeCell ref="A171:B171"/>
+    <mergeCell ref="A244:B244"/>
     <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A165:B165"/>
     <mergeCell ref="C32:G32"/>
     <mergeCell ref="C38:G38"/>
     <mergeCell ref="C125:G125"/>
-    <mergeCell ref="C209:G209"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A155:B155"/>
+    <mergeCell ref="A115:B115"/>
     <mergeCell ref="C161:G161"/>
-    <mergeCell ref="A173:B173"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="C217:G217"/>
     <mergeCell ref="C131:G131"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A143:B143"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="A157:B157"/>
+    <mergeCell ref="A229:B229"/>
+    <mergeCell ref="C145:G145"/>
+    <mergeCell ref="A166:B166"/>
     <mergeCell ref="C24:G24"/>
-    <mergeCell ref="C195:G195"/>
-    <mergeCell ref="C104:G104"/>
-    <mergeCell ref="C116:G116"/>
-    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C156:G156"/>
     <mergeCell ref="A119:B119"/>
-    <mergeCell ref="A94:B94"/>
     <mergeCell ref="C74:G74"/>
     <mergeCell ref="C88:G88"/>
     <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C35:G35"/>
     <mergeCell ref="A78:B78"/>
-    <mergeCell ref="A183:B183"/>
+    <mergeCell ref="C121:G121"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C16:G16"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C221:G221"/>
-    <mergeCell ref="C230:G230"/>
+    <mergeCell ref="A133:B133"/>
+    <mergeCell ref="C117:G117"/>
     <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A233:B233"/>
-    <mergeCell ref="C236:G236"/>
+    <mergeCell ref="C214:G214"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A239:B239"/>
-    <mergeCell ref="A104:B104"/>
-    <mergeCell ref="A175:B175"/>
+    <mergeCell ref="C223:G223"/>
+    <mergeCell ref="C238:G238"/>
+    <mergeCell ref="C232:G232"/>
     <mergeCell ref="A113:B113"/>
     <mergeCell ref="C2:G2"/>
+    <mergeCell ref="C115:G115"/>
+    <mergeCell ref="A235:B235"/>
     <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A247:B247"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="C52:G52"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C122:G122"/>
-    <mergeCell ref="A147:B147"/>
-    <mergeCell ref="A209:B209"/>
-    <mergeCell ref="C224:G224"/>
+    <mergeCell ref="A156:B156"/>
     <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C186:G186"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C199:G199"/>
+    <mergeCell ref="A220:B220"/>
     <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="C136:G136"/>
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="A201:B201"/>
+    <mergeCell ref="A148:B148"/>
     <mergeCell ref="A82:B82"/>
+    <mergeCell ref="C210:G210"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="A60:B60"/>
     <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C235:G235"/>
     <mergeCell ref="C98:G98"/>
+    <mergeCell ref="A123:B123"/>
     <mergeCell ref="C107:G107"/>
-    <mergeCell ref="A110:B110"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C64:G64"/>
+    <mergeCell ref="C184:G184"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C171:G171"/>
-    <mergeCell ref="A221:B221"/>
-    <mergeCell ref="C227:G227"/>
     <mergeCell ref="C54:G54"/>
-    <mergeCell ref="C177:G177"/>
+    <mergeCell ref="C41:G41"/>
     <mergeCell ref="A84:B84"/>
-    <mergeCell ref="C134:G134"/>
     <mergeCell ref="A66:B66"/>
-    <mergeCell ref="C212:G212"/>
-    <mergeCell ref="A149:B149"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C226:G226"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="A189:B189"/>
-    <mergeCell ref="C173:G173"/>
-    <mergeCell ref="A198:B198"/>
-    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A223:B223"/>
+    <mergeCell ref="A238:B238"/>
     <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="C148:G148"/>
+    <mergeCell ref="C105:G105"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A86:B86"/>
-    <mergeCell ref="C163:G163"/>
     <mergeCell ref="A151:B151"/>
     <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C36:G36"/>
     <mergeCell ref="C119:G119"/>
     <mergeCell ref="C8:G8"/>
-    <mergeCell ref="A159:B159"/>
-    <mergeCell ref="A122:B122"/>
-    <mergeCell ref="A215:B215"/>
-    <mergeCell ref="A224:B224"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="C82:G82"/>
     <mergeCell ref="A125:B125"/>
     <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A134:B134"/>
-    <mergeCell ref="C149:G149"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A199:B199"/>
+    <mergeCell ref="A121:B121"/>
     <mergeCell ref="C66:G66"/>
     <mergeCell ref="A161:B161"/>
     <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A127:B127"/>
+    <mergeCell ref="C111:G111"/>
     <mergeCell ref="A58:B58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5702,7 +6126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5741,69 +6165,82 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>128</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1250x2500</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>81.25</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>1220x2440</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>5.95</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
           <t>1500x3000</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B6" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C6" s="3" t="n">
         <v>54</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>סה״כ</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
-        <v>102</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>263.25</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>שטח נדרש נטו (מ״ר):</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="n">
-        <v>226.16</v>
+      <c r="B7" s="5" t="n">
+        <v>86</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>255.95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
+          <t>שטח נדרש נטו (מ״ר):</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>226.16</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
           <t>פחת כולל:</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n">
-        <v>0.1409</v>
+      <c r="B10" s="8" t="n">
+        <v>0.1164</v>
       </c>
     </row>
   </sheetData>
@@ -5862,11 +6299,11 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>1250x2500</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -5880,11 +6317,11 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>1250x2500</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -5898,11 +6335,11 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>1250x2500</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -5916,11 +6353,11 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -5934,11 +6371,11 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1000x3000</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -5952,7 +6389,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>1000x2000</t>
+          <t>1220x2440</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">

--- a/cut_plan.xlsx
+++ b/cut_plan.xlsx
@@ -486,16 +486,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G249"/>
+  <dimension ref="A1:I249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -506,30 +508,40 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>פריסה</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>מס׳ חתיכה</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>מידת פלטה (מ״מ)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>חתיכה (מקור)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>רוחב חתיכה</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>אורך חתיכה</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>X (מ״מ)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Y (מ״מ)</t>
         </is>
@@ -538,10 +550,10 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>לוח 1</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+          <t>לוח 1 | פריסה 16</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
         </is>
@@ -551,36 +563,42 @@
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>1000x2000</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>5330×780 #1 ח1/3</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>780</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="G3" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="3" t="n">
+      <c r="H3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>לוח 2</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+          <t>לוח 2 | פריסה 16</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
         </is>
@@ -590,36 +608,42 @@
       <c r="A5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>1000x2000</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>5330×780 #1 ח2/3</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>780</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="G5" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="3" t="n">
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>לוח 3</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+          <t>לוח 3 | פריסה 16</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
         </is>
@@ -629,36 +653,42 @@
       <c r="A7" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>1000x2000</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>5330×780 #2 ח1/3</t>
         </is>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>780</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="G7" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="3" t="n">
+      <c r="H7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>לוח 4</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+          <t>לוח 4 | פריסה 16</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
         </is>
@@ -668,36 +698,42 @@
       <c r="A9" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>1000x2000</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>5330×780 #2 ח2/3</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>780</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="G9" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3" t="n">
+      <c r="H9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>לוח 5</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
+          <t>לוח 5 | פריסה 16</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
         </is>
@@ -707,36 +743,42 @@
       <c r="A11" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>1000x2000</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>5330×780 #3 ח1/3</t>
         </is>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>780</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="G11" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="3" t="n">
+      <c r="H11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>לוח 6</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
+          <t>לוח 6 | פריסה 16</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
         </is>
@@ -746,36 +788,42 @@
       <c r="A13" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>1000x2000</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>5330×780 #3 ח2/3</t>
         </is>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>780</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="G13" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="3" t="n">
+      <c r="H13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>לוח 7</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
+          <t>לוח 7 | פריסה 16</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
         </is>
@@ -785,36 +833,42 @@
       <c r="A15" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>1000x2000</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>5330×780 #4 ח1/3</t>
         </is>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>780</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="G15" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3" t="n">
+      <c r="H15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>לוח 8</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
+          <t>לוח 8 | פריסה 16</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
         </is>
@@ -824,36 +878,42 @@
       <c r="A17" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>1000x2000</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>5330×780 #4 ח2/3</t>
         </is>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>780</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="G17" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="3" t="n">
+      <c r="H17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>לוח 9</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
+          <t>לוח 9 | פריסה 16</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
         </is>
@@ -863,36 +923,42 @@
       <c r="A19" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>1000x2000</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>5330×780 #5 ח1/3</t>
         </is>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>780</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="G19" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="3" t="n">
+      <c r="H19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>לוח 10</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
+          <t>לוח 10 | פריסה 16</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
         </is>
@@ -902,36 +968,42 @@
       <c r="A21" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>1000x2000</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>5330×780 #5 ח2/3</t>
         </is>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>780</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="G21" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="3" t="n">
+      <c r="H21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>לוח 11</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
+          <t>לוח 11 | פריסה 16</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
         </is>
@@ -941,36 +1013,42 @@
       <c r="A23" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>1000x2000</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>5330×780 #6 ח1/3</t>
         </is>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>780</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="G23" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="3" t="n">
+      <c r="H23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>לוח 12</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
+          <t>לוח 12 | פריסה 16</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>1000x2000 | ניצול 78% | 1 חתיכות</t>
         </is>
@@ -980,36 +1058,42 @@
       <c r="A25" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>1000x2000</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>5330×780 #6 ח2/3</t>
         </is>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>780</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="G25" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="3" t="n">
+      <c r="H25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>לוח 13</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
+          <t>לוח 13 | פריסה 17</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>1000x2000 | ניצול 77% | 2 חתיכות</t>
         </is>
@@ -1019,26 +1103,32 @@
       <c r="A27" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>1000x2000</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>5330×780 #1 ח3/3</t>
         </is>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>780</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="G27" s="3" t="n">
         <v>1330</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="3" t="n">
+      <c r="H27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1046,36 +1136,42 @@
       <c r="A28" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>1000x2000</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>780×640 #1</t>
         </is>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>780</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="G28" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="3" t="n">
+      <c r="H28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="3" t="n">
         <v>1330</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>לוח 14</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
+          <t>לוח 14 | פריסה 17</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>1000x2000 | ניצול 77% | 2 חתיכות</t>
         </is>
@@ -1085,26 +1181,32 @@
       <c r="A30" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>1000x2000</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>5330×780 #2 ח3/3</t>
         </is>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>780</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="G30" s="3" t="n">
         <v>1330</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="3" t="n">
+      <c r="H30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1112,36 +1214,42 @@
       <c r="A31" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>1000x2000</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>780×640 #2</t>
         </is>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>780</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="G31" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="3" t="n">
+      <c r="H31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="3" t="n">
         <v>1330</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>לוח 15</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
+          <t>לוח 15 | פריסה 17</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>1000x2000 | ניצול 77% | 2 חתיכות</t>
         </is>
@@ -1151,26 +1259,32 @@
       <c r="A33" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>1000x2000</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>5330×780 #3 ח3/3</t>
         </is>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>780</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="G33" s="3" t="n">
         <v>1330</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="3" t="n">
+      <c r="H33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1178,36 +1292,42 @@
       <c r="A34" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>1000x2000</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>780×640 #3</t>
         </is>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>780</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="G34" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="3" t="n">
+      <c r="H34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="3" t="n">
         <v>1330</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>לוח 16</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
+          <t>לוח 16 | פריסה 17</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>1000x2000 | ניצול 77% | 2 חתיכות</t>
         </is>
@@ -1217,26 +1337,32 @@
       <c r="A36" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>1000x2000</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>5330×780 #4 ח3/3</t>
         </is>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>780</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="G36" s="3" t="n">
         <v>1330</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="3" t="n">
+      <c r="H36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1244,36 +1370,42 @@
       <c r="A37" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>1000x2000</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>780×640 #4</t>
         </is>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>780</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="G37" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="3" t="n">
+      <c r="H37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="3" t="n">
         <v>1330</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>לוח 17</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
+          <t>לוח 17 | פריסה 17</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>1000x2000 | ניצול 77% | 2 חתיכות</t>
         </is>
@@ -1283,26 +1415,32 @@
       <c r="A39" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>1000x2000</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>5330×780 #5 ח3/3</t>
         </is>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>780</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="G39" s="3" t="n">
         <v>1330</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="3" t="n">
+      <c r="H39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1310,36 +1448,42 @@
       <c r="A40" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>1000x2000</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>780×640 #5</t>
         </is>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>780</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="G40" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="3" t="n">
+      <c r="H40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="3" t="n">
         <v>1330</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>לוח 18</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
+          <t>לוח 18 | פריסה 17</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>1000x2000 | ניצול 77% | 2 חתיכות</t>
         </is>
@@ -1349,26 +1493,32 @@
       <c r="A42" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>1000x2000</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>5330×780 #6 ח3/3</t>
         </is>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>780</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="G42" s="3" t="n">
         <v>1330</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3" t="n">
+      <c r="H42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1376,36 +1526,42 @@
       <c r="A43" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>1000x2000</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>780×640 #6</t>
         </is>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>780</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="G43" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3" t="n">
+      <c r="H43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3" t="n">
         <v>1330</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>לוח 19</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
+          <t>לוח 19 | פריסה 18</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>1000x2000 | ניצול 75% | 3 חתיכות</t>
         </is>
@@ -1415,26 +1571,32 @@
       <c r="A45" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>1000x2000</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>780×640 #7</t>
         </is>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>780</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="G45" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3" t="n">
+      <c r="H45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1442,26 +1604,32 @@
       <c r="A46" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>1000x2000</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>780×640 #8</t>
         </is>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>780</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="G46" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="3" t="n">
+      <c r="H46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="3" t="n">
         <v>640</v>
       </c>
     </row>
@@ -1469,36 +1637,42 @@
       <c r="A47" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B47" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>1000x2000</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>780×640 #9</t>
         </is>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>780</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="G47" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3" t="n">
+      <c r="H47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3" t="n">
         <v>1280</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>לוח 20</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
+          <t>לוח 20 | פריסה 18</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>1000x2000 | ניצול 75% | 3 חתיכות</t>
         </is>
@@ -1508,26 +1682,32 @@
       <c r="A49" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>1000x2000</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>780×640 #10</t>
         </is>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="F49" s="3" t="n">
         <v>780</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="G49" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="F49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3" t="n">
+      <c r="H49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1535,26 +1715,32 @@
       <c r="A50" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>1000x2000</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="E50" s="3" t="inlineStr">
         <is>
           <t>780×640 #11</t>
         </is>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="F50" s="3" t="n">
         <v>780</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="G50" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="F50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="3" t="n">
+      <c r="H50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="3" t="n">
         <v>640</v>
       </c>
     </row>
@@ -1562,36 +1748,42 @@
       <c r="A51" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B51" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>1000x2000</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>780×640 #12</t>
         </is>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="F51" s="3" t="n">
         <v>780</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="G51" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="F51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="3" t="n">
+      <c r="H51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="3" t="n">
         <v>1280</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>לוח 21</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
+          <t>לוח 21 | פריסה 4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
@@ -1601,36 +1793,42 @@
       <c r="A53" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="B53" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #1 ח1/6</t>
         </is>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="F53" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="G53" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="3" t="n">
+      <c r="H53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>לוח 22</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
+          <t>לוח 22 | פריסה 4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
@@ -1640,36 +1838,42 @@
       <c r="A55" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="B55" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #1 ח3/6</t>
         </is>
       </c>
-      <c r="D55" s="3" t="n">
+      <c r="F55" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="E55" s="3" t="n">
+      <c r="G55" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" s="3" t="n">
+      <c r="H55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>לוח 23</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
+          <t>לוח 23 | פריסה 4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
@@ -1679,36 +1883,42 @@
       <c r="A57" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="B57" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #2 ח1/6</t>
         </is>
       </c>
-      <c r="D57" s="3" t="n">
+      <c r="F57" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="E57" s="3" t="n">
+      <c r="G57" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" s="3" t="n">
+      <c r="H57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>לוח 24</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
+          <t>לוח 24 | פריסה 4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
@@ -1718,36 +1928,42 @@
       <c r="A59" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="B59" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #2 ח3/6</t>
         </is>
       </c>
-      <c r="D59" s="3" t="n">
+      <c r="F59" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="E59" s="3" t="n">
+      <c r="G59" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3" t="n">
+      <c r="H59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>לוח 25</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
+          <t>לוח 25 | פריסה 4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
@@ -1757,36 +1973,42 @@
       <c r="A61" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="B61" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #3 ח1/6</t>
         </is>
       </c>
-      <c r="D61" s="3" t="n">
+      <c r="F61" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="E61" s="3" t="n">
+      <c r="G61" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F61" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" s="3" t="n">
+      <c r="H61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>לוח 26</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
+          <t>לוח 26 | פריסה 4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
@@ -1796,36 +2018,42 @@
       <c r="A63" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="B63" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #3 ח3/6</t>
         </is>
       </c>
-      <c r="D63" s="3" t="n">
+      <c r="F63" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="E63" s="3" t="n">
+      <c r="G63" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="3" t="n">
+      <c r="H63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>לוח 27</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
+          <t>לוח 27 | פריסה 4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
@@ -1835,36 +2063,42 @@
       <c r="A65" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="B65" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #4 ח1/6</t>
         </is>
       </c>
-      <c r="D65" s="3" t="n">
+      <c r="F65" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="E65" s="3" t="n">
+      <c r="G65" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" s="3" t="n">
+      <c r="H65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>לוח 28</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
+          <t>לוח 28 | פריסה 4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
@@ -1874,36 +2108,42 @@
       <c r="A67" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="B67" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #4 ח3/6</t>
         </is>
       </c>
-      <c r="D67" s="3" t="n">
+      <c r="F67" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="E67" s="3" t="n">
+      <c r="G67" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" s="3" t="n">
+      <c r="H67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>לוח 29</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
+          <t>לוח 29 | פריסה 4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
@@ -1913,36 +2153,42 @@
       <c r="A69" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="B69" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #5 ח1/6</t>
         </is>
       </c>
-      <c r="D69" s="3" t="n">
+      <c r="F69" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="E69" s="3" t="n">
+      <c r="G69" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" s="3" t="n">
+      <c r="H69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>לוח 30</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
+          <t>לוח 30 | פריסה 4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
@@ -1952,36 +2198,42 @@
       <c r="A71" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="B71" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #5 ח3/6</t>
         </is>
       </c>
-      <c r="D71" s="3" t="n">
+      <c r="F71" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="E71" s="3" t="n">
+      <c r="G71" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" s="3" t="n">
+      <c r="H71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>לוח 31</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
+          <t>לוח 31 | פריסה 4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
@@ -1991,36 +2243,42 @@
       <c r="A73" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="B73" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #6 ח1/6</t>
         </is>
       </c>
-      <c r="D73" s="3" t="n">
+      <c r="F73" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="E73" s="3" t="n">
+      <c r="G73" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" s="3" t="n">
+      <c r="H73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>לוח 32</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
+          <t>לוח 32 | פריסה 4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
@@ -2030,36 +2288,42 @@
       <c r="A75" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="B75" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #6 ח3/6</t>
         </is>
       </c>
-      <c r="D75" s="3" t="n">
+      <c r="F75" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="E75" s="3" t="n">
+      <c r="G75" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F75" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" s="3" t="n">
+      <c r="H75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>לוח 33</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
+          <t>לוח 33 | פריסה 5</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
@@ -2069,36 +2333,42 @@
       <c r="A77" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="B77" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
         <is>
           <t>6160×1200 #1 ח1/6</t>
         </is>
       </c>
-      <c r="D77" s="3" t="n">
+      <c r="F77" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="E77" s="3" t="n">
+      <c r="G77" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" s="3" t="n">
+      <c r="H77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>לוח 34</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
+          <t>לוח 34 | פריסה 5</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
@@ -2108,36 +2378,42 @@
       <c r="A79" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="B79" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
         <is>
           <t>6160×1200 #1 ח3/6</t>
         </is>
       </c>
-      <c r="D79" s="3" t="n">
+      <c r="F79" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="E79" s="3" t="n">
+      <c r="G79" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G79" s="3" t="n">
+      <c r="H79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>לוח 35</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
+          <t>לוח 35 | פריסה 5</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
@@ -2147,36 +2423,42 @@
       <c r="A81" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="B81" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
         <is>
           <t>6160×1200 #2 ח1/6</t>
         </is>
       </c>
-      <c r="D81" s="3" t="n">
+      <c r="F81" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="E81" s="3" t="n">
+      <c r="G81" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F81" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" s="3" t="n">
+      <c r="H81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>לוח 36</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
+          <t>לוח 36 | פריסה 5</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
@@ -2186,36 +2468,42 @@
       <c r="A83" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="B83" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
         <is>
           <t>6160×1200 #2 ח3/6</t>
         </is>
       </c>
-      <c r="D83" s="3" t="n">
+      <c r="F83" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="E83" s="3" t="n">
+      <c r="G83" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F83" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3" t="n">
+      <c r="H83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>לוח 37</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
+          <t>לוח 37 | פריסה 5</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
@@ -2225,36 +2513,42 @@
       <c r="A85" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="inlineStr">
+      <c r="B85" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
         <is>
           <t>6160×1200 #3 ח1/6</t>
         </is>
       </c>
-      <c r="D85" s="3" t="n">
+      <c r="F85" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="E85" s="3" t="n">
+      <c r="G85" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" s="3" t="n">
+      <c r="H85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>לוח 38</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
+          <t>לוח 38 | פריסה 5</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
@@ -2264,36 +2558,42 @@
       <c r="A87" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="inlineStr">
+      <c r="B87" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
         <is>
           <t>6160×1200 #3 ח3/6</t>
         </is>
       </c>
-      <c r="D87" s="3" t="n">
+      <c r="F87" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="E87" s="3" t="n">
+      <c r="G87" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" s="3" t="n">
+      <c r="H87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>לוח 39</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
+          <t>לוח 39 | פריסה 8</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 100% | 4 חתיכות</t>
         </is>
@@ -2303,26 +2603,32 @@
       <c r="A89" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="inlineStr">
+      <c r="B89" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
         <is>
           <t>9060×940 #1 ח1/4</t>
         </is>
       </c>
-      <c r="D89" s="3" t="n">
+      <c r="F89" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="E89" s="3" t="n">
+      <c r="G89" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3" t="n">
+      <c r="H89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2330,26 +2636,32 @@
       <c r="A90" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="B90" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C90" s="3" t="inlineStr">
+      <c r="B90" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
         <is>
           <t>9060×940 #1 ח4/4</t>
         </is>
       </c>
-      <c r="D90" s="3" t="n">
+      <c r="F90" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E90" s="3" t="n">
+      <c r="G90" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="F90" s="3" t="n">
+      <c r="H90" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="G90" s="3" t="n">
+      <c r="I90" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2357,26 +2669,32 @@
       <c r="A91" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C91" s="3" t="inlineStr">
+      <c r="B91" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
         <is>
           <t>9060×940 #2 ח4/4</t>
         </is>
       </c>
-      <c r="D91" s="3" t="n">
+      <c r="F91" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E91" s="3" t="n">
+      <c r="G91" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="F91" s="3" t="n">
+      <c r="H91" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="G91" s="3" t="n">
+      <c r="I91" s="3" t="n">
         <v>940</v>
       </c>
     </row>
@@ -2384,36 +2702,42 @@
       <c r="A92" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C92" s="3" t="inlineStr">
+      <c r="B92" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
         <is>
           <t>9060×940 #3 ח4/4</t>
         </is>
       </c>
-      <c r="D92" s="3" t="n">
+      <c r="F92" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E92" s="3" t="n">
+      <c r="G92" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="F92" s="3" t="n">
+      <c r="H92" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="G92" s="3" t="n">
+      <c r="I92" s="3" t="n">
         <v>1880</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>לוח 40</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
+          <t>לוח 40 | פריסה 8</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 100% | 4 חתיכות</t>
         </is>
@@ -2423,26 +2747,32 @@
       <c r="A94" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="B94" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C94" s="3" t="inlineStr">
+      <c r="B94" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
         <is>
           <t>9060×940 #1 ח2/4</t>
         </is>
       </c>
-      <c r="D94" s="3" t="n">
+      <c r="F94" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="E94" s="3" t="n">
+      <c r="G94" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F94" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3" t="n">
+      <c r="H94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2450,26 +2780,32 @@
       <c r="A95" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C95" s="3" t="inlineStr">
+      <c r="B95" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
         <is>
           <t>9060×940 #4 ח4/4</t>
         </is>
       </c>
-      <c r="D95" s="3" t="n">
+      <c r="F95" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E95" s="3" t="n">
+      <c r="G95" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="F95" s="3" t="n">
+      <c r="H95" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="G95" s="3" t="n">
+      <c r="I95" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2477,26 +2813,32 @@
       <c r="A96" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C96" s="3" t="inlineStr">
+      <c r="B96" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
         <is>
           <t>9060×940 #5 ח4/4</t>
         </is>
       </c>
-      <c r="D96" s="3" t="n">
+      <c r="F96" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E96" s="3" t="n">
+      <c r="G96" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="F96" s="3" t="n">
+      <c r="H96" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="G96" s="3" t="n">
+      <c r="I96" s="3" t="n">
         <v>940</v>
       </c>
     </row>
@@ -2504,36 +2846,42 @@
       <c r="A97" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="B97" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C97" s="3" t="inlineStr">
+      <c r="B97" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
         <is>
           <t>9060×940 #6 ח4/4</t>
         </is>
       </c>
-      <c r="D97" s="3" t="n">
+      <c r="F97" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E97" s="3" t="n">
+      <c r="G97" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="F97" s="3" t="n">
+      <c r="H97" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="G97" s="3" t="n">
+      <c r="I97" s="3" t="n">
         <v>1880</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>לוח 41</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
+          <t>לוח 41 | פריסה 11</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 99% | 4 חתיכות</t>
         </is>
@@ -2543,26 +2891,32 @@
       <c r="A99" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="B99" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C99" s="3" t="inlineStr">
+      <c r="B99" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
         <is>
           <t>9060×940 #1 ח3/4</t>
         </is>
       </c>
-      <c r="D99" s="3" t="n">
+      <c r="F99" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="E99" s="3" t="n">
+      <c r="G99" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F99" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" s="3" t="n">
+      <c r="H99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2570,26 +2924,32 @@
       <c r="A100" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="inlineStr">
+      <c r="B100" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
         <is>
           <t>9060×800 #1 ח4/4</t>
         </is>
       </c>
-      <c r="D100" s="3" t="n">
+      <c r="F100" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E100" s="3" t="n">
+      <c r="G100" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="F100" s="3" t="n">
+      <c r="H100" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="G100" s="3" t="n">
+      <c r="I100" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2597,26 +2957,32 @@
       <c r="A101" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C101" s="3" t="inlineStr">
+      <c r="B101" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
         <is>
           <t>9060×800 #2 ח4/4</t>
         </is>
       </c>
-      <c r="D101" s="3" t="n">
+      <c r="F101" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E101" s="3" t="n">
+      <c r="G101" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="F101" s="3" t="n">
+      <c r="H101" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="G101" s="3" t="n">
+      <c r="I101" s="3" t="n">
         <v>800</v>
       </c>
     </row>
@@ -2624,36 +2990,42 @@
       <c r="A102" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="B102" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C102" s="3" t="inlineStr">
+      <c r="B102" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
         <is>
           <t>9060×800 #3 ח4/4</t>
         </is>
       </c>
-      <c r="D102" s="3" t="n">
+      <c r="F102" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E102" s="3" t="n">
+      <c r="G102" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="F102" s="3" t="n">
+      <c r="H102" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="G102" s="3" t="n">
+      <c r="I102" s="3" t="n">
         <v>1600</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>לוח 42</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
+          <t>לוח 42 | פריסה 3</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
         </is>
@@ -2663,36 +3035,42 @@
       <c r="A104" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C104" s="3" t="inlineStr">
+      <c r="B104" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
         <is>
           <t>9060×940 #2 ח1/4</t>
         </is>
       </c>
-      <c r="D104" s="3" t="n">
+      <c r="F104" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="E104" s="3" t="n">
+      <c r="G104" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F104" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" s="3" t="n">
+      <c r="H104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>לוח 43</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
+          <t>לוח 43 | פריסה 3</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
         </is>
@@ -2702,36 +3080,42 @@
       <c r="A106" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C106" s="3" t="inlineStr">
+      <c r="B106" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
         <is>
           <t>9060×940 #2 ח2/4</t>
         </is>
       </c>
-      <c r="D106" s="3" t="n">
+      <c r="F106" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="E106" s="3" t="n">
+      <c r="G106" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F106" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G106" s="3" t="n">
+      <c r="H106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>לוח 44</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
+          <t>לוח 44 | פריסה 3</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
         </is>
@@ -2741,36 +3125,42 @@
       <c r="A108" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="B108" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C108" s="3" t="inlineStr">
+      <c r="B108" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
         <is>
           <t>9060×940 #2 ח3/4</t>
         </is>
       </c>
-      <c r="D108" s="3" t="n">
+      <c r="F108" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="E108" s="3" t="n">
+      <c r="G108" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F108" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G108" s="3" t="n">
+      <c r="H108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>לוח 45</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
+          <t>לוח 45 | פריסה 3</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
         </is>
@@ -2780,36 +3170,42 @@
       <c r="A110" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="B110" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C110" s="3" t="inlineStr">
+      <c r="B110" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
         <is>
           <t>9060×940 #3 ח1/4</t>
         </is>
       </c>
-      <c r="D110" s="3" t="n">
+      <c r="F110" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="E110" s="3" t="n">
+      <c r="G110" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F110" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G110" s="3" t="n">
+      <c r="H110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>לוח 46</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
+          <t>לוח 46 | פריסה 3</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
         </is>
@@ -2819,36 +3215,42 @@
       <c r="A112" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="B112" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C112" s="3" t="inlineStr">
+      <c r="B112" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
         <is>
           <t>9060×940 #3 ח2/4</t>
         </is>
       </c>
-      <c r="D112" s="3" t="n">
+      <c r="F112" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="E112" s="3" t="n">
+      <c r="G112" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F112" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G112" s="3" t="n">
+      <c r="H112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>לוח 47</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
+          <t>לוח 47 | פריסה 3</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
         </is>
@@ -2858,36 +3260,42 @@
       <c r="A114" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="B114" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C114" s="3" t="inlineStr">
+      <c r="B114" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
         <is>
           <t>9060×940 #3 ח3/4</t>
         </is>
       </c>
-      <c r="D114" s="3" t="n">
+      <c r="F114" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="E114" s="3" t="n">
+      <c r="G114" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F114" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G114" s="3" t="n">
+      <c r="H114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>לוח 48</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
+          <t>לוח 48 | פריסה 3</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
         </is>
@@ -2897,36 +3305,42 @@
       <c r="A116" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="B116" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C116" s="3" t="inlineStr">
+      <c r="B116" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
         <is>
           <t>9060×940 #4 ח1/4</t>
         </is>
       </c>
-      <c r="D116" s="3" t="n">
+      <c r="F116" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="E116" s="3" t="n">
+      <c r="G116" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F116" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G116" s="3" t="n">
+      <c r="H116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>לוח 49</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
+          <t>לוח 49 | פריסה 3</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
         </is>
@@ -2936,36 +3350,42 @@
       <c r="A118" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="B118" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C118" s="3" t="inlineStr">
+      <c r="B118" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
         <is>
           <t>9060×940 #4 ח2/4</t>
         </is>
       </c>
-      <c r="D118" s="3" t="n">
+      <c r="F118" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="E118" s="3" t="n">
+      <c r="G118" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F118" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G118" s="3" t="n">
+      <c r="H118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>לוח 50</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
+          <t>לוח 50 | פריסה 3</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
         </is>
@@ -2975,36 +3395,42 @@
       <c r="A120" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C120" s="3" t="inlineStr">
+      <c r="B120" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
         <is>
           <t>9060×940 #4 ח3/4</t>
         </is>
       </c>
-      <c r="D120" s="3" t="n">
+      <c r="F120" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="E120" s="3" t="n">
+      <c r="G120" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F120" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G120" s="3" t="n">
+      <c r="H120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>לוח 51</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
+          <t>לוח 51 | פריסה 3</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
         </is>
@@ -3014,36 +3440,42 @@
       <c r="A122" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="B122" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C122" s="3" t="inlineStr">
+      <c r="B122" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
         <is>
           <t>9060×940 #5 ח1/4</t>
         </is>
       </c>
-      <c r="D122" s="3" t="n">
+      <c r="F122" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="E122" s="3" t="n">
+      <c r="G122" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F122" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G122" s="3" t="n">
+      <c r="H122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>לוח 52</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
+          <t>לוח 52 | פריסה 3</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
         </is>
@@ -3053,36 +3485,42 @@
       <c r="A124" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="B124" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C124" s="3" t="inlineStr">
+      <c r="B124" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
         <is>
           <t>9060×940 #5 ח2/4</t>
         </is>
       </c>
-      <c r="D124" s="3" t="n">
+      <c r="F124" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="E124" s="3" t="n">
+      <c r="G124" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F124" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G124" s="3" t="n">
+      <c r="H124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>לוח 53</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
+          <t>לוח 53 | פריסה 3</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
         </is>
@@ -3092,36 +3530,42 @@
       <c r="A126" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="B126" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C126" s="3" t="inlineStr">
+      <c r="B126" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
         <is>
           <t>9060×940 #5 ח3/4</t>
         </is>
       </c>
-      <c r="D126" s="3" t="n">
+      <c r="F126" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="E126" s="3" t="n">
+      <c r="G126" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F126" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G126" s="3" t="n">
+      <c r="H126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>לוח 54</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
+          <t>לוח 54 | פריסה 3</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
         </is>
@@ -3131,36 +3575,42 @@
       <c r="A128" s="3" t="n">
         <v>54</v>
       </c>
-      <c r="B128" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C128" s="3" t="inlineStr">
+      <c r="B128" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
         <is>
           <t>9060×940 #6 ח1/4</t>
         </is>
       </c>
-      <c r="D128" s="3" t="n">
+      <c r="F128" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="E128" s="3" t="n">
+      <c r="G128" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F128" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G128" s="3" t="n">
+      <c r="H128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>לוח 55</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
+          <t>לוח 55 | פריסה 3</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
         </is>
@@ -3170,36 +3620,42 @@
       <c r="A130" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="B130" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C130" s="3" t="inlineStr">
+      <c r="B130" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
         <is>
           <t>9060×940 #6 ח2/4</t>
         </is>
       </c>
-      <c r="D130" s="3" t="n">
+      <c r="F130" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="E130" s="3" t="n">
+      <c r="G130" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F130" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G130" s="3" t="n">
+      <c r="H130" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>לוח 56</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
+          <t>לוח 56 | פריסה 3</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
         </is>
@@ -3209,36 +3665,42 @@
       <c r="A132" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="B132" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C132" s="3" t="inlineStr">
+      <c r="B132" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
         <is>
           <t>9060×940 #6 ח3/4</t>
         </is>
       </c>
-      <c r="D132" s="3" t="n">
+      <c r="F132" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="E132" s="3" t="n">
+      <c r="G132" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F132" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G132" s="3" t="n">
+      <c r="H132" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>לוח 57</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
+          <t>לוח 57 | פריסה 6</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 100% | 2 חתיכות</t>
         </is>
@@ -3248,26 +3710,32 @@
       <c r="A134" s="3" t="n">
         <v>57</v>
       </c>
-      <c r="B134" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C134" s="3" t="inlineStr">
+      <c r="B134" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
         <is>
           <t>9060×800 #1 ח1/4</t>
         </is>
       </c>
-      <c r="D134" s="3" t="n">
+      <c r="F134" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="E134" s="3" t="n">
+      <c r="G134" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F134" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G134" s="3" t="n">
+      <c r="H134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3275,36 +3743,42 @@
       <c r="A135" s="3" t="n">
         <v>57</v>
       </c>
-      <c r="B135" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C135" s="3" t="inlineStr">
+      <c r="B135" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
         <is>
           <t>6160×1200 #1 ח2/6</t>
         </is>
       </c>
-      <c r="D135" s="3" t="n">
+      <c r="F135" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E135" s="3" t="n">
+      <c r="G135" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F135" s="3" t="n">
+      <c r="H135" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="G135" s="3" t="n">
+      <c r="I135" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>לוח 58</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
+          <t>לוח 58 | פריסה 6</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 100% | 2 חתיכות</t>
         </is>
@@ -3314,26 +3788,32 @@
       <c r="A137" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="B137" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C137" s="3" t="inlineStr">
+      <c r="B137" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C137" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
         <is>
           <t>9060×800 #1 ח2/4</t>
         </is>
       </c>
-      <c r="D137" s="3" t="n">
+      <c r="F137" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="E137" s="3" t="n">
+      <c r="G137" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F137" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G137" s="3" t="n">
+      <c r="H137" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3341,36 +3821,42 @@
       <c r="A138" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="B138" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C138" s="3" t="inlineStr">
+      <c r="B138" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C138" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
         <is>
           <t>6160×1200 #1 ח4/6</t>
         </is>
       </c>
-      <c r="D138" s="3" t="n">
+      <c r="F138" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E138" s="3" t="n">
+      <c r="G138" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F138" s="3" t="n">
+      <c r="H138" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="G138" s="3" t="n">
+      <c r="I138" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>לוח 59</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
+          <t>לוח 59 | פריסה 6</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 100% | 2 חתיכות</t>
         </is>
@@ -3380,26 +3866,32 @@
       <c r="A140" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="B140" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C140" s="3" t="inlineStr">
+      <c r="B140" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C140" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
         <is>
           <t>9060×800 #1 ח3/4</t>
         </is>
       </c>
-      <c r="D140" s="3" t="n">
+      <c r="F140" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="E140" s="3" t="n">
+      <c r="G140" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F140" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G140" s="3" t="n">
+      <c r="H140" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3407,36 +3899,42 @@
       <c r="A141" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="B141" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C141" s="3" t="inlineStr">
+      <c r="B141" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C141" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
         <is>
           <t>6160×1200 #2 ח2/6</t>
         </is>
       </c>
-      <c r="D141" s="3" t="n">
+      <c r="F141" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E141" s="3" t="n">
+      <c r="G141" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F141" s="3" t="n">
+      <c r="H141" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="G141" s="3" t="n">
+      <c r="I141" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>לוח 60</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
+          <t>לוח 60 | פריסה 6</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 100% | 2 חתיכות</t>
         </is>
@@ -3446,26 +3944,32 @@
       <c r="A143" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="B143" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C143" s="3" t="inlineStr">
+      <c r="B143" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C143" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
         <is>
           <t>9060×800 #2 ח1/4</t>
         </is>
       </c>
-      <c r="D143" s="3" t="n">
+      <c r="F143" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="E143" s="3" t="n">
+      <c r="G143" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F143" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G143" s="3" t="n">
+      <c r="H143" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3473,36 +3977,42 @@
       <c r="A144" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="B144" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C144" s="3" t="inlineStr">
+      <c r="B144" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C144" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
         <is>
           <t>6160×1200 #2 ח4/6</t>
         </is>
       </c>
-      <c r="D144" s="3" t="n">
+      <c r="F144" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E144" s="3" t="n">
+      <c r="G144" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F144" s="3" t="n">
+      <c r="H144" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="G144" s="3" t="n">
+      <c r="I144" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>לוח 61</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
+          <t>לוח 61 | פריסה 6</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 100% | 2 חתיכות</t>
         </is>
@@ -3512,26 +4022,32 @@
       <c r="A146" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="B146" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C146" s="3" t="inlineStr">
+      <c r="B146" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C146" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
         <is>
           <t>9060×800 #2 ח2/4</t>
         </is>
       </c>
-      <c r="D146" s="3" t="n">
+      <c r="F146" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="E146" s="3" t="n">
+      <c r="G146" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F146" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G146" s="3" t="n">
+      <c r="H146" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3539,36 +4055,42 @@
       <c r="A147" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="B147" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C147" s="3" t="inlineStr">
+      <c r="B147" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C147" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
         <is>
           <t>6160×1200 #3 ח2/6</t>
         </is>
       </c>
-      <c r="D147" s="3" t="n">
+      <c r="F147" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E147" s="3" t="n">
+      <c r="G147" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F147" s="3" t="n">
+      <c r="H147" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="G147" s="3" t="n">
+      <c r="I147" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>לוח 62</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
+          <t>לוח 62 | פריסה 6</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 100% | 2 חתיכות</t>
         </is>
@@ -3578,26 +4100,32 @@
       <c r="A149" s="3" t="n">
         <v>62</v>
       </c>
-      <c r="B149" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C149" s="3" t="inlineStr">
+      <c r="B149" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C149" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
         <is>
           <t>9060×800 #2 ח3/4</t>
         </is>
       </c>
-      <c r="D149" s="3" t="n">
+      <c r="F149" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="E149" s="3" t="n">
+      <c r="G149" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F149" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G149" s="3" t="n">
+      <c r="H149" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3605,36 +4133,42 @@
       <c r="A150" s="3" t="n">
         <v>62</v>
       </c>
-      <c r="B150" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C150" s="3" t="inlineStr">
+      <c r="B150" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C150" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
         <is>
           <t>6160×1200 #3 ח4/6</t>
         </is>
       </c>
-      <c r="D150" s="3" t="n">
+      <c r="F150" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E150" s="3" t="n">
+      <c r="G150" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F150" s="3" t="n">
+      <c r="H150" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="G150" s="3" t="n">
+      <c r="I150" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>לוח 63</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
+          <t>לוח 63 | פריסה 9</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 96% | 4 חתיכות</t>
         </is>
@@ -3644,26 +4178,32 @@
       <c r="A152" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="B152" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C152" s="3" t="inlineStr">
+      <c r="B152" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C152" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
         <is>
           <t>9060×800 #3 ח1/4</t>
         </is>
       </c>
-      <c r="D152" s="3" t="n">
+      <c r="F152" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="E152" s="3" t="n">
+      <c r="G152" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F152" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G152" s="3" t="n">
+      <c r="H152" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3671,26 +4211,32 @@
       <c r="A153" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="B153" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C153" s="3" t="inlineStr">
+      <c r="B153" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C153" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #1 ח5/6</t>
         </is>
       </c>
-      <c r="D153" s="3" t="n">
+      <c r="F153" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="E153" s="3" t="n">
+      <c r="G153" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F153" s="3" t="n">
+      <c r="H153" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="G153" s="3" t="n">
+      <c r="I153" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3698,26 +4244,32 @@
       <c r="A154" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="B154" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C154" s="3" t="inlineStr">
+      <c r="B154" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C154" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #2 ח5/6</t>
         </is>
       </c>
-      <c r="D154" s="3" t="n">
+      <c r="F154" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="E154" s="3" t="n">
+      <c r="G154" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F154" s="3" t="n">
+      <c r="H154" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="G154" s="3" t="n">
+      <c r="I154" s="3" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -3725,36 +4277,42 @@
       <c r="A155" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="B155" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C155" s="3" t="inlineStr">
+      <c r="B155" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C155" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #3 ח5/6</t>
         </is>
       </c>
-      <c r="D155" s="3" t="n">
+      <c r="F155" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="E155" s="3" t="n">
+      <c r="G155" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F155" s="3" t="n">
+      <c r="H155" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="G155" s="3" t="n">
+      <c r="I155" s="3" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>לוח 64</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
+          <t>לוח 64 | פריסה 9</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 96% | 4 חתיכות</t>
         </is>
@@ -3764,26 +4322,32 @@
       <c r="A157" s="3" t="n">
         <v>64</v>
       </c>
-      <c r="B157" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C157" s="3" t="inlineStr">
+      <c r="B157" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C157" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
         <is>
           <t>9060×800 #3 ח2/4</t>
         </is>
       </c>
-      <c r="D157" s="3" t="n">
+      <c r="F157" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="E157" s="3" t="n">
+      <c r="G157" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F157" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G157" s="3" t="n">
+      <c r="H157" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I157" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3791,26 +4355,32 @@
       <c r="A158" s="3" t="n">
         <v>64</v>
       </c>
-      <c r="B158" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C158" s="3" t="inlineStr">
+      <c r="B158" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C158" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #4 ח5/6</t>
         </is>
       </c>
-      <c r="D158" s="3" t="n">
+      <c r="F158" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="E158" s="3" t="n">
+      <c r="G158" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F158" s="3" t="n">
+      <c r="H158" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="G158" s="3" t="n">
+      <c r="I158" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3818,26 +4388,32 @@
       <c r="A159" s="3" t="n">
         <v>64</v>
       </c>
-      <c r="B159" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C159" s="3" t="inlineStr">
+      <c r="B159" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C159" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #5 ח5/6</t>
         </is>
       </c>
-      <c r="D159" s="3" t="n">
+      <c r="F159" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="E159" s="3" t="n">
+      <c r="G159" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F159" s="3" t="n">
+      <c r="H159" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="G159" s="3" t="n">
+      <c r="I159" s="3" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -3845,36 +4421,42 @@
       <c r="A160" s="3" t="n">
         <v>64</v>
       </c>
-      <c r="B160" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C160" s="3" t="inlineStr">
+      <c r="B160" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C160" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #6 ח5/6</t>
         </is>
       </c>
-      <c r="D160" s="3" t="n">
+      <c r="F160" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="E160" s="3" t="n">
+      <c r="G160" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F160" s="3" t="n">
+      <c r="H160" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="G160" s="3" t="n">
+      <c r="I160" s="3" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>לוח 65</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
+          <t>לוח 65 | פריסה 12</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 96% | 4 חתיכות</t>
         </is>
@@ -3884,26 +4466,32 @@
       <c r="A162" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="B162" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C162" s="3" t="inlineStr">
+      <c r="B162" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C162" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="inlineStr">
         <is>
           <t>9060×800 #3 ח3/4</t>
         </is>
       </c>
-      <c r="D162" s="3" t="n">
+      <c r="F162" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="E162" s="3" t="n">
+      <c r="G162" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F162" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G162" s="3" t="n">
+      <c r="H162" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I162" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3911,26 +4499,32 @@
       <c r="A163" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="B163" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C163" s="3" t="inlineStr">
+      <c r="B163" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C163" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
         <is>
           <t>6160×1200 #1 ח5/6</t>
         </is>
       </c>
-      <c r="D163" s="3" t="n">
+      <c r="F163" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="E163" s="3" t="n">
+      <c r="G163" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F163" s="3" t="n">
+      <c r="H163" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="G163" s="3" t="n">
+      <c r="I163" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3938,26 +4532,32 @@
       <c r="A164" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="B164" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C164" s="3" t="inlineStr">
+      <c r="B164" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C164" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
         <is>
           <t>6160×1200 #2 ח5/6</t>
         </is>
       </c>
-      <c r="D164" s="3" t="n">
+      <c r="F164" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="E164" s="3" t="n">
+      <c r="G164" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F164" s="3" t="n">
+      <c r="H164" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="G164" s="3" t="n">
+      <c r="I164" s="3" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -3965,36 +4565,42 @@
       <c r="A165" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="B165" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C165" s="3" t="inlineStr">
+      <c r="B165" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C165" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
         <is>
           <t>6160×1200 #3 ח5/6</t>
         </is>
       </c>
-      <c r="D165" s="3" t="n">
+      <c r="F165" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="E165" s="3" t="n">
+      <c r="G165" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F165" s="3" t="n">
+      <c r="H165" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="G165" s="3" t="n">
+      <c r="I165" s="3" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>לוח 66</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
+          <t>לוח 66 | פריסה 13</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 91% | 11 חתיכות</t>
         </is>
@@ -4004,26 +4610,32 @@
       <c r="A167" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="B167" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C167" s="3" t="inlineStr">
+      <c r="B167" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C167" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
         <is>
           <t>1240×1200 #1 ח1/2</t>
         </is>
       </c>
-      <c r="D167" s="3" t="n">
+      <c r="F167" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="E167" s="3" t="n">
+      <c r="G167" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="F167" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G167" s="3" t="n">
+      <c r="H167" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I167" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4031,26 +4643,32 @@
       <c r="A168" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="B168" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C168" s="3" t="inlineStr">
+      <c r="B168" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C168" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
         <is>
           <t>1240×1200 #2 ח1/2</t>
         </is>
       </c>
-      <c r="D168" s="3" t="n">
+      <c r="F168" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="E168" s="3" t="n">
+      <c r="G168" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="F168" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G168" s="3" t="n">
+      <c r="H168" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I168" s="3" t="n">
         <v>1200</v>
       </c>
     </row>
@@ -4058,26 +4676,32 @@
       <c r="A169" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="B169" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C169" s="3" t="inlineStr">
+      <c r="B169" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C169" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #1 ח6/6</t>
         </is>
       </c>
-      <c r="D169" s="3" t="n">
+      <c r="F169" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="E169" s="3" t="n">
+      <c r="G169" s="3" t="n">
         <v>240</v>
       </c>
-      <c r="F169" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G169" s="3" t="n">
+      <c r="H169" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I169" s="3" t="n">
         <v>2400</v>
       </c>
     </row>
@@ -4085,26 +4709,32 @@
       <c r="A170" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="B170" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C170" s="3" t="inlineStr">
+      <c r="B170" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C170" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #3 ח6/6</t>
         </is>
-      </c>
-      <c r="D170" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="E170" s="3" t="n">
-        <v>240</v>
       </c>
       <c r="F170" s="3" t="n">
         <v>160</v>
       </c>
       <c r="G170" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="H170" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="I170" s="3" t="n">
         <v>2400</v>
       </c>
     </row>
@@ -4112,26 +4742,32 @@
       <c r="A171" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="B171" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C171" s="3" t="inlineStr">
+      <c r="B171" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C171" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #5 ח6/6</t>
         </is>
       </c>
-      <c r="D171" s="3" t="n">
+      <c r="F171" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="E171" s="3" t="n">
+      <c r="G171" s="3" t="n">
         <v>240</v>
       </c>
-      <c r="F171" s="3" t="n">
+      <c r="H171" s="3" t="n">
         <v>320</v>
       </c>
-      <c r="G171" s="3" t="n">
+      <c r="I171" s="3" t="n">
         <v>2400</v>
       </c>
     </row>
@@ -4139,26 +4775,32 @@
       <c r="A172" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="B172" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C172" s="3" t="inlineStr">
+      <c r="B172" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C172" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
         <is>
           <t>6160×1200 #1 ח6/6</t>
         </is>
       </c>
-      <c r="D172" s="3" t="n">
+      <c r="F172" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E172" s="3" t="n">
+      <c r="G172" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="F172" s="3" t="n">
+      <c r="H172" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="G172" s="3" t="n">
+      <c r="I172" s="3" t="n">
         <v>2400</v>
       </c>
     </row>
@@ -4166,26 +4808,32 @@
       <c r="A173" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="B173" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C173" s="3" t="inlineStr">
+      <c r="B173" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C173" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
         <is>
           <t>6160×1200 #2 ח6/6</t>
         </is>
       </c>
-      <c r="D173" s="3" t="n">
+      <c r="F173" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E173" s="3" t="n">
+      <c r="G173" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="F173" s="3" t="n">
+      <c r="H173" s="3" t="n">
         <v>680</v>
       </c>
-      <c r="G173" s="3" t="n">
+      <c r="I173" s="3" t="n">
         <v>2400</v>
       </c>
     </row>
@@ -4193,26 +4841,32 @@
       <c r="A174" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="B174" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C174" s="3" t="inlineStr">
+      <c r="B174" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C174" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="inlineStr">
         <is>
           <t>6160×1200 #3 ח6/6</t>
         </is>
       </c>
-      <c r="D174" s="3" t="n">
+      <c r="F174" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="E174" s="3" t="n">
+      <c r="G174" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="F174" s="3" t="n">
+      <c r="H174" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="G174" s="3" t="n">
+      <c r="I174" s="3" t="n">
         <v>2560</v>
       </c>
     </row>
@@ -4220,26 +4874,32 @@
       <c r="A175" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="B175" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C175" s="3" t="inlineStr">
+      <c r="B175" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C175" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #2 ח6/6</t>
         </is>
       </c>
-      <c r="D175" s="3" t="n">
+      <c r="F175" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="E175" s="3" t="n">
+      <c r="G175" s="3" t="n">
         <v>240</v>
       </c>
-      <c r="F175" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G175" s="3" t="n">
+      <c r="H175" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I175" s="3" t="n">
         <v>2640</v>
       </c>
     </row>
@@ -4247,26 +4907,32 @@
       <c r="A176" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="B176" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C176" s="3" t="inlineStr">
+      <c r="B176" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C176" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #4 ח6/6</t>
         </is>
-      </c>
-      <c r="D176" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="E176" s="3" t="n">
-        <v>240</v>
       </c>
       <c r="F176" s="3" t="n">
         <v>160</v>
       </c>
       <c r="G176" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="H176" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="I176" s="3" t="n">
         <v>2640</v>
       </c>
     </row>
@@ -4274,36 +4940,42 @@
       <c r="A177" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="B177" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C177" s="3" t="inlineStr">
+      <c r="B177" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C177" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #6 ח6/6</t>
         </is>
       </c>
-      <c r="D177" s="3" t="n">
+      <c r="F177" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="E177" s="3" t="n">
+      <c r="G177" s="3" t="n">
         <v>240</v>
       </c>
-      <c r="F177" s="3" t="n">
+      <c r="H177" s="3" t="n">
         <v>320</v>
       </c>
-      <c r="G177" s="3" t="n">
+      <c r="I177" s="3" t="n">
         <v>2640</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>לוח 67</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
+          <t>לוח 67 | פריסה 10</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 80% | 2 חתיכות</t>
         </is>
@@ -4313,26 +4985,32 @@
       <c r="A179" s="3" t="n">
         <v>67</v>
       </c>
-      <c r="B179" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C179" s="3" t="inlineStr">
+      <c r="B179" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C179" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
         <is>
           <t>1240×1200 #3 ח1/2</t>
         </is>
       </c>
-      <c r="D179" s="3" t="n">
+      <c r="F179" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="E179" s="3" t="n">
+      <c r="G179" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="F179" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G179" s="3" t="n">
+      <c r="H179" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I179" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4340,36 +5018,42 @@
       <c r="A180" s="3" t="n">
         <v>67</v>
       </c>
-      <c r="B180" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C180" s="3" t="inlineStr">
+      <c r="B180" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C180" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="inlineStr">
         <is>
           <t>1240×1200 #4 ח1/2</t>
         </is>
       </c>
-      <c r="D180" s="3" t="n">
+      <c r="F180" s="3" t="n">
         <v>1000</v>
-      </c>
-      <c r="E180" s="3" t="n">
-        <v>1200</v>
-      </c>
-      <c r="F180" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="G180" s="3" t="n">
         <v>1200</v>
       </c>
+      <c r="H180" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I180" s="3" t="n">
+        <v>1200</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>לוח 68</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="inlineStr">
+          <t>לוח 68 | פריסה 10</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 80% | 2 חתיכות</t>
         </is>
@@ -4379,26 +5063,32 @@
       <c r="A182" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="B182" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C182" s="3" t="inlineStr">
+      <c r="B182" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C182" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="inlineStr">
         <is>
           <t>1240×1200 #5 ח1/2</t>
         </is>
       </c>
-      <c r="D182" s="3" t="n">
+      <c r="F182" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="E182" s="3" t="n">
+      <c r="G182" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="F182" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G182" s="3" t="n">
+      <c r="H182" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I182" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4406,36 +5096,42 @@
       <c r="A183" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="B183" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C183" s="3" t="inlineStr">
+      <c r="B183" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C183" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="inlineStr">
         <is>
           <t>1240×1200 #6 ח1/2</t>
         </is>
       </c>
-      <c r="D183" s="3" t="n">
+      <c r="F183" s="3" t="n">
         <v>1000</v>
-      </c>
-      <c r="E183" s="3" t="n">
-        <v>1200</v>
-      </c>
-      <c r="F183" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="G183" s="3" t="n">
         <v>1200</v>
       </c>
+      <c r="H183" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I183" s="3" t="n">
+        <v>1200</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>לוח 69</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="inlineStr">
+          <t>לוח 69 | פריסה 7</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 96% | 4 חתיכות</t>
         </is>
@@ -4445,26 +5141,32 @@
       <c r="A185" s="3" t="n">
         <v>69</v>
       </c>
-      <c r="B185" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C185" s="3" t="inlineStr">
+      <c r="B185" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C185" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #1 ח2/6</t>
         </is>
       </c>
-      <c r="D185" s="3" t="n">
+      <c r="F185" s="3" t="n">
         <v>240</v>
       </c>
-      <c r="E185" s="3" t="n">
+      <c r="G185" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F185" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G185" s="3" t="n">
+      <c r="H185" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I185" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4472,26 +5174,32 @@
       <c r="A186" s="3" t="n">
         <v>69</v>
       </c>
-      <c r="B186" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C186" s="3" t="inlineStr">
+      <c r="B186" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C186" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #1 ח4/6</t>
         </is>
-      </c>
-      <c r="D186" s="3" t="n">
-        <v>240</v>
-      </c>
-      <c r="E186" s="3" t="n">
-        <v>3000</v>
       </c>
       <c r="F186" s="3" t="n">
         <v>240</v>
       </c>
       <c r="G186" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H186" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="I186" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4499,26 +5207,32 @@
       <c r="A187" s="3" t="n">
         <v>69</v>
       </c>
-      <c r="B187" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C187" s="3" t="inlineStr">
+      <c r="B187" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C187" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #2 ח2/6</t>
         </is>
       </c>
-      <c r="D187" s="3" t="n">
+      <c r="F187" s="3" t="n">
         <v>240</v>
       </c>
-      <c r="E187" s="3" t="n">
+      <c r="G187" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F187" s="3" t="n">
+      <c r="H187" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="G187" s="3" t="n">
+      <c r="I187" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4526,36 +5240,42 @@
       <c r="A188" s="3" t="n">
         <v>69</v>
       </c>
-      <c r="B188" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C188" s="3" t="inlineStr">
+      <c r="B188" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C188" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #2 ח4/6</t>
         </is>
       </c>
-      <c r="D188" s="3" t="n">
+      <c r="F188" s="3" t="n">
         <v>240</v>
       </c>
-      <c r="E188" s="3" t="n">
+      <c r="G188" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F188" s="3" t="n">
+      <c r="H188" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="G188" s="3" t="n">
+      <c r="I188" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>לוח 70</t>
-        </is>
-      </c>
-      <c r="C189" s="2" t="inlineStr">
+          <t>לוח 70 | פריסה 7</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 96% | 4 חתיכות</t>
         </is>
@@ -4565,26 +5285,32 @@
       <c r="A190" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="B190" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C190" s="3" t="inlineStr">
+      <c r="B190" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C190" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #3 ח2/6</t>
         </is>
       </c>
-      <c r="D190" s="3" t="n">
+      <c r="F190" s="3" t="n">
         <v>240</v>
       </c>
-      <c r="E190" s="3" t="n">
+      <c r="G190" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F190" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G190" s="3" t="n">
+      <c r="H190" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I190" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4592,26 +5318,32 @@
       <c r="A191" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="B191" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C191" s="3" t="inlineStr">
+      <c r="B191" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C191" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #3 ח4/6</t>
         </is>
-      </c>
-      <c r="D191" s="3" t="n">
-        <v>240</v>
-      </c>
-      <c r="E191" s="3" t="n">
-        <v>3000</v>
       </c>
       <c r="F191" s="3" t="n">
         <v>240</v>
       </c>
       <c r="G191" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H191" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="I191" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4619,26 +5351,32 @@
       <c r="A192" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="B192" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C192" s="3" t="inlineStr">
+      <c r="B192" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C192" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #4 ח2/6</t>
         </is>
       </c>
-      <c r="D192" s="3" t="n">
+      <c r="F192" s="3" t="n">
         <v>240</v>
       </c>
-      <c r="E192" s="3" t="n">
+      <c r="G192" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F192" s="3" t="n">
+      <c r="H192" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="G192" s="3" t="n">
+      <c r="I192" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4646,36 +5384,42 @@
       <c r="A193" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="B193" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C193" s="3" t="inlineStr">
+      <c r="B193" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C193" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #4 ח4/6</t>
         </is>
       </c>
-      <c r="D193" s="3" t="n">
+      <c r="F193" s="3" t="n">
         <v>240</v>
       </c>
-      <c r="E193" s="3" t="n">
+      <c r="G193" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F193" s="3" t="n">
+      <c r="H193" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="G193" s="3" t="n">
+      <c r="I193" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>לוח 71</t>
-        </is>
-      </c>
-      <c r="C194" s="2" t="inlineStr">
+          <t>לוח 71 | פריסה 7</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 96% | 4 חתיכות</t>
         </is>
@@ -4685,26 +5429,32 @@
       <c r="A195" s="3" t="n">
         <v>71</v>
       </c>
-      <c r="B195" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C195" s="3" t="inlineStr">
+      <c r="B195" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C195" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #5 ח2/6</t>
         </is>
       </c>
-      <c r="D195" s="3" t="n">
+      <c r="F195" s="3" t="n">
         <v>240</v>
       </c>
-      <c r="E195" s="3" t="n">
+      <c r="G195" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F195" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G195" s="3" t="n">
+      <c r="H195" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I195" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4712,26 +5462,32 @@
       <c r="A196" s="3" t="n">
         <v>71</v>
       </c>
-      <c r="B196" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C196" s="3" t="inlineStr">
+      <c r="B196" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C196" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #5 ח4/6</t>
         </is>
-      </c>
-      <c r="D196" s="3" t="n">
-        <v>240</v>
-      </c>
-      <c r="E196" s="3" t="n">
-        <v>3000</v>
       </c>
       <c r="F196" s="3" t="n">
         <v>240</v>
       </c>
       <c r="G196" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H196" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="I196" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4739,26 +5495,32 @@
       <c r="A197" s="3" t="n">
         <v>71</v>
       </c>
-      <c r="B197" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C197" s="3" t="inlineStr">
+      <c r="B197" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C197" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D197" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #6 ח2/6</t>
         </is>
       </c>
-      <c r="D197" s="3" t="n">
+      <c r="F197" s="3" t="n">
         <v>240</v>
       </c>
-      <c r="E197" s="3" t="n">
+      <c r="G197" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F197" s="3" t="n">
+      <c r="H197" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="G197" s="3" t="n">
+      <c r="I197" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4766,36 +5528,42 @@
       <c r="A198" s="3" t="n">
         <v>71</v>
       </c>
-      <c r="B198" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C198" s="3" t="inlineStr">
+      <c r="B198" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C198" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D198" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E198" s="3" t="inlineStr">
         <is>
           <t>6160×1240 #6 ח4/6</t>
         </is>
       </c>
-      <c r="D198" s="3" t="n">
+      <c r="F198" s="3" t="n">
         <v>240</v>
       </c>
-      <c r="E198" s="3" t="n">
+      <c r="G198" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F198" s="3" t="n">
+      <c r="H198" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="G198" s="3" t="n">
+      <c r="I198" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>לוח 72</t>
-        </is>
-      </c>
-      <c r="C199" s="2" t="inlineStr">
+          <t>לוח 72 | פריסה 14</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 58% | 6 חתיכות</t>
         </is>
@@ -4805,26 +5573,32 @@
       <c r="A200" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="B200" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C200" s="3" t="inlineStr">
+      <c r="B200" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C200" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="inlineStr">
         <is>
           <t>1240×1200 #1 ח2/2</t>
         </is>
       </c>
-      <c r="D200" s="3" t="n">
+      <c r="F200" s="3" t="n">
         <v>240</v>
       </c>
-      <c r="E200" s="3" t="n">
+      <c r="G200" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="F200" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G200" s="3" t="n">
+      <c r="H200" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I200" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4832,26 +5606,32 @@
       <c r="A201" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="B201" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C201" s="3" t="inlineStr">
+      <c r="B201" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C201" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
         <is>
           <t>1240×1200 #2 ח2/2</t>
         </is>
-      </c>
-      <c r="D201" s="3" t="n">
-        <v>240</v>
-      </c>
-      <c r="E201" s="3" t="n">
-        <v>1200</v>
       </c>
       <c r="F201" s="3" t="n">
         <v>240</v>
       </c>
       <c r="G201" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H201" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="I201" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4859,26 +5639,32 @@
       <c r="A202" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="B202" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C202" s="3" t="inlineStr">
+      <c r="B202" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C202" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="inlineStr">
         <is>
           <t>1240×1200 #3 ח2/2</t>
         </is>
       </c>
-      <c r="D202" s="3" t="n">
+      <c r="F202" s="3" t="n">
         <v>240</v>
       </c>
-      <c r="E202" s="3" t="n">
+      <c r="G202" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="F202" s="3" t="n">
+      <c r="H202" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="G202" s="3" t="n">
+      <c r="I202" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4886,26 +5672,32 @@
       <c r="A203" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="B203" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C203" s="3" t="inlineStr">
+      <c r="B203" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C203" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="inlineStr">
         <is>
           <t>1240×1200 #4 ח2/2</t>
         </is>
       </c>
-      <c r="D203" s="3" t="n">
+      <c r="F203" s="3" t="n">
         <v>240</v>
       </c>
-      <c r="E203" s="3" t="n">
+      <c r="G203" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="F203" s="3" t="n">
+      <c r="H203" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="G203" s="3" t="n">
+      <c r="I203" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4913,26 +5705,32 @@
       <c r="A204" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="B204" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C204" s="3" t="inlineStr">
+      <c r="B204" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C204" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="inlineStr">
         <is>
           <t>1240×1200 #5 ח2/2</t>
         </is>
       </c>
-      <c r="D204" s="3" t="n">
+      <c r="F204" s="3" t="n">
         <v>240</v>
       </c>
-      <c r="E204" s="3" t="n">
+      <c r="G204" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="F204" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G204" s="3" t="n">
+      <c r="H204" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I204" s="3" t="n">
         <v>1200</v>
       </c>
     </row>
@@ -4940,21 +5738,21 @@
       <c r="A205" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="B205" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="C205" s="3" t="inlineStr">
+      <c r="B205" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C205" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="inlineStr">
         <is>
           <t>1240×1200 #6 ח2/2</t>
         </is>
-      </c>
-      <c r="D205" s="3" t="n">
-        <v>240</v>
-      </c>
-      <c r="E205" s="3" t="n">
-        <v>1200</v>
       </c>
       <c r="F205" s="3" t="n">
         <v>240</v>
@@ -4962,14 +5760,20 @@
       <c r="G205" s="3" t="n">
         <v>1200</v>
       </c>
+      <c r="H205" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="I205" s="3" t="n">
+        <v>1200</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>לוח 73</t>
-        </is>
-      </c>
-      <c r="C206" s="2" t="inlineStr">
+          <t>לוח 73 | פריסה 15</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
         <is>
           <t>1220x2440 | ניצול 76% | 3 חתיכות</t>
         </is>
@@ -4979,26 +5783,32 @@
       <c r="A207" s="3" t="n">
         <v>73</v>
       </c>
-      <c r="B207" s="3" t="inlineStr">
+      <c r="B207" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C207" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
         <is>
           <t>1220x2440</t>
         </is>
       </c>
-      <c r="C207" s="3" t="inlineStr">
+      <c r="E207" s="3" t="inlineStr">
         <is>
           <t>940×800 #1</t>
         </is>
       </c>
-      <c r="D207" s="3" t="n">
+      <c r="F207" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="E207" s="3" t="n">
+      <c r="G207" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="F207" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G207" s="3" t="n">
+      <c r="H207" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I207" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5006,26 +5816,32 @@
       <c r="A208" s="3" t="n">
         <v>73</v>
       </c>
-      <c r="B208" s="3" t="inlineStr">
+      <c r="B208" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C208" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
         <is>
           <t>1220x2440</t>
         </is>
       </c>
-      <c r="C208" s="3" t="inlineStr">
+      <c r="E208" s="3" t="inlineStr">
         <is>
           <t>940×800 #2</t>
         </is>
       </c>
-      <c r="D208" s="3" t="n">
+      <c r="F208" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="E208" s="3" t="n">
+      <c r="G208" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="F208" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G208" s="3" t="n">
+      <c r="H208" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I208" s="3" t="n">
         <v>800</v>
       </c>
     </row>
@@ -5033,36 +5849,42 @@
       <c r="A209" s="3" t="n">
         <v>73</v>
       </c>
-      <c r="B209" s="3" t="inlineStr">
+      <c r="B209" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C209" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D209" s="3" t="inlineStr">
         <is>
           <t>1220x2440</t>
         </is>
       </c>
-      <c r="C209" s="3" t="inlineStr">
+      <c r="E209" s="3" t="inlineStr">
         <is>
           <t>940×800 #3</t>
         </is>
       </c>
-      <c r="D209" s="3" t="n">
+      <c r="F209" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="E209" s="3" t="n">
+      <c r="G209" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="F209" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G209" s="3" t="n">
+      <c r="H209" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I209" s="3" t="n">
         <v>1600</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>לוח 74</t>
-        </is>
-      </c>
-      <c r="C210" s="2" t="inlineStr">
+          <t>לוח 74 | פריסה 15</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
         <is>
           <t>1220x2440 | ניצול 76% | 3 חתיכות</t>
         </is>
@@ -5072,26 +5894,32 @@
       <c r="A211" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="B211" s="3" t="inlineStr">
+      <c r="B211" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C211" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D211" s="3" t="inlineStr">
         <is>
           <t>1220x2440</t>
         </is>
       </c>
-      <c r="C211" s="3" t="inlineStr">
+      <c r="E211" s="3" t="inlineStr">
         <is>
           <t>940×800 #4</t>
         </is>
       </c>
-      <c r="D211" s="3" t="n">
+      <c r="F211" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="E211" s="3" t="n">
+      <c r="G211" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="F211" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G211" s="3" t="n">
+      <c r="H211" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I211" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5099,26 +5927,32 @@
       <c r="A212" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="B212" s="3" t="inlineStr">
+      <c r="B212" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C212" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
         <is>
           <t>1220x2440</t>
         </is>
       </c>
-      <c r="C212" s="3" t="inlineStr">
+      <c r="E212" s="3" t="inlineStr">
         <is>
           <t>940×800 #5</t>
         </is>
       </c>
-      <c r="D212" s="3" t="n">
+      <c r="F212" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="E212" s="3" t="n">
+      <c r="G212" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="F212" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G212" s="3" t="n">
+      <c r="H212" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I212" s="3" t="n">
         <v>800</v>
       </c>
     </row>
@@ -5126,36 +5960,42 @@
       <c r="A213" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="B213" s="3" t="inlineStr">
+      <c r="B213" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C213" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D213" s="3" t="inlineStr">
         <is>
           <t>1220x2440</t>
         </is>
       </c>
-      <c r="C213" s="3" t="inlineStr">
+      <c r="E213" s="3" t="inlineStr">
         <is>
           <t>940×800 #6</t>
         </is>
       </c>
-      <c r="D213" s="3" t="n">
+      <c r="F213" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="E213" s="3" t="n">
+      <c r="G213" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="F213" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G213" s="3" t="n">
+      <c r="H213" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I213" s="3" t="n">
         <v>1600</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>לוח 75</t>
-        </is>
-      </c>
-      <c r="C214" s="2" t="inlineStr">
+          <t>לוח 75 | פריסה 1</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
         <is>
           <t>1500x3000 | ניצול 85% | 2 חתיכות</t>
         </is>
@@ -5165,26 +6005,32 @@
       <c r="A215" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="B215" s="3" t="inlineStr">
+      <c r="B215" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C215" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D215" s="3" t="inlineStr">
         <is>
           <t>1500x3000</t>
         </is>
       </c>
-      <c r="C215" s="3" t="inlineStr">
+      <c r="E215" s="3" t="inlineStr">
         <is>
           <t>5330×640 #1 ח1/2</t>
         </is>
       </c>
-      <c r="D215" s="3" t="n">
+      <c r="F215" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="E215" s="3" t="n">
+      <c r="G215" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F215" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G215" s="3" t="n">
+      <c r="H215" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I215" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5192,36 +6038,42 @@
       <c r="A216" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="B216" s="3" t="inlineStr">
+      <c r="B216" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C216" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D216" s="3" t="inlineStr">
         <is>
           <t>1500x3000</t>
         </is>
       </c>
-      <c r="C216" s="3" t="inlineStr">
+      <c r="E216" s="3" t="inlineStr">
         <is>
           <t>5330×640 #2 ח1/2</t>
         </is>
-      </c>
-      <c r="D216" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="E216" s="3" t="n">
-        <v>3000</v>
       </c>
       <c r="F216" s="3" t="n">
         <v>640</v>
       </c>
       <c r="G216" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H216" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="I216" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>לוח 76</t>
-        </is>
-      </c>
-      <c r="C217" s="2" t="inlineStr">
+          <t>לוח 76 | פריסה 1</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
         <is>
           <t>1500x3000 | ניצול 85% | 2 חתיכות</t>
         </is>
@@ -5231,26 +6083,32 @@
       <c r="A218" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="B218" s="3" t="inlineStr">
+      <c r="B218" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C218" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D218" s="3" t="inlineStr">
         <is>
           <t>1500x3000</t>
         </is>
       </c>
-      <c r="C218" s="3" t="inlineStr">
+      <c r="E218" s="3" t="inlineStr">
         <is>
           <t>5330×640 #3 ח1/2</t>
         </is>
       </c>
-      <c r="D218" s="3" t="n">
+      <c r="F218" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="E218" s="3" t="n">
+      <c r="G218" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F218" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G218" s="3" t="n">
+      <c r="H218" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I218" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5258,36 +6116,42 @@
       <c r="A219" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="B219" s="3" t="inlineStr">
+      <c r="B219" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C219" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D219" s="3" t="inlineStr">
         <is>
           <t>1500x3000</t>
         </is>
       </c>
-      <c r="C219" s="3" t="inlineStr">
+      <c r="E219" s="3" t="inlineStr">
         <is>
           <t>5330×640 #4 ח1/2</t>
         </is>
-      </c>
-      <c r="D219" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="E219" s="3" t="n">
-        <v>3000</v>
       </c>
       <c r="F219" s="3" t="n">
         <v>640</v>
       </c>
       <c r="G219" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H219" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="I219" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>לוח 77</t>
-        </is>
-      </c>
-      <c r="C220" s="2" t="inlineStr">
+          <t>לוח 77 | פריסה 1</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
         <is>
           <t>1500x3000 | ניצול 85% | 2 חתיכות</t>
         </is>
@@ -5297,26 +6161,32 @@
       <c r="A221" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="B221" s="3" t="inlineStr">
+      <c r="B221" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C221" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
         <is>
           <t>1500x3000</t>
         </is>
       </c>
-      <c r="C221" s="3" t="inlineStr">
+      <c r="E221" s="3" t="inlineStr">
         <is>
           <t>5330×640 #5 ח1/2</t>
         </is>
       </c>
-      <c r="D221" s="3" t="n">
+      <c r="F221" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="E221" s="3" t="n">
+      <c r="G221" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F221" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G221" s="3" t="n">
+      <c r="H221" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I221" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5324,36 +6194,42 @@
       <c r="A222" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="B222" s="3" t="inlineStr">
+      <c r="B222" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C222" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D222" s="3" t="inlineStr">
         <is>
           <t>1500x3000</t>
         </is>
       </c>
-      <c r="C222" s="3" t="inlineStr">
+      <c r="E222" s="3" t="inlineStr">
         <is>
           <t>5330×640 #6 ח1/2</t>
         </is>
-      </c>
-      <c r="D222" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="E222" s="3" t="n">
-        <v>3000</v>
       </c>
       <c r="F222" s="3" t="n">
         <v>640</v>
       </c>
       <c r="G222" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H222" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="I222" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>לוח 78</t>
-        </is>
-      </c>
-      <c r="C223" s="2" t="inlineStr">
+          <t>לוח 78 | פריסה 1</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
         <is>
           <t>1500x3000 | ניצול 85% | 2 חתיכות</t>
         </is>
@@ -5363,26 +6239,32 @@
       <c r="A224" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="B224" s="3" t="inlineStr">
+      <c r="B224" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C224" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D224" s="3" t="inlineStr">
         <is>
           <t>1500x3000</t>
         </is>
       </c>
-      <c r="C224" s="3" t="inlineStr">
+      <c r="E224" s="3" t="inlineStr">
         <is>
           <t>5330×640 #7 ח1/2</t>
         </is>
       </c>
-      <c r="D224" s="3" t="n">
+      <c r="F224" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="E224" s="3" t="n">
+      <c r="G224" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F224" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G224" s="3" t="n">
+      <c r="H224" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I224" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5390,36 +6272,42 @@
       <c r="A225" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="B225" s="3" t="inlineStr">
+      <c r="B225" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C225" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
         <is>
           <t>1500x3000</t>
         </is>
       </c>
-      <c r="C225" s="3" t="inlineStr">
+      <c r="E225" s="3" t="inlineStr">
         <is>
           <t>5330×640 #8 ח1/2</t>
         </is>
-      </c>
-      <c r="D225" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="E225" s="3" t="n">
-        <v>3000</v>
       </c>
       <c r="F225" s="3" t="n">
         <v>640</v>
       </c>
       <c r="G225" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H225" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="I225" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>לוח 79</t>
-        </is>
-      </c>
-      <c r="C226" s="2" t="inlineStr">
+          <t>לוח 79 | פריסה 1</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
         <is>
           <t>1500x3000 | ניצול 85% | 2 חתיכות</t>
         </is>
@@ -5429,26 +6317,32 @@
       <c r="A227" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="B227" s="3" t="inlineStr">
+      <c r="B227" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C227" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
         <is>
           <t>1500x3000</t>
         </is>
       </c>
-      <c r="C227" s="3" t="inlineStr">
+      <c r="E227" s="3" t="inlineStr">
         <is>
           <t>5330×640 #9 ח1/2</t>
         </is>
       </c>
-      <c r="D227" s="3" t="n">
+      <c r="F227" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="E227" s="3" t="n">
+      <c r="G227" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F227" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G227" s="3" t="n">
+      <c r="H227" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I227" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5456,36 +6350,42 @@
       <c r="A228" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="B228" s="3" t="inlineStr">
+      <c r="B228" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C228" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D228" s="3" t="inlineStr">
         <is>
           <t>1500x3000</t>
         </is>
       </c>
-      <c r="C228" s="3" t="inlineStr">
+      <c r="E228" s="3" t="inlineStr">
         <is>
           <t>5330×640 #10 ח1/2</t>
         </is>
-      </c>
-      <c r="D228" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="E228" s="3" t="n">
-        <v>3000</v>
       </c>
       <c r="F228" s="3" t="n">
         <v>640</v>
       </c>
       <c r="G228" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H228" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="I228" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>לוח 80</t>
-        </is>
-      </c>
-      <c r="C229" s="2" t="inlineStr">
+          <t>לוח 80 | פריסה 1</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
         <is>
           <t>1500x3000 | ניצול 85% | 2 חתיכות</t>
         </is>
@@ -5495,26 +6395,32 @@
       <c r="A230" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="B230" s="3" t="inlineStr">
+      <c r="B230" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C230" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D230" s="3" t="inlineStr">
         <is>
           <t>1500x3000</t>
         </is>
       </c>
-      <c r="C230" s="3" t="inlineStr">
+      <c r="E230" s="3" t="inlineStr">
         <is>
           <t>5330×640 #11 ח1/2</t>
         </is>
       </c>
-      <c r="D230" s="3" t="n">
+      <c r="F230" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="E230" s="3" t="n">
+      <c r="G230" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F230" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G230" s="3" t="n">
+      <c r="H230" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I230" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5522,36 +6428,42 @@
       <c r="A231" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="B231" s="3" t="inlineStr">
+      <c r="B231" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C231" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
         <is>
           <t>1500x3000</t>
         </is>
       </c>
-      <c r="C231" s="3" t="inlineStr">
+      <c r="E231" s="3" t="inlineStr">
         <is>
           <t>5330×640 #12 ח1/2</t>
         </is>
-      </c>
-      <c r="D231" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="E231" s="3" t="n">
-        <v>3000</v>
       </c>
       <c r="F231" s="3" t="n">
         <v>640</v>
       </c>
       <c r="G231" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H231" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="I231" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>לוח 81</t>
-        </is>
-      </c>
-      <c r="C232" s="2" t="inlineStr">
+          <t>לוח 81 | פריסה 2</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
         <is>
           <t>1500x3000 | ניצול 66% | 2 חתיכות</t>
         </is>
@@ -5561,26 +6473,32 @@
       <c r="A233" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="B233" s="3" t="inlineStr">
+      <c r="B233" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C233" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D233" s="3" t="inlineStr">
         <is>
           <t>1500x3000</t>
         </is>
       </c>
-      <c r="C233" s="3" t="inlineStr">
+      <c r="E233" s="3" t="inlineStr">
         <is>
           <t>5330×640 #1 ח2/2</t>
         </is>
       </c>
-      <c r="D233" s="3" t="n">
+      <c r="F233" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="E233" s="3" t="n">
+      <c r="G233" s="3" t="n">
         <v>2330</v>
       </c>
-      <c r="F233" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G233" s="3" t="n">
+      <c r="H233" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I233" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5588,36 +6506,42 @@
       <c r="A234" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="B234" s="3" t="inlineStr">
+      <c r="B234" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C234" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D234" s="3" t="inlineStr">
         <is>
           <t>1500x3000</t>
         </is>
       </c>
-      <c r="C234" s="3" t="inlineStr">
+      <c r="E234" s="3" t="inlineStr">
         <is>
           <t>5330×640 #2 ח2/2</t>
         </is>
-      </c>
-      <c r="D234" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="E234" s="3" t="n">
-        <v>2330</v>
       </c>
       <c r="F234" s="3" t="n">
         <v>640</v>
       </c>
       <c r="G234" s="3" t="n">
+        <v>2330</v>
+      </c>
+      <c r="H234" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="I234" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>לוח 82</t>
-        </is>
-      </c>
-      <c r="C235" s="2" t="inlineStr">
+          <t>לוח 82 | פריסה 2</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
         <is>
           <t>1500x3000 | ניצול 66% | 2 חתיכות</t>
         </is>
@@ -5627,26 +6551,32 @@
       <c r="A236" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="B236" s="3" t="inlineStr">
+      <c r="B236" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C236" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D236" s="3" t="inlineStr">
         <is>
           <t>1500x3000</t>
         </is>
       </c>
-      <c r="C236" s="3" t="inlineStr">
+      <c r="E236" s="3" t="inlineStr">
         <is>
           <t>5330×640 #3 ח2/2</t>
         </is>
       </c>
-      <c r="D236" s="3" t="n">
+      <c r="F236" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="E236" s="3" t="n">
+      <c r="G236" s="3" t="n">
         <v>2330</v>
       </c>
-      <c r="F236" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G236" s="3" t="n">
+      <c r="H236" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I236" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5654,36 +6584,42 @@
       <c r="A237" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="B237" s="3" t="inlineStr">
+      <c r="B237" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C237" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D237" s="3" t="inlineStr">
         <is>
           <t>1500x3000</t>
         </is>
       </c>
-      <c r="C237" s="3" t="inlineStr">
+      <c r="E237" s="3" t="inlineStr">
         <is>
           <t>5330×640 #4 ח2/2</t>
         </is>
-      </c>
-      <c r="D237" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="E237" s="3" t="n">
-        <v>2330</v>
       </c>
       <c r="F237" s="3" t="n">
         <v>640</v>
       </c>
       <c r="G237" s="3" t="n">
+        <v>2330</v>
+      </c>
+      <c r="H237" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="I237" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>לוח 83</t>
-        </is>
-      </c>
-      <c r="C238" s="2" t="inlineStr">
+          <t>לוח 83 | פריסה 2</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
         <is>
           <t>1500x3000 | ניצול 66% | 2 חתיכות</t>
         </is>
@@ -5693,26 +6629,32 @@
       <c r="A239" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="B239" s="3" t="inlineStr">
+      <c r="B239" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C239" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
         <is>
           <t>1500x3000</t>
         </is>
       </c>
-      <c r="C239" s="3" t="inlineStr">
+      <c r="E239" s="3" t="inlineStr">
         <is>
           <t>5330×640 #5 ח2/2</t>
         </is>
       </c>
-      <c r="D239" s="3" t="n">
+      <c r="F239" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="E239" s="3" t="n">
+      <c r="G239" s="3" t="n">
         <v>2330</v>
       </c>
-      <c r="F239" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G239" s="3" t="n">
+      <c r="H239" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I239" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5720,36 +6662,42 @@
       <c r="A240" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="B240" s="3" t="inlineStr">
+      <c r="B240" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C240" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D240" s="3" t="inlineStr">
         <is>
           <t>1500x3000</t>
         </is>
       </c>
-      <c r="C240" s="3" t="inlineStr">
+      <c r="E240" s="3" t="inlineStr">
         <is>
           <t>5330×640 #6 ח2/2</t>
         </is>
-      </c>
-      <c r="D240" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="E240" s="3" t="n">
-        <v>2330</v>
       </c>
       <c r="F240" s="3" t="n">
         <v>640</v>
       </c>
       <c r="G240" s="3" t="n">
+        <v>2330</v>
+      </c>
+      <c r="H240" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="I240" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>לוח 84</t>
-        </is>
-      </c>
-      <c r="C241" s="2" t="inlineStr">
+          <t>לוח 84 | פריסה 2</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
         <is>
           <t>1500x3000 | ניצול 66% | 2 חתיכות</t>
         </is>
@@ -5759,26 +6707,32 @@
       <c r="A242" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="B242" s="3" t="inlineStr">
+      <c r="B242" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C242" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D242" s="3" t="inlineStr">
         <is>
           <t>1500x3000</t>
         </is>
       </c>
-      <c r="C242" s="3" t="inlineStr">
+      <c r="E242" s="3" t="inlineStr">
         <is>
           <t>5330×640 #7 ח2/2</t>
         </is>
       </c>
-      <c r="D242" s="3" t="n">
+      <c r="F242" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="E242" s="3" t="n">
+      <c r="G242" s="3" t="n">
         <v>2330</v>
       </c>
-      <c r="F242" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G242" s="3" t="n">
+      <c r="H242" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I242" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5786,36 +6740,42 @@
       <c r="A243" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="B243" s="3" t="inlineStr">
+      <c r="B243" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C243" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D243" s="3" t="inlineStr">
         <is>
           <t>1500x3000</t>
         </is>
       </c>
-      <c r="C243" s="3" t="inlineStr">
+      <c r="E243" s="3" t="inlineStr">
         <is>
           <t>5330×640 #8 ח2/2</t>
         </is>
-      </c>
-      <c r="D243" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="E243" s="3" t="n">
-        <v>2330</v>
       </c>
       <c r="F243" s="3" t="n">
         <v>640</v>
       </c>
       <c r="G243" s="3" t="n">
+        <v>2330</v>
+      </c>
+      <c r="H243" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="I243" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>לוח 85</t>
-        </is>
-      </c>
-      <c r="C244" s="2" t="inlineStr">
+          <t>לוח 85 | פריסה 2</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
         <is>
           <t>1500x3000 | ניצול 66% | 2 חתיכות</t>
         </is>
@@ -5825,26 +6785,32 @@
       <c r="A245" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="B245" s="3" t="inlineStr">
+      <c r="B245" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C245" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D245" s="3" t="inlineStr">
         <is>
           <t>1500x3000</t>
         </is>
       </c>
-      <c r="C245" s="3" t="inlineStr">
+      <c r="E245" s="3" t="inlineStr">
         <is>
           <t>5330×640 #9 ח2/2</t>
         </is>
       </c>
-      <c r="D245" s="3" t="n">
+      <c r="F245" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="E245" s="3" t="n">
+      <c r="G245" s="3" t="n">
         <v>2330</v>
       </c>
-      <c r="F245" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G245" s="3" t="n">
+      <c r="H245" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I245" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5852,36 +6818,42 @@
       <c r="A246" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="B246" s="3" t="inlineStr">
+      <c r="B246" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C246" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D246" s="3" t="inlineStr">
         <is>
           <t>1500x3000</t>
         </is>
       </c>
-      <c r="C246" s="3" t="inlineStr">
+      <c r="E246" s="3" t="inlineStr">
         <is>
           <t>5330×640 #10 ח2/2</t>
         </is>
-      </c>
-      <c r="D246" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="E246" s="3" t="n">
-        <v>2330</v>
       </c>
       <c r="F246" s="3" t="n">
         <v>640</v>
       </c>
       <c r="G246" s="3" t="n">
+        <v>2330</v>
+      </c>
+      <c r="H246" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="I246" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>לוח 86</t>
-        </is>
-      </c>
-      <c r="C247" s="2" t="inlineStr">
+          <t>לוח 86 | פריסה 2</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
         <is>
           <t>1500x3000 | ניצול 66% | 2 חתיכות</t>
         </is>
@@ -5891,26 +6863,32 @@
       <c r="A248" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="B248" s="3" t="inlineStr">
+      <c r="B248" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C248" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D248" s="3" t="inlineStr">
         <is>
           <t>1500x3000</t>
         </is>
       </c>
-      <c r="C248" s="3" t="inlineStr">
+      <c r="E248" s="3" t="inlineStr">
         <is>
           <t>5330×640 #11 ח2/2</t>
         </is>
       </c>
-      <c r="D248" s="3" t="n">
+      <c r="F248" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="E248" s="3" t="n">
+      <c r="G248" s="3" t="n">
         <v>2330</v>
       </c>
-      <c r="F248" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G248" s="3" t="n">
+      <c r="H248" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I248" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5918,203 +6896,209 @@
       <c r="A249" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="B249" s="3" t="inlineStr">
+      <c r="B249" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C249" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
         <is>
           <t>1500x3000</t>
         </is>
       </c>
-      <c r="C249" s="3" t="inlineStr">
+      <c r="E249" s="3" t="inlineStr">
         <is>
           <t>5330×640 #12 ח2/2</t>
         </is>
-      </c>
-      <c r="D249" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="E249" s="3" t="n">
-        <v>2330</v>
       </c>
       <c r="F249" s="3" t="n">
         <v>640</v>
       </c>
       <c r="G249" s="3" t="n">
+        <v>2330</v>
+      </c>
+      <c r="H249" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="I249" s="3" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="172">
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="C166:G166"/>
-    <mergeCell ref="A98:B98"/>
-    <mergeCell ref="A226:B226"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="A107:B107"/>
-    <mergeCell ref="A178:B178"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="A88:B88"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A241:B241"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="C109:G109"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="C129:G129"/>
-    <mergeCell ref="A214:B214"/>
-    <mergeCell ref="C139:G139"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C244:G244"/>
-    <mergeCell ref="C241:G241"/>
-    <mergeCell ref="C123:G123"/>
-    <mergeCell ref="C194:G194"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="C181:G181"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A206:B206"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A117:B117"/>
-    <mergeCell ref="A111:B111"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="C189:G189"/>
-    <mergeCell ref="C220:G220"/>
-    <mergeCell ref="C229:G229"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A232:B232"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="A142:B142"/>
-    <mergeCell ref="C151:G151"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="C206:G206"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C113:G113"/>
-    <mergeCell ref="C103:G103"/>
-    <mergeCell ref="A217:B217"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C133:G133"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C127:G127"/>
-    <mergeCell ref="A136:B136"/>
-    <mergeCell ref="C142:G142"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="A105:B105"/>
-    <mergeCell ref="A145:B145"/>
-    <mergeCell ref="C247:G247"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A139:B139"/>
-    <mergeCell ref="A210:B210"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="A129:B129"/>
-    <mergeCell ref="A194:B194"/>
-    <mergeCell ref="C178:G178"/>
-    <mergeCell ref="A181:B181"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="A184:B184"/>
-    <mergeCell ref="A131:B131"/>
-    <mergeCell ref="A244:B244"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C125:G125"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A115:B115"/>
-    <mergeCell ref="C161:G161"/>
-    <mergeCell ref="A93:B93"/>
-    <mergeCell ref="C217:G217"/>
-    <mergeCell ref="C131:G131"/>
-    <mergeCell ref="A229:B229"/>
-    <mergeCell ref="C145:G145"/>
-    <mergeCell ref="A166:B166"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="C156:G156"/>
-    <mergeCell ref="A119:B119"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="C121:G121"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="A133:B133"/>
-    <mergeCell ref="C117:G117"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C214:G214"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C223:G223"/>
-    <mergeCell ref="C238:G238"/>
-    <mergeCell ref="C232:G232"/>
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="C115:G115"/>
-    <mergeCell ref="A235:B235"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A247:B247"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A156:B156"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C199:G199"/>
-    <mergeCell ref="A220:B220"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C136:G136"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A148:B148"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="C210:G210"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C235:G235"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="A123:B123"/>
-    <mergeCell ref="C107:G107"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="C184:G184"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C226:G226"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A189:B189"/>
-    <mergeCell ref="A223:B223"/>
-    <mergeCell ref="A238:B238"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C148:G148"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A86:B86"/>
-    <mergeCell ref="A151:B151"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C119:G119"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="A125:B125"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A199:B199"/>
-    <mergeCell ref="A121:B121"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="A161:B161"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A127:B127"/>
-    <mergeCell ref="C111:G111"/>
-    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A80:C80"/>
+    <mergeCell ref="D32:I32"/>
+    <mergeCell ref="D145:I145"/>
+    <mergeCell ref="D41:I41"/>
+    <mergeCell ref="A136:C136"/>
+    <mergeCell ref="A105:C105"/>
+    <mergeCell ref="D16:I16"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A113:C113"/>
+    <mergeCell ref="A210:C210"/>
+    <mergeCell ref="A235:C235"/>
+    <mergeCell ref="D156:I156"/>
+    <mergeCell ref="D214:I214"/>
+    <mergeCell ref="A247:C247"/>
+    <mergeCell ref="A194:C194"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="A181:C181"/>
+    <mergeCell ref="D220:I220"/>
+    <mergeCell ref="D121:I121"/>
+    <mergeCell ref="A184:C184"/>
+    <mergeCell ref="D74:I74"/>
+    <mergeCell ref="A156:C156"/>
+    <mergeCell ref="D68:I68"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="D82:I82"/>
+    <mergeCell ref="D117:I117"/>
+    <mergeCell ref="A93:C93"/>
+    <mergeCell ref="D123:I123"/>
+    <mergeCell ref="A220:C220"/>
+    <mergeCell ref="A229:C229"/>
+    <mergeCell ref="D20:I20"/>
+    <mergeCell ref="A148:C148"/>
+    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="D109:I109"/>
+    <mergeCell ref="D84:I84"/>
+    <mergeCell ref="D22:I22"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A119:C119"/>
+    <mergeCell ref="D229:I229"/>
+    <mergeCell ref="D111:I111"/>
+    <mergeCell ref="D6:I6"/>
+    <mergeCell ref="D86:I86"/>
+    <mergeCell ref="A66:C66"/>
+    <mergeCell ref="A133:C133"/>
+    <mergeCell ref="D136:I136"/>
+    <mergeCell ref="D70:I70"/>
+    <mergeCell ref="A238:C238"/>
+    <mergeCell ref="D210:I210"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D72:I72"/>
+    <mergeCell ref="D78:I78"/>
+    <mergeCell ref="D4:I4"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="D56:I56"/>
+    <mergeCell ref="D62:I62"/>
+    <mergeCell ref="D184:I184"/>
+    <mergeCell ref="D58:I58"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="D8:I8"/>
+    <mergeCell ref="D64:I64"/>
+    <mergeCell ref="A121:C121"/>
+    <mergeCell ref="A161:C161"/>
+    <mergeCell ref="D226:I226"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="D113:I113"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="D148:I148"/>
+    <mergeCell ref="D241:I241"/>
+    <mergeCell ref="D35:I35"/>
+    <mergeCell ref="D44:I44"/>
+    <mergeCell ref="D115:I115"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A226:C226"/>
+    <mergeCell ref="D178:I178"/>
+    <mergeCell ref="A82:C82"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A241:C241"/>
+    <mergeCell ref="A123:C123"/>
+    <mergeCell ref="D131:I131"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="D189:I189"/>
+    <mergeCell ref="D151:I151"/>
+    <mergeCell ref="A84:C84"/>
+    <mergeCell ref="A214:C214"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A189:C189"/>
+    <mergeCell ref="A223:C223"/>
+    <mergeCell ref="D166:I166"/>
+    <mergeCell ref="D48:I48"/>
+    <mergeCell ref="D206:I206"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A86:C86"/>
+    <mergeCell ref="D238:I238"/>
+    <mergeCell ref="D125:I125"/>
+    <mergeCell ref="A151:C151"/>
+    <mergeCell ref="D103:I103"/>
+    <mergeCell ref="D235:I235"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A206:C206"/>
+    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="D127:I127"/>
+    <mergeCell ref="D161:I161"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A125:C125"/>
+    <mergeCell ref="D232:I232"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A199:C199"/>
+    <mergeCell ref="D142:I142"/>
+    <mergeCell ref="D24:I24"/>
+    <mergeCell ref="D38:I38"/>
+    <mergeCell ref="D98:I98"/>
+    <mergeCell ref="D129:I129"/>
+    <mergeCell ref="A127:C127"/>
+    <mergeCell ref="D88:I88"/>
+    <mergeCell ref="D26:I26"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="D247:I247"/>
+    <mergeCell ref="A98:C98"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A178:C178"/>
+    <mergeCell ref="D217:I217"/>
+    <mergeCell ref="A88:C88"/>
+    <mergeCell ref="A70:C70"/>
+    <mergeCell ref="D105:I105"/>
+    <mergeCell ref="D139:I139"/>
+    <mergeCell ref="D52:I52"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="A217:C217"/>
+    <mergeCell ref="D194:I194"/>
+    <mergeCell ref="D76:I76"/>
+    <mergeCell ref="D107:I107"/>
+    <mergeCell ref="A74:C74"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A145:C145"/>
+    <mergeCell ref="A139:C139"/>
+    <mergeCell ref="D66:I66"/>
+    <mergeCell ref="D244:I244"/>
+    <mergeCell ref="A129:C129"/>
+    <mergeCell ref="A76:C76"/>
+    <mergeCell ref="D181:I181"/>
+    <mergeCell ref="D93:I93"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A131:C131"/>
+    <mergeCell ref="A244:C244"/>
+    <mergeCell ref="D12:I12"/>
+    <mergeCell ref="A109:C109"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="D223:I223"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A115:C115"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="D133:I133"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="D29:I29"/>
+    <mergeCell ref="A117:C117"/>
+    <mergeCell ref="A111:C111"/>
+    <mergeCell ref="D54:I54"/>
+    <mergeCell ref="A166:C166"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A232:C232"/>
+    <mergeCell ref="A142:C142"/>
+    <mergeCell ref="D119:I119"/>
+    <mergeCell ref="A103:C103"/>
+    <mergeCell ref="D199:I199"/>
+    <mergeCell ref="D80:I80"/>
+    <mergeCell ref="A78:C78"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cut_plan.xlsx
+++ b/cut_plan.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I249"/>
+  <dimension ref="A1:I225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>לוח 1 | פריסה 16</t>
+          <t>לוח 1 | פריסה 14</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -564,7 +564,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>1</v>
@@ -595,7 +595,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>לוח 2 | פריסה 16</t>
+          <t>לוח 2 | פריסה 14</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>1</v>
@@ -640,7 +640,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>לוח 3 | פריסה 16</t>
+          <t>לוח 3 | פריסה 14</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -654,7 +654,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>1</v>
@@ -685,7 +685,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>לוח 4 | פריסה 16</t>
+          <t>לוח 4 | פריסה 14</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>1</v>
@@ -730,7 +730,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>לוח 5 | פריסה 16</t>
+          <t>לוח 5 | פריסה 14</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -744,7 +744,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>1</v>
@@ -775,7 +775,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>לוח 6 | פריסה 16</t>
+          <t>לוח 6 | פריסה 14</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -789,7 +789,7 @@
         <v>6</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>1</v>
@@ -820,7 +820,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>לוח 7 | פריסה 16</t>
+          <t>לוח 7 | פריסה 14</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
         <v>7</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>1</v>
@@ -865,7 +865,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>לוח 8 | פריסה 16</t>
+          <t>לוח 8 | פריסה 14</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
         <v>8</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>1</v>
@@ -910,7 +910,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>לוח 9 | פריסה 16</t>
+          <t>לוח 9 | פריסה 14</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -924,7 +924,7 @@
         <v>9</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C19" s="3" t="n">
         <v>1</v>
@@ -955,7 +955,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>לוח 10 | פריסה 16</t>
+          <t>לוח 10 | פריסה 14</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -969,7 +969,7 @@
         <v>10</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>1</v>
@@ -1000,7 +1000,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>לוח 11 | פריסה 16</t>
+          <t>לוח 11 | פריסה 14</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
         <v>11</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>1</v>
@@ -1045,7 +1045,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>לוח 12 | פריסה 16</t>
+          <t>לוח 12 | פריסה 14</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1059,7 +1059,7 @@
         <v>12</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>1</v>
@@ -1090,7 +1090,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>לוח 13 | פריסה 17</t>
+          <t>לוח 13 | פריסה 15</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
         <v>13</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>1</v>
@@ -1137,7 +1137,7 @@
         <v>13</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>2</v>
@@ -1168,7 +1168,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>לוח 14 | פריסה 17</t>
+          <t>לוח 14 | פריסה 15</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>1</v>
@@ -1215,7 +1215,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>2</v>
@@ -1246,7 +1246,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>לוח 15 | פריסה 17</t>
+          <t>לוח 15 | פריסה 15</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
         <v>15</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C33" s="3" t="n">
         <v>1</v>
@@ -1293,7 +1293,7 @@
         <v>15</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>2</v>
@@ -1324,7 +1324,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>לוח 16 | פריסה 17</t>
+          <t>לוח 16 | פריסה 15</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1338,7 +1338,7 @@
         <v>16</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>1</v>
@@ -1371,7 +1371,7 @@
         <v>16</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C37" s="3" t="n">
         <v>2</v>
@@ -1402,7 +1402,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>לוח 17 | פריסה 17</t>
+          <t>לוח 17 | פריסה 15</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1416,7 +1416,7 @@
         <v>17</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C39" s="3" t="n">
         <v>1</v>
@@ -1449,7 +1449,7 @@
         <v>17</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>2</v>
@@ -1480,7 +1480,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>לוח 18 | פריסה 17</t>
+          <t>לוח 18 | פריסה 15</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
         <v>18</v>
       </c>
       <c r="B42" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C42" s="3" t="n">
         <v>1</v>
@@ -1527,7 +1527,7 @@
         <v>18</v>
       </c>
       <c r="B43" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C43" s="3" t="n">
         <v>2</v>
@@ -1558,12 +1558,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>לוח 19 | פריסה 18</t>
+          <t>לוח 19 | פריסה 16</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>1000x2000 | ניצול 75% | 3 חתיכות</t>
+          <t>1000x2000 | ניצול 75% | 2 חתיכות</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
         <v>19</v>
       </c>
       <c r="B45" s="3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C45" s="3" t="n">
         <v>1</v>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>780×640 #7</t>
+          <t>940×800 #1</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>780</v>
+        <v>940</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>640</v>
+        <v>800</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>0</v>
@@ -1605,7 +1605,7 @@
         <v>19</v>
       </c>
       <c r="B46" s="3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C46" s="3" t="n">
         <v>2</v>
@@ -1617,65 +1617,65 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>780×640 #8</t>
+          <t>940×800 #2</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>780</v>
+        <v>940</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>640</v>
+        <v>800</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>640</v>
+        <v>800</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="B47" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="C47" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>לוח 20 | פריסה 16</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>1000x2000 | ניצול 75% | 2 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>1000x2000</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>780×640 #9</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>780</v>
-      </c>
-      <c r="G47" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="H47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3" t="n">
-        <v>1280</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>לוח 20 | פריסה 18</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>1000x2000 | ניצול 75% | 3 חתיכות</t>
-        </is>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>940×800 #3</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1683,10 +1683,10 @@
         <v>20</v>
       </c>
       <c r="B49" s="3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
@@ -1695,64 +1695,43 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>780×640 #10</t>
+          <t>940×800 #4</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>780</v>
+        <v>940</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>640</v>
+        <v>800</v>
       </c>
       <c r="H49" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="B50" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="C50" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>1000x2000</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>780×640 #11</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="n">
-        <v>780</v>
-      </c>
-      <c r="G50" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="H50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="3" t="n">
-        <v>640</v>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>לוח 21 | פריסה 16</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>1000x2000 | ניצול 75% | 2 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B51" s="3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
@@ -1761,77 +1740,98 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>780×640 #12</t>
+          <t>940×800 #5</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>1000x2000</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>940×800 #6</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="H52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>לוח 22 | פריסה 17</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>1000x2000 | ניצול 75% | 3 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>1000x2000</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>780×640 #7</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="n">
         <v>780</v>
       </c>
-      <c r="G51" s="3" t="n">
+      <c r="G54" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="H51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="3" t="n">
-        <v>1280</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>לוח 21 | פריסה 4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="B53" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C53" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>6160×1240 #1 ח1/6</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G53" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>לוח 22 | פריסה 4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
-        </is>
+      <c r="H54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1839,460 +1839,502 @@
         <v>22</v>
       </c>
       <c r="B55" s="3" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>1000x3000</t>
+          <t>1000x2000</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>6160×1240 #1 ח3/6</t>
+          <t>780×640 #8</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>1000</v>
+        <v>780</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>3000</v>
+        <v>640</v>
       </c>
       <c r="H55" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>לוח 23 | פריסה 4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
-        </is>
+      <c r="A56" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>1000x2000</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>780×640 #9</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>780</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="3" t="n">
+        <v>1280</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>לוח 23 | פריסה 17</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>1000x2000 | ניצול 75% | 3 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="B57" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C57" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>6160×1240 #2 ח1/6</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G57" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>לוח 24 | פריסה 4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>1000x2000</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>780×640 #10</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>780</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>1000x2000</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>780×640 #11</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>780</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="H59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3" t="n">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>1000x2000</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>780×640 #12</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>780</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>לוח 24 | פריסה 7</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="B59" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C59" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="B62" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>1000x3000</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>6160×1240 #2 ח3/6</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="n">
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>6160×1200 #1 ח1/6</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="G59" s="3" t="n">
+      <c r="G62" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="H59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>לוח 25 | פריסה 4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="H62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>לוח 25 | פריסה 7</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="3" t="n">
+    <row r="64">
+      <c r="A64" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="B61" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C61" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="B64" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>1000x3000</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>6160×1240 #3 ח1/6</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="n">
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>6160×1200 #1 ח3/6</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="G61" s="3" t="n">
+      <c r="G64" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="H61" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>לוח 26 | פריסה 4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="H64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>לוח 26 | פריסה 7</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="3" t="n">
+    <row r="66">
+      <c r="A66" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="B63" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C63" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="B66" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>1000x3000</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>6160×1240 #3 ח3/6</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="n">
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>6160×1200 #2 ח1/6</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="G63" s="3" t="n">
+      <c r="G66" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="H63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>לוח 27 | פריסה 4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="H66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>לוח 27 | פריסה 7</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="3" t="n">
+    <row r="68">
+      <c r="A68" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="B65" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C65" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="B68" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>1000x3000</t>
         </is>
       </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>6160×1240 #4 ח1/6</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="n">
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>6160×1200 #2 ח3/6</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="G65" s="3" t="n">
+      <c r="G68" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="H65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>לוח 28 | פריסה 4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="H68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>לוח 28 | פריסה 7</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="3" t="n">
+    <row r="70">
+      <c r="A70" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="B67" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C67" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="B70" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>1000x3000</t>
         </is>
       </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>6160×1240 #4 ח3/6</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="n">
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>6160×1200 #3 ח1/6</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="G67" s="3" t="n">
+      <c r="G70" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="H67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>לוח 29 | פריסה 4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="H70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>לוח 29 | פריסה 7</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="3" t="n">
+    <row r="72">
+      <c r="A72" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="B69" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C69" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="B72" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>1000x3000</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>6160×1240 #5 ח1/6</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="n">
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>6160×1200 #3 ח3/6</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="G69" s="3" t="n">
+      <c r="G72" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="H69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>לוח 30 | פריסה 4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="n">
+      <c r="H72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>לוח 30 | פריסה 9</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 100% | 4 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="B71" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C71" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="B74" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
         <is>
           <t>1000x3000</t>
         </is>
       </c>
-      <c r="E71" s="3" t="inlineStr">
-        <is>
-          <t>6160×1240 #5 ח3/6</t>
-        </is>
-      </c>
-      <c r="F71" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G71" s="3" t="n">
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>9060×940 #1 ח1/4</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="G74" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="H71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>לוח 31 | פריסה 4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="B73" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C73" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="inlineStr">
-        <is>
-          <t>6160×1240 #6 ח1/6</t>
-        </is>
-      </c>
-      <c r="F73" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G73" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>לוח 32 | פריסה 4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
-        </is>
+      <c r="H74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B75" s="3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
@@ -2301,43 +2343,64 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>6160×1240 #6 ח3/6</t>
+          <t>9060×940 #1 ח4/4</t>
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>3000</v>
+        <v>940</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0</v>
+        <v>940</v>
       </c>
       <c r="I75" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>לוח 33 | פריסה 5</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
-        </is>
+      <c r="A76" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>9060×940 #2 ח4/4</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="H76" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>940</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B77" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
@@ -2346,40 +2409,40 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>6160×1200 #1 ח1/6</t>
+          <t>9060×940 #3 ח4/4</t>
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>3000</v>
+        <v>940</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>0</v>
+        <v>940</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>0</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>לוח 34 | פריסה 5</t>
+          <t>לוח 31 | פריסה 9</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
+          <t>1000x3000 | ניצול 100% | 4 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B79" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C79" s="3" t="n">
         <v>1</v>
@@ -2391,11 +2454,11 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>6160×1200 #1 ח3/6</t>
+          <t>9060×940 #1 ח2/4</t>
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>1000</v>
+        <v>940</v>
       </c>
       <c r="G79" s="3" t="n">
         <v>3000</v>
@@ -2408,26 +2471,47 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>לוח 35 | פריסה 5</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
-        </is>
+      <c r="A80" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>9060×940 #4 ח4/4</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B81" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C81" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
@@ -2436,88 +2520,109 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>6160×1200 #2 ח1/6</t>
+          <t>9060×940 #5 ח4/4</t>
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="G81" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="H81" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="I81" s="3" t="n">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B82" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>9060×940 #6 ח4/4</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="H82" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="I82" s="3" t="n">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>לוח 32 | פריסה 10</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 99% | 4 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B84" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>9060×940 #1 ח3/4</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="G84" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="H81" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>לוח 36 | פריסה 5</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="B83" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C83" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="inlineStr">
-        <is>
-          <t>6160×1200 #2 ח3/6</t>
-        </is>
-      </c>
-      <c r="F83" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G83" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H83" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>לוח 37 | פריסה 5</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
-        </is>
+      <c r="H84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B85" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
@@ -2526,43 +2631,64 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>6160×1200 #3 ח1/6</t>
+          <t>9060×800 #1 ח4/4</t>
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>3000</v>
+        <v>800</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>0</v>
+        <v>940</v>
       </c>
       <c r="I85" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>לוח 38 | פריסה 5</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>1000x3000 | ניצול 100% | 1 חתיכות</t>
-        </is>
+      <c r="A86" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>9060×800 #2 ח4/4</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>800</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B87" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C87" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
@@ -2571,40 +2697,40 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>6160×1200 #3 ח3/6</t>
+          <t>9060×800 #3 ח4/4</t>
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>3000</v>
+        <v>800</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>0</v>
+        <v>940</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>לוח 39 | פריסה 8</t>
+          <t>לוח 33 | פריסה 6</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>1000x3000 | ניצול 100% | 4 חתיכות</t>
+          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B89" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C89" s="3" t="n">
         <v>1</v>
@@ -2616,7 +2742,7 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>9060×940 #1 ח1/4</t>
+          <t>9060×940 #2 ח1/4</t>
         </is>
       </c>
       <c r="F89" s="3" t="n">
@@ -2633,47 +2759,26 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="B90" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C90" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="inlineStr">
-        <is>
-          <t>9060×940 #1 ח4/4</t>
-        </is>
-      </c>
-      <c r="F90" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="G90" s="3" t="n">
-        <v>940</v>
-      </c>
-      <c r="H90" s="3" t="n">
-        <v>940</v>
-      </c>
-      <c r="I90" s="3" t="n">
-        <v>0</v>
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>לוח 34 | פריסה 6</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B91" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
@@ -2682,109 +2787,88 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>9060×940 #2 ח4/4</t>
+          <t>9060×940 #2 ח2/4</t>
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>60</v>
+        <v>940</v>
       </c>
       <c r="G91" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>לוח 35 | פריסה 6</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B93" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>9060×940 #2 ח3/4</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="n">
         <v>940</v>
       </c>
-      <c r="H91" s="3" t="n">
-        <v>940</v>
-      </c>
-      <c r="I91" s="3" t="n">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="B92" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C92" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D92" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="inlineStr">
-        <is>
-          <t>9060×940 #3 ח4/4</t>
-        </is>
-      </c>
-      <c r="F92" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="G92" s="3" t="n">
-        <v>940</v>
-      </c>
-      <c r="H92" s="3" t="n">
-        <v>940</v>
-      </c>
-      <c r="I92" s="3" t="n">
-        <v>1880</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>לוח 40 | פריסה 8</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>1000x3000 | ניצול 100% | 4 חתיכות</t>
-        </is>
+      <c r="G93" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="B94" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C94" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D94" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="inlineStr">
-        <is>
-          <t>9060×940 #1 ח2/4</t>
-        </is>
-      </c>
-      <c r="F94" s="3" t="n">
-        <v>940</v>
-      </c>
-      <c r="G94" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H94" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3" t="n">
-        <v>0</v>
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>לוח 36 | פריסה 6</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B95" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C95" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
@@ -2793,64 +2877,43 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>9060×940 #4 ח4/4</t>
+          <t>9060×940 #3 ח1/4</t>
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>60</v>
+        <v>940</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>940</v>
+        <v>3000</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>940</v>
+        <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="B96" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C96" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D96" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="inlineStr">
-        <is>
-          <t>9060×940 #5 ח4/4</t>
-        </is>
-      </c>
-      <c r="F96" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="G96" s="3" t="n">
-        <v>940</v>
-      </c>
-      <c r="H96" s="3" t="n">
-        <v>940</v>
-      </c>
-      <c r="I96" s="3" t="n">
-        <v>940</v>
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>לוח 37 | פריסה 6</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B97" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C97" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
@@ -2859,40 +2922,40 @@
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>9060×940 #6 ח4/4</t>
+          <t>9060×940 #3 ח2/4</t>
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>60</v>
+        <v>940</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>940</v>
+        <v>3000</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>940</v>
+        <v>0</v>
       </c>
       <c r="I97" s="3" t="n">
-        <v>1880</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>לוח 41 | פריסה 11</t>
+          <t>לוח 38 | פריסה 6</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>1000x3000 | ניצול 99% | 4 חתיכות</t>
+          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B99" s="3" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>1</v>
@@ -2904,7 +2967,7 @@
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>9060×940 #1 ח3/4</t>
+          <t>9060×940 #3 ח3/4</t>
         </is>
       </c>
       <c r="F99" s="3" t="n">
@@ -2921,485 +2984,464 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="B100" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="C100" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D100" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E100" s="3" t="inlineStr">
-        <is>
-          <t>9060×800 #1 ח4/4</t>
-        </is>
-      </c>
-      <c r="F100" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="G100" s="3" t="n">
-        <v>800</v>
-      </c>
-      <c r="H100" s="3" t="n">
-        <v>940</v>
-      </c>
-      <c r="I100" s="3" t="n">
-        <v>0</v>
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>לוח 39 | פריסה 6</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="B101" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>9060×940 #4 ח1/4</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="G101" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>לוח 40 | פריסה 6</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="B103" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>9060×940 #4 ח2/4</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>לוח 41 | פריסה 6</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="B101" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="C101" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D101" s="3" t="inlineStr">
+      <c r="B105" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
         <is>
           <t>1000x3000</t>
         </is>
       </c>
-      <c r="E101" s="3" t="inlineStr">
-        <is>
-          <t>9060×800 #2 ח4/4</t>
-        </is>
-      </c>
-      <c r="F101" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="G101" s="3" t="n">
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>9060×940 #4 ח3/4</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>לוח 42 | פריסה 6</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="B107" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>9060×940 #5 ח1/4</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>לוח 43 | פריסה 6</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="B109" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>9060×940 #5 ח2/4</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="G109" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>לוח 44 | פריסה 6</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="B111" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>9060×940 #5 ח3/4</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>לוח 45 | פריסה 6</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="B113" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>9060×940 #6 ח1/4</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="G113" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>לוח 46 | פריסה 6</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="B115" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>9060×940 #6 ח2/4</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>לוח 47 | פריסה 6</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="B117" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>9060×940 #6 ח3/4</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>לוח 48 | פריסה 8</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 100% | 2 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="B119" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>9060×800 #1 ח1/4</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="H101" s="3" t="n">
-        <v>940</v>
-      </c>
-      <c r="I101" s="3" t="n">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="B102" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="C102" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="inlineStr">
-        <is>
-          <t>9060×800 #3 ח4/4</t>
-        </is>
-      </c>
-      <c r="F102" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="G102" s="3" t="n">
-        <v>800</v>
-      </c>
-      <c r="H102" s="3" t="n">
-        <v>940</v>
-      </c>
-      <c r="I102" s="3" t="n">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>לוח 42 | פריסה 3</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="B104" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C104" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D104" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E104" s="3" t="inlineStr">
-        <is>
-          <t>9060×940 #2 ח1/4</t>
-        </is>
-      </c>
-      <c r="F104" s="3" t="n">
-        <v>940</v>
-      </c>
-      <c r="G104" s="3" t="n">
+      <c r="G119" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="H104" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>לוח 43 | פריסה 3</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="B106" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C106" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="inlineStr">
-        <is>
-          <t>9060×940 #2 ח2/4</t>
-        </is>
-      </c>
-      <c r="F106" s="3" t="n">
-        <v>940</v>
-      </c>
-      <c r="G106" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H106" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I106" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>לוח 44 | פריסה 3</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="B108" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C108" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E108" s="3" t="inlineStr">
-        <is>
-          <t>9060×940 #2 ח3/4</t>
-        </is>
-      </c>
-      <c r="F108" s="3" t="n">
-        <v>940</v>
-      </c>
-      <c r="G108" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H108" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>לוח 45 | פריסה 3</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="B110" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C110" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="inlineStr">
-        <is>
-          <t>9060×940 #3 ח1/4</t>
-        </is>
-      </c>
-      <c r="F110" s="3" t="n">
-        <v>940</v>
-      </c>
-      <c r="G110" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H110" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I110" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>לוח 46 | פריסה 3</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="B112" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C112" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="inlineStr">
-        <is>
-          <t>9060×940 #3 ח2/4</t>
-        </is>
-      </c>
-      <c r="F112" s="3" t="n">
-        <v>940</v>
-      </c>
-      <c r="G112" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H112" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I112" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>לוח 47 | פריסה 3</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="3" t="n">
-        <v>47</v>
-      </c>
-      <c r="B114" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C114" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D114" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="inlineStr">
-        <is>
-          <t>9060×940 #3 ח3/4</t>
-        </is>
-      </c>
-      <c r="F114" s="3" t="n">
-        <v>940</v>
-      </c>
-      <c r="G114" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H114" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I114" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>לוח 48 | פריסה 3</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="B116" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C116" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D116" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E116" s="3" t="inlineStr">
-        <is>
-          <t>9060×940 #4 ח1/4</t>
-        </is>
-      </c>
-      <c r="F116" s="3" t="n">
-        <v>940</v>
-      </c>
-      <c r="G116" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H116" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I116" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>לוח 49 | פריסה 3</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
-        <is>
-          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="B118" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C118" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D118" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E118" s="3" t="inlineStr">
-        <is>
-          <t>9060×940 #4 ח2/4</t>
-        </is>
-      </c>
-      <c r="F118" s="3" t="n">
-        <v>940</v>
-      </c>
-      <c r="G118" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H118" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I118" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>לוח 50 | פריסה 3</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
-        <is>
-          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
-        </is>
+      <c r="H119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B120" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
@@ -3408,17 +3450,17 @@
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>9060×940 #4 ח3/4</t>
+          <t>6160×1200 #1 ח2/6</t>
         </is>
       </c>
       <c r="F120" s="3" t="n">
-        <v>940</v>
+        <v>200</v>
       </c>
       <c r="G120" s="3" t="n">
         <v>3000</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="I120" s="3" t="n">
         <v>0</v>
@@ -3427,21 +3469,21 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>לוח 51 | פריסה 3</t>
+          <t>לוח 49 | פריסה 8</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
+          <t>1000x3000 | ניצול 100% | 2 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B122" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C122" s="3" t="n">
         <v>1</v>
@@ -3453,11 +3495,11 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>9060×940 #5 ח1/4</t>
+          <t>9060×800 #1 ח2/4</t>
         </is>
       </c>
       <c r="F122" s="3" t="n">
-        <v>940</v>
+        <v>800</v>
       </c>
       <c r="G122" s="3" t="n">
         <v>3000</v>
@@ -3470,71 +3512,92 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>לוח 52 | פריסה 3</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
-        </is>
+      <c r="A123" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="B123" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>6160×1200 #1 ח4/6</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H123" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="I123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="B124" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C124" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D124" s="3" t="inlineStr">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>לוח 50 | פריסה 8</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 100% | 2 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="B125" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
         <is>
           <t>1000x3000</t>
         </is>
       </c>
-      <c r="E124" s="3" t="inlineStr">
-        <is>
-          <t>9060×940 #5 ח2/4</t>
-        </is>
-      </c>
-      <c r="F124" s="3" t="n">
-        <v>940</v>
-      </c>
-      <c r="G124" s="3" t="n">
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>9060×800 #1 ח3/4</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="G125" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="H124" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I124" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>לוח 53 | פריסה 3</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
-        <is>
-          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
-        </is>
+      <c r="H125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B126" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C126" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
@@ -3543,17 +3606,17 @@
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>9060×940 #5 ח3/4</t>
+          <t>6160×1200 #2 ח2/6</t>
         </is>
       </c>
       <c r="F126" s="3" t="n">
-        <v>940</v>
+        <v>200</v>
       </c>
       <c r="G126" s="3" t="n">
         <v>3000</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="I126" s="3" t="n">
         <v>0</v>
@@ -3562,21 +3625,21 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>לוח 54 | פריסה 3</t>
+          <t>לוח 51 | פריסה 8</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
+          <t>1000x3000 | ניצול 100% | 2 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B128" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C128" s="3" t="n">
         <v>1</v>
@@ -3588,11 +3651,11 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>9060×940 #6 ח1/4</t>
+          <t>9060×800 #2 ח1/4</t>
         </is>
       </c>
       <c r="F128" s="3" t="n">
-        <v>940</v>
+        <v>800</v>
       </c>
       <c r="G128" s="3" t="n">
         <v>3000</v>
@@ -3605,71 +3668,92 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>לוח 55 | פריסה 3</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
-        <is>
-          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
-        </is>
+      <c r="A129" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="B129" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>6160×1200 #2 ח4/6</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H129" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="I129" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="B130" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C130" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D130" s="3" t="inlineStr">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>לוח 52 | פריסה 8</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 100% | 2 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="B131" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
         <is>
           <t>1000x3000</t>
         </is>
       </c>
-      <c r="E130" s="3" t="inlineStr">
-        <is>
-          <t>9060×940 #6 ח2/4</t>
-        </is>
-      </c>
-      <c r="F130" s="3" t="n">
-        <v>940</v>
-      </c>
-      <c r="G130" s="3" t="n">
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>9060×800 #2 ח2/4</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="G131" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="H130" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I130" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>לוח 56 | פריסה 3</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
-        <is>
-          <t>1000x3000 | ניצול 94% | 1 חתיכות</t>
-        </is>
+      <c r="H131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B132" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C132" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
@@ -3678,17 +3762,17 @@
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>9060×940 #6 ח3/4</t>
+          <t>6160×1200 #3 ח2/6</t>
         </is>
       </c>
       <c r="F132" s="3" t="n">
-        <v>940</v>
+        <v>200</v>
       </c>
       <c r="G132" s="3" t="n">
         <v>3000</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="I132" s="3" t="n">
         <v>0</v>
@@ -3697,7 +3781,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>לוח 57 | פריסה 6</t>
+          <t>לוח 53 | פריסה 8</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -3708,10 +3792,10 @@
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B134" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>1</v>
@@ -3723,7 +3807,7 @@
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>9060×800 #1 ח1/4</t>
+          <t>9060×800 #2 ח3/4</t>
         </is>
       </c>
       <c r="F134" s="3" t="n">
@@ -3741,10 +3825,10 @@
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B135" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>2</v>
@@ -3756,7 +3840,7 @@
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>6160×1200 #1 ח2/6</t>
+          <t>6160×1200 #3 ח4/6</t>
         </is>
       </c>
       <c r="F135" s="3" t="n">
@@ -3775,21 +3859,21 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>לוח 58 | פריסה 6</t>
+          <t>לוח 54 | פריסה 11</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>1000x3000 | ניצול 100% | 2 חתיכות</t>
+          <t>1000x3000 | ניצול 96% | 4 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B137" s="3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C137" s="3" t="n">
         <v>1</v>
@@ -3801,7 +3885,7 @@
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>9060×800 #1 ח2/4</t>
+          <t>9060×800 #3 ח1/4</t>
         </is>
       </c>
       <c r="F137" s="3" t="n">
@@ -3819,10 +3903,10 @@
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B138" s="3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C138" s="3" t="n">
         <v>2</v>
@@ -3834,14 +3918,14 @@
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>6160×1200 #1 ח4/6</t>
+          <t>6160×1200 #1 ח5/6</t>
         </is>
       </c>
       <c r="F138" s="3" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="H138" s="3" t="n">
         <v>800</v>
@@ -3851,26 +3935,47 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>לוח 59 | פריסה 6</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>1000x3000 | ניצול 100% | 2 חתיכות</t>
-        </is>
+      <c r="A139" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="B139" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C139" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>6160×1200 #2 ח5/6</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="G139" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H139" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="I139" s="3" t="n">
+        <v>1000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B140" s="3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C140" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
@@ -3879,76 +3984,76 @@
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>9060×800 #1 ח3/4</t>
+          <t>6160×1200 #3 ח5/6</t>
         </is>
       </c>
       <c r="F140" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="G140" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H140" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="G140" s="3" t="n">
+      <c r="I140" s="3" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>לוח 55 | פריסה 12</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 83% | 4 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="B142" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C142" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>9060×800 #3 ח2/4</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="G142" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="H140" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I140" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="B141" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="C141" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D141" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E141" s="3" t="inlineStr">
-        <is>
-          <t>6160×1200 #2 ח2/6</t>
-        </is>
-      </c>
-      <c r="F141" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="G141" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H141" s="3" t="n">
-        <v>800</v>
-      </c>
-      <c r="I141" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>לוח 60 | פריסה 6</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
-        <is>
-          <t>1000x3000 | ניצול 100% | 2 חתיכות</t>
-        </is>
+      <c r="H142" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B143" s="3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C143" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
@@ -3957,17 +4062,17 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>9060×800 #2 ח1/4</t>
+          <t>6160×1200 #1 ח6/6</t>
         </is>
       </c>
       <c r="F143" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="G143" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="H143" s="3" t="n">
         <v>800</v>
-      </c>
-      <c r="G143" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H143" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="I143" s="3" t="n">
         <v>0</v>
@@ -3975,13 +4080,13 @@
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B144" s="3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C144" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
@@ -3990,76 +4095,76 @@
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>6160×1200 #2 ח4/6</t>
+          <t>6160×1200 #2 ח6/6</t>
         </is>
       </c>
       <c r="F144" s="3" t="n">
         <v>200</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>3000</v>
+        <v>160</v>
       </c>
       <c r="H144" s="3" t="n">
         <v>800</v>
       </c>
       <c r="I144" s="3" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>לוח 61 | פריסה 6</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
-        <is>
-          <t>1000x3000 | ניצול 100% | 2 חתיכות</t>
-        </is>
+      <c r="A145" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="B145" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C145" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>1000x3000</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>6160×1200 #3 ח6/6</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="G145" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="H145" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="I145" s="3" t="n">
+        <v>320</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="B146" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="C146" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D146" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E146" s="3" t="inlineStr">
-        <is>
-          <t>9060×800 #2 ח2/4</t>
-        </is>
-      </c>
-      <c r="F146" s="3" t="n">
-        <v>800</v>
-      </c>
-      <c r="G146" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H146" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I146" s="3" t="n">
-        <v>0</v>
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>לוח 56 | פריסה 13</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>1000x3000 | ניצול 80% | 1 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B147" s="3" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C147" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
@@ -4068,17 +4173,17 @@
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>6160×1200 #3 ח2/6</t>
+          <t>9060×800 #3 ח3/4</t>
         </is>
       </c>
       <c r="F147" s="3" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="G147" s="3" t="n">
         <v>3000</v>
       </c>
       <c r="H147" s="3" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="I147" s="3" t="n">
         <v>0</v>
@@ -4087,40 +4192,40 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>לוח 62 | פריסה 6</t>
+          <t>לוח 57 | פריסה 3</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>1000x3000 | ניצול 100% | 2 חתיכות</t>
+          <t>1250x2500 | ניצול 99% | 1 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B149" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C149" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>1000x3000</t>
+          <t>1250x2500</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>9060×800 #2 ח3/4</t>
+          <t>6160×1240 #1 ח1/3</t>
         </is>
       </c>
       <c r="F149" s="3" t="n">
-        <v>800</v>
+        <v>1240</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="H149" s="3" t="n">
         <v>0</v>
@@ -4130,219 +4235,177 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="B150" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="C150" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D150" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E150" s="3" t="inlineStr">
-        <is>
-          <t>6160×1200 #3 ח4/6</t>
-        </is>
-      </c>
-      <c r="F150" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="G150" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H150" s="3" t="n">
-        <v>800</v>
-      </c>
-      <c r="I150" s="3" t="n">
-        <v>0</v>
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>לוח 58 | פריסה 3</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>1250x2500 | ניצול 99% | 1 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="inlineStr">
-        <is>
-          <t>לוח 63 | פריסה 9</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
-        <is>
-          <t>1000x3000 | ניצול 96% | 4 חתיכות</t>
-        </is>
+      <c r="A151" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="B151" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C151" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>1250x2500</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>6160×1240 #1 ח2/3</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="n">
+        <v>1240</v>
+      </c>
+      <c r="G151" s="3" t="n">
+        <v>2500</v>
+      </c>
+      <c r="H151" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="B152" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="C152" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D152" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E152" s="3" t="inlineStr">
-        <is>
-          <t>9060×800 #3 ח1/4</t>
-        </is>
-      </c>
-      <c r="F152" s="3" t="n">
-        <v>800</v>
-      </c>
-      <c r="G152" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H152" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I152" s="3" t="n">
-        <v>0</v>
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>לוח 59 | פריסה 3</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>1250x2500 | ניצול 99% | 1 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B153" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C153" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>1000x3000</t>
+          <t>1250x2500</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>6160×1240 #1 ח5/6</t>
+          <t>6160×1240 #2 ח1/3</t>
         </is>
       </c>
       <c r="F153" s="3" t="n">
-        <v>160</v>
+        <v>1240</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="I153" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="B154" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="C154" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D154" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E154" s="3" t="inlineStr">
-        <is>
-          <t>6160×1240 #2 ח5/6</t>
-        </is>
-      </c>
-      <c r="F154" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="G154" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H154" s="3" t="n">
-        <v>800</v>
-      </c>
-      <c r="I154" s="3" t="n">
-        <v>1000</v>
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>לוח 60 | פריסה 3</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>1250x2500 | ניצול 99% | 1 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B155" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C155" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>1000x3000</t>
+          <t>1250x2500</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>6160×1240 #3 ח5/6</t>
+          <t>6160×1240 #2 ח2/3</t>
         </is>
       </c>
       <c r="F155" s="3" t="n">
-        <v>160</v>
+        <v>1240</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="H155" s="3" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="I155" s="3" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>לוח 64 | פריסה 9</t>
+          <t>לוח 61 | פריסה 3</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>1000x3000 | ניצול 96% | 4 חתיכות</t>
+          <t>1250x2500 | ניצול 99% | 1 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B157" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C157" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>1000x3000</t>
+          <t>1250x2500</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>9060×800 #3 ח2/4</t>
+          <t>6160×1240 #3 ח1/3</t>
         </is>
       </c>
       <c r="F157" s="3" t="n">
-        <v>800</v>
+        <v>1240</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="H157" s="3" t="n">
         <v>0</v>
@@ -4352,213 +4415,150 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="B158" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="C158" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D158" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E158" s="3" t="inlineStr">
-        <is>
-          <t>6160×1240 #4 ח5/6</t>
-        </is>
-      </c>
-      <c r="F158" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="G158" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H158" s="3" t="n">
-        <v>800</v>
-      </c>
-      <c r="I158" s="3" t="n">
-        <v>0</v>
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>לוח 62 | פריסה 3</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>1250x2500 | ניצול 99% | 1 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B159" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C159" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>1250x2500</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="inlineStr">
+        <is>
+          <t>6160×1240 #3 ח2/3</t>
+        </is>
+      </c>
+      <c r="F159" s="3" t="n">
+        <v>1240</v>
+      </c>
+      <c r="G159" s="3" t="n">
+        <v>2500</v>
+      </c>
+      <c r="H159" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I159" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>לוח 63 | פריסה 3</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>1250x2500 | ניצול 99% | 1 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="B161" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D159" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E159" s="3" t="inlineStr">
-        <is>
-          <t>6160×1240 #5 ח5/6</t>
-        </is>
-      </c>
-      <c r="F159" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="G159" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H159" s="3" t="n">
-        <v>800</v>
-      </c>
-      <c r="I159" s="3" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="B160" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="C160" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D160" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E160" s="3" t="inlineStr">
-        <is>
-          <t>6160×1240 #6 ח5/6</t>
-        </is>
-      </c>
-      <c r="F160" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="G160" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H160" s="3" t="n">
-        <v>800</v>
-      </c>
-      <c r="I160" s="3" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
-        <is>
-          <t>לוח 65 | פריסה 12</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
-        <is>
-          <t>1000x3000 | ניצול 96% | 4 חתיכות</t>
-        </is>
+      <c r="C161" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>1250x2500</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="inlineStr">
+        <is>
+          <t>6160×1240 #4 ח1/3</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="n">
+        <v>1240</v>
+      </c>
+      <c r="G161" s="3" t="n">
+        <v>2500</v>
+      </c>
+      <c r="H161" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I161" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="3" t="n">
-        <v>65</v>
-      </c>
-      <c r="B162" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="C162" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D162" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E162" s="3" t="inlineStr">
-        <is>
-          <t>9060×800 #3 ח3/4</t>
-        </is>
-      </c>
-      <c r="F162" s="3" t="n">
-        <v>800</v>
-      </c>
-      <c r="G162" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H162" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I162" s="3" t="n">
-        <v>0</v>
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>לוח 64 | פריסה 3</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>1250x2500 | ניצול 99% | 1 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="3" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B163" s="3" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C163" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>1000x3000</t>
+          <t>1250x2500</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>6160×1200 #1 ח5/6</t>
+          <t>6160×1240 #4 ח2/3</t>
         </is>
       </c>
       <c r="F163" s="3" t="n">
-        <v>160</v>
+        <v>1240</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="H163" s="3" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="I163" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="3" t="n">
-        <v>65</v>
-      </c>
-      <c r="B164" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="C164" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D164" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E164" s="3" t="inlineStr">
-        <is>
-          <t>6160×1200 #2 ח5/6</t>
-        </is>
-      </c>
-      <c r="F164" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="G164" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H164" s="3" t="n">
-        <v>800</v>
-      </c>
-      <c r="I164" s="3" t="n">
-        <v>1000</v>
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>לוח 65 | פריסה 3</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>1250x2500 | ניצול 99% | 1 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="165">
@@ -4566,43 +4566,43 @@
         <v>65</v>
       </c>
       <c r="B165" s="3" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C165" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>1000x3000</t>
+          <t>1250x2500</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>6160×1200 #3 ח5/6</t>
+          <t>6160×1240 #5 ח1/3</t>
         </is>
       </c>
       <c r="F165" s="3" t="n">
-        <v>160</v>
+        <v>1240</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="H165" s="3" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="I165" s="3" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>לוח 66 | פריסה 13</t>
+          <t>לוח 66 | פריסה 3</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>1000x3000 | ניצול 91% | 11 חתיכות</t>
+          <t>1250x2500 | ניצול 99% | 1 חתיכות</t>
         </is>
       </c>
     </row>
@@ -4611,26 +4611,26 @@
         <v>66</v>
       </c>
       <c r="B167" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C167" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>1000x3000</t>
+          <t>1250x2500</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>1240×1200 #1 ח1/2</t>
+          <t>6160×1240 #5 ח2/3</t>
         </is>
       </c>
       <c r="F167" s="3" t="n">
-        <v>1000</v>
+        <v>1240</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>1200</v>
+        <v>2500</v>
       </c>
       <c r="H167" s="3" t="n">
         <v>0</v>
@@ -4640,369 +4640,285 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="B168" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="C168" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D168" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E168" s="3" t="inlineStr">
-        <is>
-          <t>1240×1200 #2 ח1/2</t>
-        </is>
-      </c>
-      <c r="F168" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G168" s="3" t="n">
-        <v>1200</v>
-      </c>
-      <c r="H168" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I168" s="3" t="n">
-        <v>1200</v>
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>לוח 67 | פריסה 3</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>1250x2500 | ניצול 99% | 1 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="3" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B169" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C169" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>1000x3000</t>
+          <t>1250x2500</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>6160×1240 #1 ח6/6</t>
+          <t>6160×1240 #6 ח1/3</t>
         </is>
       </c>
       <c r="F169" s="3" t="n">
-        <v>160</v>
+        <v>1240</v>
       </c>
       <c r="G169" s="3" t="n">
-        <v>240</v>
+        <v>2500</v>
       </c>
       <c r="H169" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I169" s="3" t="n">
-        <v>2400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="B170" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="C170" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D170" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E170" s="3" t="inlineStr">
-        <is>
-          <t>6160×1240 #3 ח6/6</t>
-        </is>
-      </c>
-      <c r="F170" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="G170" s="3" t="n">
-        <v>240</v>
-      </c>
-      <c r="H170" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="I170" s="3" t="n">
-        <v>2400</v>
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>לוח 68 | פריסה 3</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>1250x2500 | ניצול 99% | 1 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="3" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B171" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C171" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>1000x3000</t>
+          <t>1250x2500</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>6160×1240 #5 ח6/6</t>
+          <t>6160×1240 #6 ח2/3</t>
         </is>
       </c>
       <c r="F171" s="3" t="n">
-        <v>160</v>
+        <v>1240</v>
       </c>
       <c r="G171" s="3" t="n">
-        <v>240</v>
+        <v>2500</v>
       </c>
       <c r="H171" s="3" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="I171" s="3" t="n">
-        <v>2400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="B172" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="C172" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="D172" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E172" s="3" t="inlineStr">
-        <is>
-          <t>6160×1200 #1 ח6/6</t>
-        </is>
-      </c>
-      <c r="F172" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="G172" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="H172" s="3" t="n">
-        <v>480</v>
-      </c>
-      <c r="I172" s="3" t="n">
-        <v>2400</v>
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>לוח 69 | פריסה 4</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>1250x2500 | ניצול 95% | 2 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="3" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B173" s="3" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C173" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>1000x3000</t>
+          <t>1250x2500</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>6160×1200 #2 ח6/6</t>
+          <t>1240×1200 #1</t>
         </is>
       </c>
       <c r="F173" s="3" t="n">
-        <v>200</v>
+        <v>1240</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>160</v>
+        <v>1200</v>
       </c>
       <c r="H173" s="3" t="n">
-        <v>680</v>
+        <v>0</v>
       </c>
       <c r="I173" s="3" t="n">
-        <v>2400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="3" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B174" s="3" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C174" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>1000x3000</t>
+          <t>1250x2500</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>6160×1200 #3 ח6/6</t>
+          <t>1240×1200 #2</t>
         </is>
       </c>
       <c r="F174" s="3" t="n">
-        <v>160</v>
+        <v>1240</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>200</v>
+        <v>1200</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="I174" s="3" t="n">
-        <v>2560</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="B175" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="C175" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="D175" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E175" s="3" t="inlineStr">
-        <is>
-          <t>6160×1240 #2 ח6/6</t>
-        </is>
-      </c>
-      <c r="F175" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="G175" s="3" t="n">
-        <v>240</v>
-      </c>
-      <c r="H175" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I175" s="3" t="n">
-        <v>2640</v>
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>לוח 70 | פריסה 4</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>1250x2500 | ניצול 95% | 2 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="3" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B176" s="3" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C176" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>1000x3000</t>
+          <t>1250x2500</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>6160×1240 #4 ח6/6</t>
+          <t>1240×1200 #3</t>
         </is>
       </c>
       <c r="F176" s="3" t="n">
-        <v>160</v>
+        <v>1240</v>
       </c>
       <c r="G176" s="3" t="n">
-        <v>240</v>
+        <v>1200</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="I176" s="3" t="n">
-        <v>2640</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="3" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B177" s="3" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C177" s="3" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>1000x3000</t>
+          <t>1250x2500</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>6160×1240 #6 ח6/6</t>
+          <t>1240×1200 #4</t>
         </is>
       </c>
       <c r="F177" s="3" t="n">
-        <v>160</v>
+        <v>1240</v>
       </c>
       <c r="G177" s="3" t="n">
-        <v>240</v>
+        <v>1200</v>
       </c>
       <c r="H177" s="3" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="I177" s="3" t="n">
-        <v>2640</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>לוח 67 | פריסה 10</t>
+          <t>לוח 71 | פריסה 4</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>1000x3000 | ניצול 80% | 2 חתיכות</t>
+          <t>1250x2500 | ניצול 95% | 2 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="3" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B179" s="3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C179" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>1000x3000</t>
+          <t>1250x2500</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>1240×1200 #3 ח1/2</t>
+          <t>1240×1200 #5</t>
         </is>
       </c>
       <c r="F179" s="3" t="n">
-        <v>1000</v>
+        <v>1240</v>
       </c>
       <c r="G179" s="3" t="n">
         <v>1200</v>
@@ -5016,26 +4932,26 @@
     </row>
     <row r="180">
       <c r="A180" s="3" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B180" s="3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C180" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>1000x3000</t>
+          <t>1250x2500</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>1240×1200 #4 ח1/2</t>
+          <t>1240×1200 #6</t>
         </is>
       </c>
       <c r="F180" s="3" t="n">
-        <v>1000</v>
+        <v>1240</v>
       </c>
       <c r="G180" s="3" t="n">
         <v>1200</v>
@@ -5050,40 +4966,40 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>לוח 68 | פריסה 10</t>
+          <t>לוח 72 | פריסה 5</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>1000x3000 | ניצול 80% | 2 חתיכות</t>
+          <t>1250x2500 | ניצול 92% | 2 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="3" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B182" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C182" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>1000x3000</t>
+          <t>1250x2500</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>1240×1200 #5 ח1/2</t>
+          <t>6160×1240 #1 ח3/3</t>
         </is>
       </c>
       <c r="F182" s="3" t="n">
-        <v>1000</v>
+        <v>1240</v>
       </c>
       <c r="G182" s="3" t="n">
-        <v>1200</v>
+        <v>1160</v>
       </c>
       <c r="H182" s="3" t="n">
         <v>0</v>
@@ -5094,74 +5010,74 @@
     </row>
     <row r="183">
       <c r="A183" s="3" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B183" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C183" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>1000x3000</t>
+          <t>1250x2500</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>1240×1200 #6 ח1/2</t>
+          <t>6160×1240 #2 ח3/3</t>
         </is>
       </c>
       <c r="F183" s="3" t="n">
-        <v>1000</v>
+        <v>1240</v>
       </c>
       <c r="G183" s="3" t="n">
-        <v>1200</v>
+        <v>1160</v>
       </c>
       <c r="H183" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I183" s="3" t="n">
-        <v>1200</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>לוח 69 | פריסה 7</t>
+          <t>לוח 73 | פריסה 5</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>1000x3000 | ניצול 96% | 4 חתיכות</t>
+          <t>1250x2500 | ניצול 92% | 2 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="3" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B185" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C185" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>1000x3000</t>
+          <t>1250x2500</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>6160×1240 #1 ח2/6</t>
+          <t>6160×1240 #3 ח3/3</t>
         </is>
       </c>
       <c r="F185" s="3" t="n">
-        <v>240</v>
+        <v>1240</v>
       </c>
       <c r="G185" s="3" t="n">
-        <v>3000</v>
+        <v>1160</v>
       </c>
       <c r="H185" s="3" t="n">
         <v>0</v>
@@ -5172,176 +5088,155 @@
     </row>
     <row r="186">
       <c r="A186" s="3" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B186" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C186" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>1000x3000</t>
+          <t>1250x2500</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>6160×1240 #1 ח4/6</t>
+          <t>6160×1240 #4 ח3/3</t>
         </is>
       </c>
       <c r="F186" s="3" t="n">
-        <v>240</v>
+        <v>1240</v>
       </c>
       <c r="G186" s="3" t="n">
-        <v>3000</v>
+        <v>1160</v>
       </c>
       <c r="H186" s="3" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="I186" s="3" t="n">
-        <v>0</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="3" t="n">
-        <v>69</v>
-      </c>
-      <c r="B187" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C187" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D187" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E187" s="3" t="inlineStr">
-        <is>
-          <t>6160×1240 #2 ח2/6</t>
-        </is>
-      </c>
-      <c r="F187" s="3" t="n">
-        <v>240</v>
-      </c>
-      <c r="G187" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H187" s="3" t="n">
-        <v>480</v>
-      </c>
-      <c r="I187" s="3" t="n">
-        <v>0</v>
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>לוח 74 | פריסה 5</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>1250x2500 | ניצול 92% | 2 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="3" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B188" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C188" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>1000x3000</t>
+          <t>1250x2500</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>6160×1240 #2 ח4/6</t>
+          <t>6160×1240 #5 ח3/3</t>
         </is>
       </c>
       <c r="F188" s="3" t="n">
-        <v>240</v>
+        <v>1240</v>
       </c>
       <c r="G188" s="3" t="n">
-        <v>3000</v>
+        <v>1160</v>
       </c>
       <c r="H188" s="3" t="n">
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="I188" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="inlineStr">
-        <is>
-          <t>לוח 70 | פריסה 7</t>
-        </is>
-      </c>
-      <c r="D189" s="2" t="inlineStr">
-        <is>
-          <t>1000x3000 | ניצול 96% | 4 חתיכות</t>
-        </is>
+      <c r="A189" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="B189" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C189" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t>1250x2500</t>
+        </is>
+      </c>
+      <c r="E189" s="3" t="inlineStr">
+        <is>
+          <t>6160×1240 #6 ח3/3</t>
+        </is>
+      </c>
+      <c r="F189" s="3" t="n">
+        <v>1240</v>
+      </c>
+      <c r="G189" s="3" t="n">
+        <v>1160</v>
+      </c>
+      <c r="H189" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I189" s="3" t="n">
+        <v>1160</v>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="B190" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C190" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D190" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E190" s="3" t="inlineStr">
-        <is>
-          <t>6160×1240 #3 ח2/6</t>
-        </is>
-      </c>
-      <c r="F190" s="3" t="n">
-        <v>240</v>
-      </c>
-      <c r="G190" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H190" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I190" s="3" t="n">
-        <v>0</v>
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>לוח 75 | פריסה 1</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>1500x3000 | ניצול 85% | 2 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="3" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B191" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C191" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>1000x3000</t>
+          <t>1500x3000</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>6160×1240 #3 ח4/6</t>
+          <t>5330×640 #1 ח1/2</t>
         </is>
       </c>
       <c r="F191" s="3" t="n">
-        <v>240</v>
+        <v>640</v>
       </c>
       <c r="G191" s="3" t="n">
         <v>3000</v>
       </c>
       <c r="H191" s="3" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="I191" s="3" t="n">
         <v>0</v>
@@ -5349,176 +5244,155 @@
     </row>
     <row r="192">
       <c r="A192" s="3" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B192" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C192" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>1000x3000</t>
+          <t>1500x3000</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>6160×1240 #4 ח2/6</t>
+          <t>5330×640 #2 ח1/2</t>
         </is>
       </c>
       <c r="F192" s="3" t="n">
-        <v>240</v>
+        <v>640</v>
       </c>
       <c r="G192" s="3" t="n">
         <v>3000</v>
       </c>
       <c r="H192" s="3" t="n">
-        <v>480</v>
+        <v>640</v>
       </c>
       <c r="I192" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="B193" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C193" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D193" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E193" s="3" t="inlineStr">
-        <is>
-          <t>6160×1240 #4 ח4/6</t>
-        </is>
-      </c>
-      <c r="F193" s="3" t="n">
-        <v>240</v>
-      </c>
-      <c r="G193" s="3" t="n">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>לוח 76 | פריסה 1</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>1500x3000 | ניצול 85% | 2 חתיכות</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="B194" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C194" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>1500x3000</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="inlineStr">
+        <is>
+          <t>5330×640 #3 ח1/2</t>
+        </is>
+      </c>
+      <c r="F194" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="G194" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="H193" s="3" t="n">
-        <v>720</v>
-      </c>
-      <c r="I193" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
-        <is>
-          <t>לוח 71 | פריסה 7</t>
-        </is>
-      </c>
-      <c r="D194" s="2" t="inlineStr">
-        <is>
-          <t>1000x3000 | ניצול 96% | 4 חתיכות</t>
-        </is>
+      <c r="H194" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I194" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="3" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B195" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C195" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>1000x3000</t>
+          <t>1500x3000</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>6160×1240 #5 ח2/6</t>
+          <t>5330×640 #4 ח1/2</t>
         </is>
       </c>
       <c r="F195" s="3" t="n">
-        <v>240</v>
+        <v>640</v>
       </c>
       <c r="G195" s="3" t="n">
         <v>3000</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="I195" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="3" t="n">
-        <v>71</v>
-      </c>
-      <c r="B196" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C196" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D196" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E196" s="3" t="inlineStr">
-        <is>
-          <t>6160×1240 #5 ח4/6</t>
-        </is>
-      </c>
-      <c r="F196" s="3" t="n">
-        <v>240</v>
-      </c>
-      <c r="G196" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H196" s="3" t="n">
-        <v>240</v>
-      </c>
-      <c r="I196" s="3" t="n">
-        <v>0</v>
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>לוח 77 | פריסה 1</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>1500x3000 | ניצול 85% | 2 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="3" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B197" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C197" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>1000x3000</t>
+          <t>1500x3000</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>6160×1240 #6 ח2/6</t>
+          <t>5330×640 #5 ח1/2</t>
         </is>
       </c>
       <c r="F197" s="3" t="n">
-        <v>240</v>
+        <v>640</v>
       </c>
       <c r="G197" s="3" t="n">
         <v>3000</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="I197" s="3" t="n">
         <v>0</v>
@@ -5526,32 +5400,32 @@
     </row>
     <row r="198">
       <c r="A198" s="3" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B198" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C198" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>1000x3000</t>
+          <t>1500x3000</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>6160×1240 #6 ח4/6</t>
+          <t>5330×640 #6 ח1/2</t>
         </is>
       </c>
       <c r="F198" s="3" t="n">
-        <v>240</v>
+        <v>640</v>
       </c>
       <c r="G198" s="3" t="n">
         <v>3000</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>720</v>
+        <v>640</v>
       </c>
       <c r="I198" s="3" t="n">
         <v>0</v>
@@ -5560,40 +5434,40 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>לוח 72 | פריסה 14</t>
+          <t>לוח 78 | פריסה 1</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>1000x3000 | ניצול 58% | 6 חתיכות</t>
+          <t>1500x3000 | ניצול 85% | 2 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="3" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B200" s="3" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C200" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>1000x3000</t>
+          <t>1500x3000</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>1240×1200 #1 ח2/2</t>
+          <t>5330×640 #7 ח1/2</t>
         </is>
       </c>
       <c r="F200" s="3" t="n">
-        <v>240</v>
+        <v>640</v>
       </c>
       <c r="G200" s="3" t="n">
-        <v>1200</v>
+        <v>3000</v>
       </c>
       <c r="H200" s="3" t="n">
         <v>0</v>
@@ -5604,98 +5478,77 @@
     </row>
     <row r="201">
       <c r="A201" s="3" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B201" s="3" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C201" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>1000x3000</t>
+          <t>1500x3000</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>1240×1200 #2 ח2/2</t>
+          <t>5330×640 #8 ח1/2</t>
         </is>
       </c>
       <c r="F201" s="3" t="n">
-        <v>240</v>
+        <v>640</v>
       </c>
       <c r="G201" s="3" t="n">
-        <v>1200</v>
+        <v>3000</v>
       </c>
       <c r="H201" s="3" t="n">
-        <v>240</v>
+        <v>640</v>
       </c>
       <c r="I201" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="B202" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="C202" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D202" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E202" s="3" t="inlineStr">
-        <is>
-          <t>1240×1200 #3 ח2/2</t>
-        </is>
-      </c>
-      <c r="F202" s="3" t="n">
-        <v>240</v>
-      </c>
-      <c r="G202" s="3" t="n">
-        <v>1200</v>
-      </c>
-      <c r="H202" s="3" t="n">
-        <v>480</v>
-      </c>
-      <c r="I202" s="3" t="n">
-        <v>0</v>
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>לוח 79 | פריסה 1</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>1500x3000 | ניצול 85% | 2 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="3" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B203" s="3" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C203" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
-          <t>1000x3000</t>
+          <t>1500x3000</t>
         </is>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>1240×1200 #4 ח2/2</t>
+          <t>5330×640 #9 ח1/2</t>
         </is>
       </c>
       <c r="F203" s="3" t="n">
-        <v>240</v>
+        <v>640</v>
       </c>
       <c r="G203" s="3" t="n">
-        <v>1200</v>
+        <v>3000</v>
       </c>
       <c r="H203" s="3" t="n">
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="I203" s="3" t="n">
         <v>0</v>
@@ -5703,310 +5556,289 @@
     </row>
     <row r="204">
       <c r="A204" s="3" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B204" s="3" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C204" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>1000x3000</t>
+          <t>1500x3000</t>
         </is>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>1240×1200 #5 ח2/2</t>
+          <t>5330×640 #10 ח1/2</t>
         </is>
       </c>
       <c r="F204" s="3" t="n">
-        <v>240</v>
+        <v>640</v>
       </c>
       <c r="G204" s="3" t="n">
-        <v>1200</v>
+        <v>3000</v>
       </c>
       <c r="H204" s="3" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="I204" s="3" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="B205" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="C205" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="D205" s="3" t="inlineStr">
-        <is>
-          <t>1000x3000</t>
-        </is>
-      </c>
-      <c r="E205" s="3" t="inlineStr">
-        <is>
-          <t>1240×1200 #6 ח2/2</t>
-        </is>
-      </c>
-      <c r="F205" s="3" t="n">
-        <v>240</v>
-      </c>
-      <c r="G205" s="3" t="n">
-        <v>1200</v>
-      </c>
-      <c r="H205" s="3" t="n">
-        <v>240</v>
-      </c>
-      <c r="I205" s="3" t="n">
-        <v>1200</v>
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>לוח 80 | פריסה 1</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>1500x3000 | ניצול 85% | 2 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="inlineStr">
-        <is>
-          <t>לוח 73 | פריסה 15</t>
-        </is>
-      </c>
-      <c r="D206" s="2" t="inlineStr">
-        <is>
-          <t>1220x2440 | ניצול 76% | 3 חתיכות</t>
-        </is>
+      <c r="A206" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="B206" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C206" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D206" s="3" t="inlineStr">
+        <is>
+          <t>1500x3000</t>
+        </is>
+      </c>
+      <c r="E206" s="3" t="inlineStr">
+        <is>
+          <t>5330×640 #11 ח1/2</t>
+        </is>
+      </c>
+      <c r="F206" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="G206" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H206" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I206" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="3" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B207" s="3" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C207" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D207" s="3" t="inlineStr">
         <is>
-          <t>1220x2440</t>
+          <t>1500x3000</t>
         </is>
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>940×800 #1</t>
+          <t>5330×640 #12 ח1/2</t>
         </is>
       </c>
       <c r="F207" s="3" t="n">
-        <v>940</v>
+        <v>640</v>
       </c>
       <c r="G207" s="3" t="n">
-        <v>800</v>
+        <v>3000</v>
       </c>
       <c r="H207" s="3" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="I207" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="3" t="n">
-        <v>73</v>
-      </c>
-      <c r="B208" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="C208" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D208" s="3" t="inlineStr">
-        <is>
-          <t>1220x2440</t>
-        </is>
-      </c>
-      <c r="E208" s="3" t="inlineStr">
-        <is>
-          <t>940×800 #2</t>
-        </is>
-      </c>
-      <c r="F208" s="3" t="n">
-        <v>940</v>
-      </c>
-      <c r="G208" s="3" t="n">
-        <v>800</v>
-      </c>
-      <c r="H208" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I208" s="3" t="n">
-        <v>800</v>
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>לוח 81 | פריסה 2</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>1500x3000 | ניצול 66% | 2 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="3" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B209" s="3" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C209" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>1220x2440</t>
+          <t>1500x3000</t>
         </is>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>940×800 #3</t>
+          <t>5330×640 #1 ח2/2</t>
         </is>
       </c>
       <c r="F209" s="3" t="n">
-        <v>940</v>
+        <v>640</v>
       </c>
       <c r="G209" s="3" t="n">
-        <v>800</v>
+        <v>2330</v>
       </c>
       <c r="H209" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I209" s="3" t="n">
-        <v>1600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="inlineStr">
-        <is>
-          <t>לוח 74 | פריסה 15</t>
-        </is>
-      </c>
-      <c r="D210" s="2" t="inlineStr">
-        <is>
-          <t>1220x2440 | ניצול 76% | 3 חתיכות</t>
-        </is>
+      <c r="A210" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="B210" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C210" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D210" s="3" t="inlineStr">
+        <is>
+          <t>1500x3000</t>
+        </is>
+      </c>
+      <c r="E210" s="3" t="inlineStr">
+        <is>
+          <t>5330×640 #2 ח2/2</t>
+        </is>
+      </c>
+      <c r="F210" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="G210" s="3" t="n">
+        <v>2330</v>
+      </c>
+      <c r="H210" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="I210" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="3" t="n">
-        <v>74</v>
-      </c>
-      <c r="B211" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="C211" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D211" s="3" t="inlineStr">
-        <is>
-          <t>1220x2440</t>
-        </is>
-      </c>
-      <c r="E211" s="3" t="inlineStr">
-        <is>
-          <t>940×800 #4</t>
-        </is>
-      </c>
-      <c r="F211" s="3" t="n">
-        <v>940</v>
-      </c>
-      <c r="G211" s="3" t="n">
-        <v>800</v>
-      </c>
-      <c r="H211" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I211" s="3" t="n">
-        <v>0</v>
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>לוח 82 | פריסה 2</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>1500x3000 | ניצול 66% | 2 חתיכות</t>
+        </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="3" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="B212" s="3" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C212" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>1220x2440</t>
+          <t>1500x3000</t>
         </is>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>940×800 #5</t>
+          <t>5330×640 #3 ח2/2</t>
         </is>
       </c>
       <c r="F212" s="3" t="n">
-        <v>940</v>
+        <v>640</v>
       </c>
       <c r="G212" s="3" t="n">
-        <v>800</v>
+        <v>2330</v>
       </c>
       <c r="H212" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I212" s="3" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="3" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="B213" s="3" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C213" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
-          <t>1220x2440</t>
+          <t>1500x3000</t>
         </is>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
-          <t>940×800 #6</t>
+          <t>5330×640 #4 ח2/2</t>
         </is>
       </c>
       <c r="F213" s="3" t="n">
-        <v>940</v>
+        <v>640</v>
       </c>
       <c r="G213" s="3" t="n">
-        <v>800</v>
+        <v>2330</v>
       </c>
       <c r="H213" s="3" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="I213" s="3" t="n">
-        <v>1600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>לוח 75 | פריסה 1</t>
+          <t>לוח 83 | פריסה 2</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>1500x3000 | ניצול 85% | 2 חתיכות</t>
+          <t>1500x3000 | ניצול 66% | 2 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="3" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B215" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C215" s="3" t="n">
         <v>1</v>
@@ -6018,14 +5850,14 @@
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>5330×640 #1 ח1/2</t>
+          <t>5330×640 #5 ח2/2</t>
         </is>
       </c>
       <c r="F215" s="3" t="n">
         <v>640</v>
       </c>
       <c r="G215" s="3" t="n">
-        <v>3000</v>
+        <v>2330</v>
       </c>
       <c r="H215" s="3" t="n">
         <v>0</v>
@@ -6036,10 +5868,10 @@
     </row>
     <row r="216">
       <c r="A216" s="3" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B216" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C216" s="3" t="n">
         <v>2</v>
@@ -6051,14 +5883,14 @@
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>5330×640 #2 ח1/2</t>
+          <t>5330×640 #6 ח2/2</t>
         </is>
       </c>
       <c r="F216" s="3" t="n">
         <v>640</v>
       </c>
       <c r="G216" s="3" t="n">
-        <v>3000</v>
+        <v>2330</v>
       </c>
       <c r="H216" s="3" t="n">
         <v>640</v>
@@ -6070,21 +5902,21 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>לוח 76 | פריסה 1</t>
+          <t>לוח 84 | פריסה 2</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>1500x3000 | ניצול 85% | 2 חתיכות</t>
+          <t>1500x3000 | ניצול 66% | 2 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="3" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B218" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C218" s="3" t="n">
         <v>1</v>
@@ -6096,14 +5928,14 @@
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>5330×640 #3 ח1/2</t>
+          <t>5330×640 #7 ח2/2</t>
         </is>
       </c>
       <c r="F218" s="3" t="n">
         <v>640</v>
       </c>
       <c r="G218" s="3" t="n">
-        <v>3000</v>
+        <v>2330</v>
       </c>
       <c r="H218" s="3" t="n">
         <v>0</v>
@@ -6114,10 +5946,10 @@
     </row>
     <row r="219">
       <c r="A219" s="3" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B219" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C219" s="3" t="n">
         <v>2</v>
@@ -6129,14 +5961,14 @@
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
-          <t>5330×640 #4 ח1/2</t>
+          <t>5330×640 #8 ח2/2</t>
         </is>
       </c>
       <c r="F219" s="3" t="n">
         <v>640</v>
       </c>
       <c r="G219" s="3" t="n">
-        <v>3000</v>
+        <v>2330</v>
       </c>
       <c r="H219" s="3" t="n">
         <v>640</v>
@@ -6148,21 +5980,21 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>לוח 77 | פריסה 1</t>
+          <t>לוח 85 | פריסה 2</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>1500x3000 | ניצול 85% | 2 חתיכות</t>
+          <t>1500x3000 | ניצול 66% | 2 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="3" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B221" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C221" s="3" t="n">
         <v>1</v>
@@ -6174,14 +6006,14 @@
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
-          <t>5330×640 #5 ח1/2</t>
+          <t>5330×640 #9 ח2/2</t>
         </is>
       </c>
       <c r="F221" s="3" t="n">
         <v>640</v>
       </c>
       <c r="G221" s="3" t="n">
-        <v>3000</v>
+        <v>2330</v>
       </c>
       <c r="H221" s="3" t="n">
         <v>0</v>
@@ -6192,10 +6024,10 @@
     </row>
     <row r="222">
       <c r="A222" s="3" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B222" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C222" s="3" t="n">
         <v>2</v>
@@ -6207,14 +6039,14 @@
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
-          <t>5330×640 #6 ח1/2</t>
+          <t>5330×640 #10 ח2/2</t>
         </is>
       </c>
       <c r="F222" s="3" t="n">
         <v>640</v>
       </c>
       <c r="G222" s="3" t="n">
-        <v>3000</v>
+        <v>2330</v>
       </c>
       <c r="H222" s="3" t="n">
         <v>640</v>
@@ -6226,21 +6058,21 @@
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>לוח 78 | פריסה 1</t>
+          <t>לוח 86 | פריסה 2</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>1500x3000 | ניצול 85% | 2 חתיכות</t>
+          <t>1500x3000 | ניצול 66% | 2 חתיכות</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="3" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B224" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C224" s="3" t="n">
         <v>1</v>
@@ -6252,14 +6084,14 @@
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
-          <t>5330×640 #7 ח1/2</t>
+          <t>5330×640 #11 ח2/2</t>
         </is>
       </c>
       <c r="F224" s="3" t="n">
         <v>640</v>
       </c>
       <c r="G224" s="3" t="n">
-        <v>3000</v>
+        <v>2330</v>
       </c>
       <c r="H224" s="3" t="n">
         <v>0</v>
@@ -6270,10 +6102,10 @@
     </row>
     <row r="225">
       <c r="A225" s="3" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B225" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C225" s="3" t="n">
         <v>2</v>
@@ -6285,14 +6117,14 @@
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
-          <t>5330×640 #8 ח1/2</t>
+          <t>5330×640 #12 ח2/2</t>
         </is>
       </c>
       <c r="F225" s="3" t="n">
         <v>640</v>
       </c>
       <c r="G225" s="3" t="n">
-        <v>3000</v>
+        <v>2330</v>
       </c>
       <c r="H225" s="3" t="n">
         <v>640</v>
@@ -6301,804 +6133,180 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="2" t="inlineStr">
-        <is>
-          <t>לוח 79 | פריסה 1</t>
-        </is>
-      </c>
-      <c r="D226" s="2" t="inlineStr">
-        <is>
-          <t>1500x3000 | ניצול 85% | 2 חתיכות</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="B227" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C227" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D227" s="3" t="inlineStr">
-        <is>
-          <t>1500x3000</t>
-        </is>
-      </c>
-      <c r="E227" s="3" t="inlineStr">
-        <is>
-          <t>5330×640 #9 ח1/2</t>
-        </is>
-      </c>
-      <c r="F227" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="G227" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H227" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I227" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="B228" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C228" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D228" s="3" t="inlineStr">
-        <is>
-          <t>1500x3000</t>
-        </is>
-      </c>
-      <c r="E228" s="3" t="inlineStr">
-        <is>
-          <t>5330×640 #10 ח1/2</t>
-        </is>
-      </c>
-      <c r="F228" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="G228" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H228" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="I228" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="2" t="inlineStr">
-        <is>
-          <t>לוח 80 | פריסה 1</t>
-        </is>
-      </c>
-      <c r="D229" s="2" t="inlineStr">
-        <is>
-          <t>1500x3000 | ניצול 85% | 2 חתיכות</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="B230" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C230" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D230" s="3" t="inlineStr">
-        <is>
-          <t>1500x3000</t>
-        </is>
-      </c>
-      <c r="E230" s="3" t="inlineStr">
-        <is>
-          <t>5330×640 #11 ח1/2</t>
-        </is>
-      </c>
-      <c r="F230" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="G230" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H230" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I230" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="B231" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C231" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D231" s="3" t="inlineStr">
-        <is>
-          <t>1500x3000</t>
-        </is>
-      </c>
-      <c r="E231" s="3" t="inlineStr">
-        <is>
-          <t>5330×640 #12 ח1/2</t>
-        </is>
-      </c>
-      <c r="F231" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="G231" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H231" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="I231" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="2" t="inlineStr">
-        <is>
-          <t>לוח 81 | פריסה 2</t>
-        </is>
-      </c>
-      <c r="D232" s="2" t="inlineStr">
-        <is>
-          <t>1500x3000 | ניצול 66% | 2 חתיכות</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="B233" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C233" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D233" s="3" t="inlineStr">
-        <is>
-          <t>1500x3000</t>
-        </is>
-      </c>
-      <c r="E233" s="3" t="inlineStr">
-        <is>
-          <t>5330×640 #1 ח2/2</t>
-        </is>
-      </c>
-      <c r="F233" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="G233" s="3" t="n">
-        <v>2330</v>
-      </c>
-      <c r="H233" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I233" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="B234" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C234" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D234" s="3" t="inlineStr">
-        <is>
-          <t>1500x3000</t>
-        </is>
-      </c>
-      <c r="E234" s="3" t="inlineStr">
-        <is>
-          <t>5330×640 #2 ח2/2</t>
-        </is>
-      </c>
-      <c r="F234" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="G234" s="3" t="n">
-        <v>2330</v>
-      </c>
-      <c r="H234" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="I234" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="2" t="inlineStr">
-        <is>
-          <t>לוח 82 | פריסה 2</t>
-        </is>
-      </c>
-      <c r="D235" s="2" t="inlineStr">
-        <is>
-          <t>1500x3000 | ניצול 66% | 2 חתיכות</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="B236" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C236" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D236" s="3" t="inlineStr">
-        <is>
-          <t>1500x3000</t>
-        </is>
-      </c>
-      <c r="E236" s="3" t="inlineStr">
-        <is>
-          <t>5330×640 #3 ח2/2</t>
-        </is>
-      </c>
-      <c r="F236" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="G236" s="3" t="n">
-        <v>2330</v>
-      </c>
-      <c r="H236" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I236" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="B237" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C237" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D237" s="3" t="inlineStr">
-        <is>
-          <t>1500x3000</t>
-        </is>
-      </c>
-      <c r="E237" s="3" t="inlineStr">
-        <is>
-          <t>5330×640 #4 ח2/2</t>
-        </is>
-      </c>
-      <c r="F237" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="G237" s="3" t="n">
-        <v>2330</v>
-      </c>
-      <c r="H237" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="I237" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="2" t="inlineStr">
-        <is>
-          <t>לוח 83 | פריסה 2</t>
-        </is>
-      </c>
-      <c r="D238" s="2" t="inlineStr">
-        <is>
-          <t>1500x3000 | ניצול 66% | 2 חתיכות</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="B239" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C239" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D239" s="3" t="inlineStr">
-        <is>
-          <t>1500x3000</t>
-        </is>
-      </c>
-      <c r="E239" s="3" t="inlineStr">
-        <is>
-          <t>5330×640 #5 ח2/2</t>
-        </is>
-      </c>
-      <c r="F239" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="G239" s="3" t="n">
-        <v>2330</v>
-      </c>
-      <c r="H239" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I239" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="B240" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C240" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D240" s="3" t="inlineStr">
-        <is>
-          <t>1500x3000</t>
-        </is>
-      </c>
-      <c r="E240" s="3" t="inlineStr">
-        <is>
-          <t>5330×640 #6 ח2/2</t>
-        </is>
-      </c>
-      <c r="F240" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="G240" s="3" t="n">
-        <v>2330</v>
-      </c>
-      <c r="H240" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="I240" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="2" t="inlineStr">
-        <is>
-          <t>לוח 84 | פריסה 2</t>
-        </is>
-      </c>
-      <c r="D241" s="2" t="inlineStr">
-        <is>
-          <t>1500x3000 | ניצול 66% | 2 חתיכות</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="B242" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C242" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D242" s="3" t="inlineStr">
-        <is>
-          <t>1500x3000</t>
-        </is>
-      </c>
-      <c r="E242" s="3" t="inlineStr">
-        <is>
-          <t>5330×640 #7 ח2/2</t>
-        </is>
-      </c>
-      <c r="F242" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="G242" s="3" t="n">
-        <v>2330</v>
-      </c>
-      <c r="H242" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I242" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="B243" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C243" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D243" s="3" t="inlineStr">
-        <is>
-          <t>1500x3000</t>
-        </is>
-      </c>
-      <c r="E243" s="3" t="inlineStr">
-        <is>
-          <t>5330×640 #8 ח2/2</t>
-        </is>
-      </c>
-      <c r="F243" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="G243" s="3" t="n">
-        <v>2330</v>
-      </c>
-      <c r="H243" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="I243" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="2" t="inlineStr">
-        <is>
-          <t>לוח 85 | פריסה 2</t>
-        </is>
-      </c>
-      <c r="D244" s="2" t="inlineStr">
-        <is>
-          <t>1500x3000 | ניצול 66% | 2 חתיכות</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="B245" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C245" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D245" s="3" t="inlineStr">
-        <is>
-          <t>1500x3000</t>
-        </is>
-      </c>
-      <c r="E245" s="3" t="inlineStr">
-        <is>
-          <t>5330×640 #9 ח2/2</t>
-        </is>
-      </c>
-      <c r="F245" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="G245" s="3" t="n">
-        <v>2330</v>
-      </c>
-      <c r="H245" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I245" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="B246" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C246" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D246" s="3" t="inlineStr">
-        <is>
-          <t>1500x3000</t>
-        </is>
-      </c>
-      <c r="E246" s="3" t="inlineStr">
-        <is>
-          <t>5330×640 #10 ח2/2</t>
-        </is>
-      </c>
-      <c r="F246" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="G246" s="3" t="n">
-        <v>2330</v>
-      </c>
-      <c r="H246" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="I246" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="2" t="inlineStr">
-        <is>
-          <t>לוח 86 | פריסה 2</t>
-        </is>
-      </c>
-      <c r="D247" s="2" t="inlineStr">
-        <is>
-          <t>1500x3000 | ניצול 66% | 2 חתיכות</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="3" t="n">
-        <v>86</v>
-      </c>
-      <c r="B248" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C248" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D248" s="3" t="inlineStr">
-        <is>
-          <t>1500x3000</t>
-        </is>
-      </c>
-      <c r="E248" s="3" t="inlineStr">
-        <is>
-          <t>5330×640 #11 ח2/2</t>
-        </is>
-      </c>
-      <c r="F248" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="G248" s="3" t="n">
-        <v>2330</v>
-      </c>
-      <c r="H248" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I248" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="3" t="n">
-        <v>86</v>
-      </c>
-      <c r="B249" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C249" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D249" s="3" t="inlineStr">
-        <is>
-          <t>1500x3000</t>
-        </is>
-      </c>
-      <c r="E249" s="3" t="inlineStr">
-        <is>
-          <t>5330×640 #12 ח2/2</t>
-        </is>
-      </c>
-      <c r="F249" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="G249" s="3" t="n">
-        <v>2330</v>
-      </c>
-      <c r="H249" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="I249" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="172">
-    <mergeCell ref="A80:C80"/>
+    <mergeCell ref="D57:I57"/>
+    <mergeCell ref="D170:I170"/>
+    <mergeCell ref="A193:C193"/>
     <mergeCell ref="D32:I32"/>
-    <mergeCell ref="D145:I145"/>
+    <mergeCell ref="A208:C208"/>
     <mergeCell ref="D41:I41"/>
+    <mergeCell ref="D154:I154"/>
     <mergeCell ref="A136:C136"/>
-    <mergeCell ref="A105:C105"/>
     <mergeCell ref="D16:I16"/>
     <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A113:C113"/>
-    <mergeCell ref="A210:C210"/>
-    <mergeCell ref="A235:C235"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="D162:I162"/>
     <mergeCell ref="D156:I156"/>
     <mergeCell ref="D214:I214"/>
-    <mergeCell ref="A247:C247"/>
-    <mergeCell ref="A194:C194"/>
+    <mergeCell ref="A71:C71"/>
+    <mergeCell ref="D106:I106"/>
     <mergeCell ref="D18:I18"/>
+    <mergeCell ref="D146:I146"/>
     <mergeCell ref="A181:C181"/>
+    <mergeCell ref="D211:I211"/>
     <mergeCell ref="D220:I220"/>
     <mergeCell ref="D121:I121"/>
     <mergeCell ref="A184:C184"/>
-    <mergeCell ref="D74:I74"/>
+    <mergeCell ref="D130:I130"/>
     <mergeCell ref="A156:C156"/>
-    <mergeCell ref="D68:I68"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="D82:I82"/>
-    <mergeCell ref="D117:I117"/>
-    <mergeCell ref="A93:C93"/>
-    <mergeCell ref="D123:I123"/>
+    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="D67:I67"/>
     <mergeCell ref="A220:C220"/>
-    <mergeCell ref="A229:C229"/>
+    <mergeCell ref="D110:I110"/>
+    <mergeCell ref="A130:C130"/>
     <mergeCell ref="D20:I20"/>
+    <mergeCell ref="A83:C83"/>
     <mergeCell ref="A148:C148"/>
-    <mergeCell ref="D60:I60"/>
-    <mergeCell ref="D109:I109"/>
-    <mergeCell ref="D84:I84"/>
+    <mergeCell ref="D187:I187"/>
+    <mergeCell ref="D69:I69"/>
+    <mergeCell ref="D100:I100"/>
+    <mergeCell ref="A110:C110"/>
     <mergeCell ref="D22:I22"/>
     <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A119:C119"/>
-    <mergeCell ref="D229:I229"/>
-    <mergeCell ref="D111:I111"/>
+    <mergeCell ref="D158:I158"/>
+    <mergeCell ref="A69:C69"/>
     <mergeCell ref="D6:I6"/>
-    <mergeCell ref="D86:I86"/>
-    <mergeCell ref="A66:C66"/>
+    <mergeCell ref="A196:C196"/>
+    <mergeCell ref="D108:I108"/>
+    <mergeCell ref="A205:C205"/>
+    <mergeCell ref="D160:I160"/>
+    <mergeCell ref="A118:C118"/>
     <mergeCell ref="A133:C133"/>
     <mergeCell ref="D136:I136"/>
-    <mergeCell ref="D70:I70"/>
-    <mergeCell ref="A238:C238"/>
-    <mergeCell ref="D210:I210"/>
+    <mergeCell ref="D150:I150"/>
     <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D72:I72"/>
     <mergeCell ref="D78:I78"/>
+    <mergeCell ref="A104:C104"/>
+    <mergeCell ref="A160:C160"/>
+    <mergeCell ref="A175:C175"/>
     <mergeCell ref="D4:I4"/>
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="A14:C14"/>
-    <mergeCell ref="D56:I56"/>
-    <mergeCell ref="D62:I62"/>
+    <mergeCell ref="D71:I71"/>
     <mergeCell ref="D184:I184"/>
-    <mergeCell ref="D58:I58"/>
+    <mergeCell ref="D193:I193"/>
+    <mergeCell ref="D202:I202"/>
+    <mergeCell ref="A106:C106"/>
+    <mergeCell ref="D114:I114"/>
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="D8:I8"/>
-    <mergeCell ref="D64:I64"/>
+    <mergeCell ref="A96:C96"/>
     <mergeCell ref="A121:C121"/>
-    <mergeCell ref="A161:C161"/>
-    <mergeCell ref="D226:I226"/>
+    <mergeCell ref="D73:I73"/>
+    <mergeCell ref="D164:I164"/>
+    <mergeCell ref="A170:C170"/>
     <mergeCell ref="A44:C44"/>
-    <mergeCell ref="D113:I113"/>
-    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A202:C202"/>
     <mergeCell ref="D148:I148"/>
-    <mergeCell ref="D241:I241"/>
+    <mergeCell ref="A211:C211"/>
+    <mergeCell ref="A67:C67"/>
     <mergeCell ref="D35:I35"/>
+    <mergeCell ref="D50:I50"/>
     <mergeCell ref="D44:I44"/>
-    <mergeCell ref="D115:I115"/>
     <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A226:C226"/>
+    <mergeCell ref="A73:C73"/>
     <mergeCell ref="D178:I178"/>
-    <mergeCell ref="A82:C82"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="A241:C241"/>
-    <mergeCell ref="A123:C123"/>
-    <mergeCell ref="D131:I131"/>
+    <mergeCell ref="D172:I172"/>
+    <mergeCell ref="A146:C146"/>
+    <mergeCell ref="A124:C124"/>
+    <mergeCell ref="A172:C172"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="D189:I189"/>
-    <mergeCell ref="D151:I151"/>
-    <mergeCell ref="A84:C84"/>
+    <mergeCell ref="D124:I124"/>
+    <mergeCell ref="A187:C187"/>
+    <mergeCell ref="A108:C108"/>
+    <mergeCell ref="D61:I61"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="D141:I141"/>
+    <mergeCell ref="A158:C158"/>
     <mergeCell ref="A214:C214"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A189:C189"/>
+    <mergeCell ref="D166:I166"/>
     <mergeCell ref="A223:C223"/>
-    <mergeCell ref="D166:I166"/>
-    <mergeCell ref="D48:I48"/>
-    <mergeCell ref="D206:I206"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="D175:I175"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A86:C86"/>
-    <mergeCell ref="D238:I238"/>
-    <mergeCell ref="D125:I125"/>
-    <mergeCell ref="A151:C151"/>
-    <mergeCell ref="D103:I103"/>
-    <mergeCell ref="D235:I235"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="D112:I112"/>
+    <mergeCell ref="D168:I168"/>
+    <mergeCell ref="D205:I205"/>
+    <mergeCell ref="A141:C141"/>
     <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A206:C206"/>
-    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="A150:C150"/>
+    <mergeCell ref="D118:I118"/>
+    <mergeCell ref="D152:I152"/>
     <mergeCell ref="D127:I127"/>
-    <mergeCell ref="D161:I161"/>
     <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A125:C125"/>
-    <mergeCell ref="D232:I232"/>
-    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A190:C190"/>
     <mergeCell ref="A199:C199"/>
-    <mergeCell ref="D142:I142"/>
+    <mergeCell ref="A112:C112"/>
     <mergeCell ref="D24:I24"/>
+    <mergeCell ref="A152:C152"/>
     <mergeCell ref="D38:I38"/>
     <mergeCell ref="D98:I98"/>
-    <mergeCell ref="D129:I129"/>
     <mergeCell ref="A127:C127"/>
     <mergeCell ref="D88:I88"/>
+    <mergeCell ref="A114:C114"/>
     <mergeCell ref="D26:I26"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="D247:I247"/>
+    <mergeCell ref="D63:I63"/>
     <mergeCell ref="A98:C98"/>
     <mergeCell ref="D10:I10"/>
-    <mergeCell ref="A107:C107"/>
     <mergeCell ref="A178:C178"/>
+    <mergeCell ref="D90:I90"/>
+    <mergeCell ref="D208:I208"/>
     <mergeCell ref="D217:I217"/>
+    <mergeCell ref="A61:C61"/>
     <mergeCell ref="A88:C88"/>
-    <mergeCell ref="A70:C70"/>
-    <mergeCell ref="D105:I105"/>
-    <mergeCell ref="D139:I139"/>
-    <mergeCell ref="D52:I52"/>
-    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="D65:I65"/>
+    <mergeCell ref="A162:C162"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="D2:I2"/>
+    <mergeCell ref="A90:C90"/>
     <mergeCell ref="A217:C217"/>
-    <mergeCell ref="D194:I194"/>
-    <mergeCell ref="D76:I76"/>
-    <mergeCell ref="D107:I107"/>
-    <mergeCell ref="A74:C74"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A145:C145"/>
-    <mergeCell ref="A139:C139"/>
-    <mergeCell ref="D66:I66"/>
-    <mergeCell ref="D244:I244"/>
-    <mergeCell ref="A129:C129"/>
-    <mergeCell ref="A76:C76"/>
+    <mergeCell ref="A164:C164"/>
+    <mergeCell ref="D116:I116"/>
+    <mergeCell ref="A154:C154"/>
+    <mergeCell ref="D53:I53"/>
+    <mergeCell ref="D47:I47"/>
     <mergeCell ref="D181:I181"/>
-    <mergeCell ref="D93:I93"/>
+    <mergeCell ref="A116:C116"/>
     <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A131:C131"/>
-    <mergeCell ref="A244:C244"/>
+    <mergeCell ref="D102:I102"/>
+    <mergeCell ref="A100:C100"/>
     <mergeCell ref="D12:I12"/>
-    <mergeCell ref="A109:C109"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="D83:I83"/>
     <mergeCell ref="A35:C35"/>
+    <mergeCell ref="D196:I196"/>
+    <mergeCell ref="D92:I92"/>
     <mergeCell ref="D223:I223"/>
     <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A115:C115"/>
-    <mergeCell ref="A68:C68"/>
     <mergeCell ref="D133:I133"/>
+    <mergeCell ref="A102:C102"/>
     <mergeCell ref="D14:I14"/>
     <mergeCell ref="D29:I29"/>
-    <mergeCell ref="A117:C117"/>
-    <mergeCell ref="A111:C111"/>
-    <mergeCell ref="D54:I54"/>
+    <mergeCell ref="D94:I94"/>
+    <mergeCell ref="A92:C92"/>
     <mergeCell ref="A166:C166"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A232:C232"/>
-    <mergeCell ref="A142:C142"/>
-    <mergeCell ref="D119:I119"/>
-    <mergeCell ref="A103:C103"/>
+    <mergeCell ref="D190:I190"/>
+    <mergeCell ref="A94:C94"/>
     <mergeCell ref="D199:I199"/>
-    <mergeCell ref="D80:I80"/>
+    <mergeCell ref="A168:C168"/>
     <mergeCell ref="A78:C78"/>
+    <mergeCell ref="D96:I96"/>
+    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="D104:I104"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7149,10 +6357,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
@@ -7162,23 +6370,23 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>156</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>1220x2440</t>
+          <t>1250x2500</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>5.95</v>
+        <v>56.25</v>
       </c>
     </row>
     <row r="6">
@@ -7204,7 +6412,7 @@
         <v>86</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>255.95</v>
+        <v>255.25</v>
       </c>
     </row>
     <row r="9">
@@ -7224,7 +6432,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.1164</v>
+        <v>0.114</v>
       </c>
     </row>
   </sheetData>
@@ -7283,11 +6491,11 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>1000x3000</t>
+          <t>1250x2500</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -7319,11 +6527,11 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>1000x3000</t>
+          <t>1250x2500</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -7373,7 +6581,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>1220x2440</t>
+          <t>1000x2000</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
